--- a/LunaRune66.xlsx
+++ b/LunaRune66.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -21,13 +21,15 @@
     <sheet name="Direction" sheetId="17" r:id="rId7"/>
     <sheet name="Lots" sheetId="21" r:id="rId8"/>
     <sheet name="Moon" sheetId="22" r:id="rId9"/>
+    <sheet name="Grammar" sheetId="23" r:id="rId10"/>
+    <sheet name="Interactions" sheetId="24" r:id="rId11"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2533" uniqueCount="1850">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3073" uniqueCount="2141">
   <si>
     <t>編號</t>
   </si>
@@ -5082,16 +5084,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>礦物
-Mineral</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>元素
-Element</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>秩序
 Order</t>
     <phoneticPr fontId="19" type="noConversion"/>
@@ -6358,12 +6350,1594 @@
     <t>連、契、關係、羈絆、強化</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
+  <si>
+    <t>礦物
+Mineral</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>元素
+Element</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="3"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>分類</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="3"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>項目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="3"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>內容</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="18"/>
+        <color theme="3"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>補充說明</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>全域</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>語法分層</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>詞彙層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>卡片位置層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>治理層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>時間修飾層</t>
+    </r>
+  </si>
+  <si>
+    <t>後層時間的月相交互只作修飾，不覆蓋符文本義。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>單卡</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>治理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>解牌方式</t>
+    </r>
+  </si>
+  <si>
+    <t>符文本義＋卡牌方向＋月相交互</t>
+  </si>
+  <si>
+    <t>月相交互只作低權重時間修飾。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>兩卡</t>
+    </r>
+  </si>
+  <si>
+    <t>治理解牌方式</t>
+  </si>
+  <si>
+    <t>因＋果＋月相交互</t>
+  </si>
+  <si>
+    <t>交互描述兩個主題因果如何作用，不單獨決定吉凶。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>三卡</t>
+    </r>
+  </si>
+  <si>
+    <t>源＋轉＋合＋月相交互</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>形成「源起、過程、顯化」的完整圖景。</t>
+    </r>
+  </si>
+  <si>
+    <t>源</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>啟動點、潛因、內在狀態</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>回答事情從何而起。</t>
+    </r>
+  </si>
+  <si>
+    <t>轉</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>過程中介、能量互動、挑戰與助力</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>回答事情如何轉化。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>合</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>結果顯化、整合方向、當下建議</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不是絕對宿命判決。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>五卡</t>
+    </r>
+  </si>
+  <si>
+    <t>過去＋現在＋未來顯化＋周圍環境＋自己心境＋月相交互</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不是「兩卡＋三卡」的拼接。</t>
+    </r>
+  </si>
+  <si>
+    <t>過去</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>過去、成因、既有條件</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>回答「現在為何形成」。</t>
+    </r>
+  </si>
+  <si>
+    <t>現在</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>當前核心狀態</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>五卡主句與主要判讀中心。</t>
+    </r>
+  </si>
+  <si>
+    <t>未來顯化</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>若目前條件延續，最可能的發展趨勢</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不是絕對結果。</t>
+    </r>
+  </si>
+  <si>
+    <t>環境</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>他人、環境、制度、現實限制與外部助力</t>
+    </r>
+  </si>
+  <si>
+    <t>周圍環境的狀態</t>
+  </si>
+  <si>
+    <t>心境</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>本人立場、期待、恐懼、動機與主觀認知</t>
+    </r>
+  </si>
+  <si>
+    <t>自己心境的狀態</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>關係優先</t>
+    </r>
+  </si>
+  <si>
+    <t>過去→現在→未來→環境→心境</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>只計算具有語義關係的卡對，不要求五張彼此全連。</t>
+    </r>
+  </si>
+  <si>
+    <t>OW3gs</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1–6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>因的描述層</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>＋</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">7–11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>果的判定層＋月相交互</t>
+    </r>
+  </si>
+  <si>
+    <t>用符文模型完整形容事件，十一張牌不是等權並列。</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1–6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>因的描述層</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>背景</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 2.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>現在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 3.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>資源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 4.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>意向</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 5.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>外部擾動</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 6.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>尚未成形因素</t>
+    </r>
+  </si>
+  <si>
+    <t>分析產生問題的可能狀態</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7–11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>果的判定層</t>
+    </r>
+  </si>
+  <si>
+    <t>建議：7.成因 8.現在 9.未來 10.環境 11.心境</t>
+  </si>
+  <si>
+    <t>建議該怎麼做的治理原則。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>讀取順序</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>先讀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 7–11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>再掃描</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1–6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>→</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>最後套月相交互</t>
+    </r>
+  </si>
+  <si>
+    <t>治理原則為分成兩個模型。鑑古知今為原則。</t>
+  </si>
+  <si>
+    <t>額外說明</t>
+  </si>
+  <si>
+    <t>有時候跟每日符文交替比照，會很有意思。</t>
+  </si>
+  <si>
+    <t>重在模型的關聯，而非把抽牌維度提高的複雜化。</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>符文交互</t>
+    </r>
+  </si>
+  <si>
+    <t>描述兩個符文語義主題的共鳴、互補、衝突與語氣張力</t>
+  </si>
+  <si>
+    <t>月符沙盒專用，因符文關係為平等。</t>
+  </si>
+  <si>
+    <t>月相交互</t>
+  </si>
+  <si>
+    <t>額外小幅低權重</t>
+  </si>
+  <si>
+    <t>卡片月相跟真實月相的交互作用</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="3"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>真實月相是低權重時間情境修飾。</t>
+    </r>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>關係/模式</t>
+  </si>
+  <si>
+    <t>解釋/訊息</t>
+  </si>
+  <si>
+    <t>↑</t>
+  </si>
+  <si>
+    <t>正位</t>
+  </si>
+  <si>
+    <t>能量順行｜主題自然流動、力量顯現、外顯無礙</t>
+  </si>
+  <si>
+    <t>＋</t>
+  </si>
+  <si>
+    <t>半正位</t>
+  </si>
+  <si>
+    <t>初生漸顯｜潛能正在凝聚、尚未完全流動，代表準備與激活</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>半逆位</t>
+  </si>
+  <si>
+    <t>釋放收束｜能量正在退潮、進入整合期，是轉化與療癒階段</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>逆位</t>
+  </si>
+  <si>
+    <t>能量阻滯｜主題反向顯現、力量扭曲、潛藏或危機感浮現</t>
+  </si>
+  <si>
+    <t>新月☉</t>
+  </si>
+  <si>
+    <t>正位（↑）</t>
+  </si>
+  <si>
+    <t>種子發芽</t>
+  </si>
+  <si>
+    <t>內在意圖與宇宙準備一致，適合啟動靜默中的創造</t>
+  </si>
+  <si>
+    <t>半正位（＋）</t>
+  </si>
+  <si>
+    <t>光尚未現</t>
+  </si>
+  <si>
+    <t>內在想動但時機未到，建議靜觀其變，等待契機</t>
+  </si>
+  <si>
+    <t>半逆位（—）</t>
+  </si>
+  <si>
+    <t>內潛釋放</t>
+  </si>
+  <si>
+    <t>正在釋放舊的創傷種子，是蛻變的準備期</t>
+  </si>
+  <si>
+    <t>逆位（↓）</t>
+  </si>
+  <si>
+    <t>種子阻塞</t>
+  </si>
+  <si>
+    <t>潛意識被壓抑，黑暗中難見光，需自我淨化與釋放</t>
+  </si>
+  <si>
+    <t>上弦△</t>
+  </si>
+  <si>
+    <t>行動之力</t>
+  </si>
+  <si>
+    <t>內外一致推進，適合主動出擊，逐步構建理想</t>
+  </si>
+  <si>
+    <t>焦躁之芽</t>
+  </si>
+  <si>
+    <t>內心躁動但實際力道尚不足，建議規劃而非急行</t>
+  </si>
+  <si>
+    <t>回收嘗試</t>
+  </si>
+  <si>
+    <t>曾嘗試某事未果，現在正在撤回與調整策略</t>
+  </si>
+  <si>
+    <t>阻斷行動</t>
+  </si>
+  <si>
+    <t>外力推動但你卻抗拒行動，可能因恐懼或拖延</t>
+  </si>
+  <si>
+    <t>滿月●</t>
+  </si>
+  <si>
+    <t>顯化高峰</t>
+  </si>
+  <si>
+    <t>內外完全共振，是展現、收穫與綻放的時刻</t>
+  </si>
+  <si>
+    <t>光中迷失</t>
+  </si>
+  <si>
+    <t>雖處高峰但焦點不明，可能能量過盛造成混亂</t>
+  </si>
+  <si>
+    <t>光後退場</t>
+  </si>
+  <si>
+    <t>繁盛之後開始退 潮，是總結與整合的契機</t>
+  </si>
+  <si>
+    <t>反射之光</t>
+  </si>
+  <si>
+    <t>事情表面光鮮但內裡不實，建議內觀真實感受</t>
+  </si>
+  <si>
+    <t>下弦▼</t>
+  </si>
+  <si>
+    <t>釋放清明</t>
+  </si>
+  <si>
+    <t>內在與宇宙都進入收束，適合整理與放下</t>
+  </si>
+  <si>
+    <t>整理未完</t>
+  </si>
+  <si>
+    <t>你開始整理但仍有執著，建議覺察仍卡住之處</t>
+  </si>
+  <si>
+    <t>釋放完成</t>
+  </si>
+  <si>
+    <t>你正好順勢放手，是準備迎接新週期的轉點</t>
+  </si>
+  <si>
+    <t>固執難釋</t>
+  </si>
+  <si>
+    <t>該放的未放，可能陷入重複舊模式的循環中</t>
+  </si>
+  <si>
+    <t>流暢合鳴</t>
+  </si>
+  <si>
+    <t>雙主題順行，宇宙與內在共振，是最強顯化組合之~</t>
+  </si>
+  <si>
+    <t>引導激活</t>
+  </si>
+  <si>
+    <t>你已行動，但另一主題尚待展現，是領導與帶動的結構</t>
+  </si>
+  <si>
+    <t>前行與整合</t>
+  </si>
+  <si>
+    <t>行動中帶有反思或療癒意味，是從創傷中推進的力量</t>
+  </si>
+  <si>
+    <t>前行與牽絆</t>
+  </si>
+  <si>
+    <t>你行進中卻被另一能量拉住，代表矛盾與修正功課</t>
+  </si>
+  <si>
+    <t>準備與照映</t>
+  </si>
+  <si>
+    <t>尚未動身的你，看見他人或外界已經啟動，是激勵與感應</t>
+  </si>
+  <si>
+    <t>潛能交疊</t>
+  </si>
+  <si>
+    <t>兩能量都在蓄勢待發，強烈暗示蘊含巨大突破可能</t>
+  </si>
+  <si>
+    <t>啟動回收交錯</t>
+  </si>
+  <si>
+    <t>有些還沒開始，有些已進入整合，是交叉能量場</t>
+  </si>
+  <si>
+    <t>內外緊張</t>
+  </si>
+  <si>
+    <t>準備階段受到阻力，需辨識內在恐懼或外在制約</t>
+  </si>
+  <si>
+    <t>內整外行</t>
+  </si>
+  <si>
+    <t>你已完成內在釋放，準備讓顯化能量帶動轉變</t>
+  </si>
+  <si>
+    <t>整合啟動序列</t>
+  </si>
+  <si>
+    <t>如同從療癒中走向重生，是自然節奏的過渡</t>
+  </si>
+  <si>
+    <t>雙向轉化</t>
+  </si>
+  <si>
+    <t>兩主題都在整合與釋放，為內在極佳的重建機會</t>
+  </si>
+  <si>
+    <t>殘餘影響</t>
+  </si>
+  <si>
+    <t>你已準備放手，但過往殘影仍在干擾，建議深層釋放</t>
+  </si>
+  <si>
+    <t>阻力轉化</t>
+  </si>
+  <si>
+    <t>你的陰影或課題正被顯化的能量反映出來，適合內觀</t>
+  </si>
+  <si>
+    <t>危機激化</t>
+  </si>
+  <si>
+    <t>混亂與潛能交錯，可能進入情緒／能量波動期</t>
+  </si>
+  <si>
+    <t>解構療癒</t>
+  </si>
+  <si>
+    <t>從混亂轉入療癒，代表自我解體與重組過程</t>
+  </si>
+  <si>
+    <t>雙重阻滯</t>
+  </si>
+  <si>
+    <t>兩個主題都處於逆流，建議停下腳步，進行深度清理</t>
+  </si>
+  <si>
+    <t>正</t>
+  </si>
+  <si>
+    <t>順行顯化</t>
+  </si>
+  <si>
+    <t>內外三位一致，強烈顯化循環，是展現與實現的命運契機</t>
+  </si>
+  <si>
+    <t>半正</t>
+  </si>
+  <si>
+    <t>穩定激活</t>
+  </si>
+  <si>
+    <t>行動穩定推進中，結果仍在醞釀與調整階段，提醒你保持耐心與信任。</t>
+  </si>
+  <si>
+    <t>半逆</t>
+  </si>
+  <si>
+    <t>尚未完成</t>
+  </si>
+  <si>
+    <t>內外一致但結尾偏弱，表示需要補強或延伸支持系統。</t>
+  </si>
+  <si>
+    <t>逆</t>
+  </si>
+  <si>
+    <t>明顯受阻</t>
+  </si>
+  <si>
+    <t>儘管起步順利，中後段力量突然斷裂，可能遭遇突發干擾或未察覺的內在抗拒。</t>
+  </si>
+  <si>
+    <t>領航共振</t>
+  </si>
+  <si>
+    <t>你已在穩定前行之路上，過程帶動他人或局勢逐步啟動，結果象徵良好回響與共振顯化。</t>
+  </si>
+  <si>
+    <t>漸進合流</t>
+  </si>
+  <si>
+    <t>穩定出發並正在推動變化，最終抵達一個尚未完全顯化但趨勢良好的節點，建議保持節奏。</t>
+  </si>
+  <si>
+    <t>外顯內縮</t>
+  </si>
+  <si>
+    <t>雖然整體能量持續展開，但結尾傾向收斂與整合，可能需要重新聚焦或調整方向。</t>
+  </si>
+  <si>
+    <t>外順內裂</t>
+  </si>
+  <si>
+    <t>起始順利並逐步啟動，但最終可能因忽略內在訊號或潛在隱憂而出現能量反轉。</t>
+  </si>
+  <si>
+    <t>前行整合</t>
+  </si>
+  <si>
+    <t>穩定出發後進入內在整合階段，最終重新對齊初衷，是帶有覺察與調整後的顯化。</t>
+  </si>
+  <si>
+    <t>穩中有伏</t>
+  </si>
+  <si>
+    <t>外在穩定推進，但過程內收、結果尚未完全打開，象徵能量正在重新聚焦，建議不急於顯現。</t>
+  </si>
+  <si>
+    <t>穩定退潮</t>
+  </si>
+  <si>
+    <t>起點穩固，但整體能量逐步收束，暗示你可能正在完成一段歷程或進入沉潛期。</t>
+  </si>
+  <si>
+    <t>外強內崩</t>
+  </si>
+  <si>
+    <t>雖然你以堅定姿態開始，但內在整合不穩，最終導致力量崩潰或情勢逆轉，需正視內在裂縫。</t>
+  </si>
+  <si>
+    <t>內斷外續</t>
+  </si>
+  <si>
+    <t>中段遭遇阻力但整體仍推進，提醒過程中需正視陰影課題。</t>
+  </si>
+  <si>
+    <t>穩中現憂</t>
+  </si>
+  <si>
+    <t>雖然最終看似可見轉機，但中途的反轉仍可能留下未處理的陰影或疑慮，需逐步釐清。</t>
+  </si>
+  <si>
+    <t>逆後整合</t>
+  </si>
+  <si>
+    <t>經歷中段挫折後進入能量收束，表示你開始試圖整理錯誤或修補破裂狀態。</t>
+  </si>
+  <si>
+    <t>反轉崩解</t>
+  </si>
+  <si>
+    <t>雖有良好起步，但命運之力遭遇劇烈反彈，情勢進一步惡化，需重新評估整體方向。</t>
+  </si>
+  <si>
+    <t>漸啟顯化</t>
+  </si>
+  <si>
+    <t>從醞釀走向實踐，最終達到完整顯化，是潛能被喚醒後的強力展現期。</t>
+  </si>
+  <si>
+    <t>引導未竟</t>
+  </si>
+  <si>
+    <t>雖有外力支持，但最終顯化尚不穩定，象徵你正被引領但還未全然開展。</t>
+  </si>
+  <si>
+    <t>力量反饋</t>
+  </si>
+  <si>
+    <t>實踐後產生回收效應，過程激烈但結尾進入反思與內在調整，需消化過多輸出。</t>
+  </si>
+  <si>
+    <t>承壓逆襲</t>
+  </si>
+  <si>
+    <t>外界壓力或主動行動過早啟動，導致結果無法承受能量負荷，最終產生逆轉或瓦解。</t>
+  </si>
+  <si>
+    <t>潛力爆發</t>
+  </si>
+  <si>
+    <t>雙重醞釀疊加後導致能量突破，是從靜默轉向顯現的關鍵躍進點。</t>
+  </si>
+  <si>
+    <t>穩定擴展</t>
+  </si>
+  <si>
+    <t>雖然進展不快，但穩定累積能量，整體狀態正在朝顯化前緩慢移動。</t>
+  </si>
+  <si>
+    <t>雙重內整</t>
+  </si>
+  <si>
+    <t>所有能量仍集中於內部醞釀與整合，顯示尚需時間消化轉變，不宜急行。</t>
+  </si>
+  <si>
+    <t>遲未轉化</t>
+  </si>
+  <si>
+    <t>醞釀過久而未能突破，能量卡滯導致反轉或錯失時機，需警惕停滯。</t>
+  </si>
+  <si>
+    <t>調和甦醒</t>
+  </si>
+  <si>
+    <t>初始潛能尚未展開，中段進入整合，最終由內而外重新對齊，是靜轉動的契機。</t>
+  </si>
+  <si>
+    <t>轉向萌動</t>
+  </si>
+  <si>
+    <t>你正在從內部調整過渡，能量逐步往外推展，象徵變化正在醞釀中。</t>
+  </si>
+  <si>
+    <t>靜能潛流</t>
+  </si>
+  <si>
+    <t>雙重內聚導致顯化遲緩，此時重點不在結果，而在內在建構與情緒沉澱。</t>
+  </si>
+  <si>
+    <t>未果回折</t>
+  </si>
+  <si>
+    <t>雖有起步之意，但能量過程無法外放，最終進入停滯或反向，提醒你重審動機與方法。</t>
+  </si>
+  <si>
+    <t>陰中返陽</t>
+  </si>
+  <si>
+    <t>儘管中段受阻，你仍可能轉化壓力為動力，結果迎來正面顯現，是逆勢中的突破之機。</t>
+  </si>
+  <si>
+    <t>調和未果</t>
+  </si>
+  <si>
+    <t>原本的行動被打斷，雖試圖重啟，但能量仍顯薄弱，結果顯示需更多支持與耐性。</t>
+  </si>
+  <si>
+    <t>崩後整理</t>
+  </si>
+  <si>
+    <t>結構中斷後進入內整期，此時不宜急行，而要關注殘餘能量與情緒的重新歸位。</t>
+  </si>
+  <si>
+    <t>錯失良機</t>
+  </si>
+  <si>
+    <t>醞釀之力未能及時展開，內外阻力接連出現，導致整體逆轉，提醒你勿忽略時機感。</t>
+  </si>
+  <si>
+    <t>內整外展</t>
+  </si>
+  <si>
+    <t>經歷內在整合後開始外顯推進，最終達成成果，是從療癒走向顯化的實踐循環。</t>
+  </si>
+  <si>
+    <t>穩定恢復</t>
+  </si>
+  <si>
+    <t>你已從整合期中重建力量，當下正處於逐步展現的過渡階段，能量趨穩但仍在累積。</t>
+  </si>
+  <si>
+    <t>收整停歇</t>
+  </si>
+  <si>
+    <t>行動後你選擇退後一步，讓自己沉澱與修復，代表一種主動的收束與守成。</t>
+  </si>
+  <si>
+    <t>明進暗退</t>
+  </si>
+  <si>
+    <t>雖曾推進但內在仍有未解之處，最終結果可能反轉，提示過程中忽略了潛藏的情緒或關鍵細節。</t>
+  </si>
+  <si>
+    <t>轉折開啟</t>
+  </si>
+  <si>
+    <t>從整理中緩步提昇，能量逐漸轉向顯現，是柔性的進展節奏。</t>
+  </si>
+  <si>
+    <t>緩步醞釀</t>
+  </si>
+  <si>
+    <t>雙方能量皆未完全展開，整體處於準備與醞釀交疊的狀態，需耐心等待時機成熟。</t>
+  </si>
+  <si>
+    <t>反覆沉整</t>
+  </si>
+  <si>
+    <t>正在進行多層整合，能量上下起伏，代表反覆調整與內在回應。</t>
+  </si>
+  <si>
+    <t>動念挫敗</t>
+  </si>
+  <si>
+    <t>雖有出發意願，但行動未全然落地，最終因干擾或動搖導致退卻與終止。</t>
+  </si>
+  <si>
+    <t>準備出擊</t>
+  </si>
+  <si>
+    <t>潛能尚未完全覺醒，過程穩定發酵，是蓄力期後即將啟動的關鍵轉點。</t>
+  </si>
+  <si>
+    <t>潛勢待發</t>
+  </si>
+  <si>
+    <t>能量仍聚於內部調和，雖有萌動之兆，仍需觀察並等待更明確的啟動信號。</t>
+  </si>
+  <si>
+    <t>內潛反芻</t>
+  </si>
+  <si>
+    <t>三重整合暗示深層轉化期，雖未見表面動靜，但內在運作劇烈，建議靜守蛻變。</t>
+  </si>
+  <si>
+    <t>能量斷裂</t>
+  </si>
+  <si>
+    <t>整合未竟便遭受打擊，代表潛勢尚未穩固就被外力或自我否定截斷，需謹慎。</t>
+  </si>
+  <si>
+    <t>錯線復明</t>
+  </si>
+  <si>
+    <t>雖經挫折與混亂，但仍可能在過程中覺醒新的方向，重返有序的顯化路徑。</t>
+  </si>
+  <si>
+    <t>漸返有序</t>
+  </si>
+  <si>
+    <t>從內部整合轉向混沌後，正在努力重組秩序，象徵你開始試圖恢復掌控權。</t>
+  </si>
+  <si>
+    <t>疲勞整合</t>
+  </si>
+  <si>
+    <t>消耗與混亂交錯之後進入內省與療癒，這是一段身心重整的過渡期。</t>
+  </si>
+  <si>
+    <t>崩解退場</t>
+  </si>
+  <si>
+    <t>雙重壓力導致崩潰結果，代表當前局勢已無法支撐，需要終止或徹底退出。</t>
+  </si>
+  <si>
+    <t>療癒轉化</t>
+  </si>
+  <si>
+    <t>開場困難但力量漸升，是從創傷中走向覺醒的重建模式。</t>
+  </si>
+  <si>
+    <t>轉穩待啟</t>
+  </si>
+  <si>
+    <t>雖然已突破逆境，但仍需穩定醞釀，象徵進入恢復後的積蓄期。</t>
+  </si>
+  <si>
+    <t>陰影整合</t>
+  </si>
+  <si>
+    <t>力量被重新召回後，你選擇內省與調整，代表逆境後的深層整合與修復。</t>
+  </si>
+  <si>
+    <t>復甦未果</t>
+  </si>
+  <si>
+    <t>即使中段有所突破，但整體仍未脫離阻力圈，結果顯示復甦尚未徹底成功。</t>
+  </si>
+  <si>
+    <t>援引突破</t>
+  </si>
+  <si>
+    <t>你正從低谷中回升，外部助力將協助你重建自信與行動，突破當前瓶頸。</t>
+  </si>
+  <si>
+    <t>修補進展</t>
+  </si>
+  <si>
+    <t>雖未徹底恢復，但正在接受支持與引導，能量慢慢流動，有機會逐步恢復動能。</t>
+  </si>
+  <si>
+    <t>半明半昧</t>
+  </si>
+  <si>
+    <t>你正處於陰影與希望交界，內心仍有波動，但整體趨勢向調整與收束前進。</t>
+  </si>
+  <si>
+    <t>激盪未解</t>
+  </si>
+  <si>
+    <t>嘗試修復但未見成效，內外矛盾依然存在，可能需要更長期的處理與覺察。</t>
+  </si>
+  <si>
+    <t>解構重生</t>
+  </si>
+  <si>
+    <t>雖從混亂中開始，但你選擇整合與釋放，最終將迎來更新的顯化，是重生的徵兆。</t>
+  </si>
+  <si>
+    <t>漸進修補</t>
+  </si>
+  <si>
+    <t>你正從崩裂狀態中恢復，雖未完全顯化，但新的希望正在醞釀。</t>
+  </si>
+  <si>
+    <t>殘餘清理</t>
+  </si>
+  <si>
+    <t>持續面對過去創傷與未解議題，是一段深度清掃與修復的時期。</t>
+  </si>
+  <si>
+    <t>影纏未散</t>
+  </si>
+  <si>
+    <t>雖努力整合但陰影仍未退散，顯示你尚未真正放下，循環可能重演。</t>
+  </si>
+  <si>
+    <t>阻中現光</t>
+  </si>
+  <si>
+    <t>即使歷經多重阻力，你仍可能由內而外產生突破，是暗處覓光之路。</t>
+  </si>
+  <si>
+    <t>破舊立新</t>
+  </si>
+  <si>
+    <t>雙重逆境促成覺醒的動力，代表你正在重新建立新的行動路線與心態。</t>
+  </si>
+  <si>
+    <t>清算回潮</t>
+  </si>
+  <si>
+    <t>累積的卡滯正在退潮，你逐漸回到整合狀態，是深層療癒期的後段。</t>
+  </si>
+  <si>
+    <t>兩個主題都處於逆流，建議停下腳步，進行深度清理與自我審視。</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="34" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -6550,8 +8124,55 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="3"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="26">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -6645,8 +8266,58 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79995117038483843"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59996337778862885"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="78">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -7665,8 +9336,87 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="11">
+  <cellStyleXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
@@ -7692,8 +9442,29 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="304">
+  <cellXfs count="372">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -8254,12 +10025,165 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="14" xfId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="39" xfId="11" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="11" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="11" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="14" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="39" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="39" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="16" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="0" xfId="12" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="20" borderId="39" xfId="12" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="14" xfId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="39" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="22" borderId="16" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" xfId="13" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="39" xfId="13" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="13" xfId="13" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="11" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="78" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="21" borderId="11" xfId="13" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="2" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="6" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="12" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="3" xfId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="36" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="36" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="42" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="44" xfId="14" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="40" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="45" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="2" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="2" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="37" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="41" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="3" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="36" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="36" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="42" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="42" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="4" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="38" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="38" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="43" xfId="15" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="14" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="6" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="80" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="36" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="42" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="40" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="40" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="45" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="81" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="2" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="37" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="41" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="38" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="38" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="43" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="82" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="83" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="52" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="84" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="11">
+  <cellStyles count="18">
     <cellStyle name="20% - 輔色1" xfId="7"/>
     <cellStyle name="20% - 輔色2" xfId="9"/>
+    <cellStyle name="20% - 輔色3 2" xfId="12"/>
+    <cellStyle name="20% - 輔色4 2" xfId="13"/>
+    <cellStyle name="20% - 輔色5 2" xfId="14"/>
     <cellStyle name="40% - 輔色1" xfId="8"/>
     <cellStyle name="40% - 輔色2" xfId="10"/>
+    <cellStyle name="40% - 輔色5 2" xfId="15"/>
+    <cellStyle name="60% - 輔色5 2" xfId="16"/>
     <cellStyle name="Excel Built-in Normal" xfId="1"/>
     <cellStyle name="一般" xfId="0" builtinId="0"/>
     <cellStyle name="一般 2" xfId="2"/>
@@ -8267,6 +10191,8 @@
     <cellStyle name="中等" xfId="5"/>
     <cellStyle name="好" xfId="4"/>
     <cellStyle name="備註" xfId="6"/>
+    <cellStyle name="輔色5 2" xfId="17"/>
+    <cellStyle name="標題 5" xfId="11"/>
   </cellStyles>
   <dxfs count="55">
     <dxf>
@@ -9777,6 +11703,19 @@
 </table>
 </file>
 
+<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="InteractionsTable" displayName="InteractionsTable" ref="A1:E185" totalsRowShown="0">
+  <tableColumns count="5">
+    <tableColumn id="3" name="A"/>
+    <tableColumn id="4" name="B"/>
+    <tableColumn id="5" name="C"/>
+    <tableColumn id="6" name="關係/模式"/>
+    <tableColumn id="7" name="解釋/訊息"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 佈景主題">
   <a:themeElements>
@@ -10031,10 +11970,10 @@
         <v>6</v>
       </c>
       <c r="H1" s="118" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="I1" s="287" t="s">
-        <v>1629</v>
+        <v>1627</v>
       </c>
       <c r="J1" s="287" t="s">
         <v>1342</v>
@@ -10063,7 +12002,7 @@
         <v>11</v>
       </c>
       <c r="H2" s="278" t="s">
-        <v>1568</v>
+        <v>1566</v>
       </c>
       <c r="I2" s="268" t="s">
         <v>1280</v>
@@ -10095,7 +12034,7 @@
         <v>16</v>
       </c>
       <c r="H3" s="277" t="s">
-        <v>1569</v>
+        <v>1567</v>
       </c>
       <c r="I3" s="87" t="s">
         <v>1281</v>
@@ -10127,7 +12066,7 @@
         <v>11</v>
       </c>
       <c r="H4" s="277" t="s">
-        <v>1630</v>
+        <v>1628</v>
       </c>
       <c r="I4" s="270" t="s">
         <v>1282</v>
@@ -10159,7 +12098,7 @@
         <v>16</v>
       </c>
       <c r="H5" s="277" t="s">
-        <v>1570</v>
+        <v>1568</v>
       </c>
       <c r="I5" s="87" t="s">
         <v>1283</v>
@@ -10191,7 +12130,7 @@
         <v>16</v>
       </c>
       <c r="H6" s="277" t="s">
-        <v>1567</v>
+        <v>1565</v>
       </c>
       <c r="I6" s="270" t="s">
         <v>1284</v>
@@ -10223,7 +12162,7 @@
         <v>16</v>
       </c>
       <c r="H7" s="277" t="s">
-        <v>1571</v>
+        <v>1569</v>
       </c>
       <c r="I7" s="87" t="s">
         <v>1285</v>
@@ -10255,7 +12194,7 @@
         <v>11</v>
       </c>
       <c r="H8" s="277" t="s">
-        <v>1572</v>
+        <v>1570</v>
       </c>
       <c r="I8" s="270" t="s">
         <v>1286</v>
@@ -10287,7 +12226,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="279" t="s">
-        <v>1573</v>
+        <v>1571</v>
       </c>
       <c r="I9" s="88" t="s">
         <v>1287</v>
@@ -10319,7 +12258,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="282" t="s">
-        <v>1578</v>
+        <v>1576</v>
       </c>
       <c r="I10" s="283" t="s">
         <v>1288</v>
@@ -10351,7 +12290,7 @@
         <v>36</v>
       </c>
       <c r="H11" s="277" t="s">
-        <v>1576</v>
+        <v>1574</v>
       </c>
       <c r="I11" s="87" t="s">
         <v>37</v>
@@ -10383,7 +12322,7 @@
         <v>36</v>
       </c>
       <c r="H12" s="277" t="s">
-        <v>1577</v>
+        <v>1575</v>
       </c>
       <c r="I12" s="270" t="s">
         <v>1289</v>
@@ -10415,7 +12354,7 @@
         <v>16</v>
       </c>
       <c r="H13" s="277" t="s">
-        <v>1575</v>
+        <v>1573</v>
       </c>
       <c r="I13" s="87" t="s">
         <v>1290</v>
@@ -10447,7 +12386,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="277" t="s">
-        <v>1580</v>
+        <v>1578</v>
       </c>
       <c r="I14" s="270" t="s">
         <v>1291</v>
@@ -10479,7 +12418,7 @@
         <v>36</v>
       </c>
       <c r="H15" s="277" t="s">
-        <v>1574</v>
+        <v>1572</v>
       </c>
       <c r="I15" s="87" t="s">
         <v>1292</v>
@@ -10511,7 +12450,7 @@
         <v>16</v>
       </c>
       <c r="H16" s="277" t="s">
-        <v>1581</v>
+        <v>1579</v>
       </c>
       <c r="I16" s="270" t="s">
         <v>1293</v>
@@ -10543,7 +12482,7 @@
         <v>36</v>
       </c>
       <c r="H17" s="279" t="s">
-        <v>1579</v>
+        <v>1577</v>
       </c>
       <c r="I17" s="88" t="s">
         <v>1294</v>
@@ -10575,7 +12514,7 @@
         <v>11</v>
       </c>
       <c r="H18" s="282" t="s">
-        <v>1582</v>
+        <v>1580</v>
       </c>
       <c r="I18" s="283" t="s">
         <v>1295</v>
@@ -10607,7 +12546,7 @@
         <v>11</v>
       </c>
       <c r="H19" s="277" t="s">
-        <v>1583</v>
+        <v>1581</v>
       </c>
       <c r="I19" s="87" t="s">
         <v>1296</v>
@@ -10639,7 +12578,7 @@
         <v>36</v>
       </c>
       <c r="H20" s="277" t="s">
-        <v>1589</v>
+        <v>1587</v>
       </c>
       <c r="I20" s="270" t="s">
         <v>1297</v>
@@ -10671,7 +12610,7 @@
         <v>36</v>
       </c>
       <c r="H21" s="277" t="s">
-        <v>1584</v>
+        <v>1582</v>
       </c>
       <c r="I21" s="87" t="s">
         <v>1298</v>
@@ -10703,7 +12642,7 @@
         <v>11</v>
       </c>
       <c r="H22" s="277" t="s">
-        <v>1585</v>
+        <v>1583</v>
       </c>
       <c r="I22" s="270" t="s">
         <v>1299</v>
@@ -10735,7 +12674,7 @@
         <v>11</v>
       </c>
       <c r="H23" s="277" t="s">
-        <v>1586</v>
+        <v>1584</v>
       </c>
       <c r="I23" s="87" t="s">
         <v>1300</v>
@@ -10767,7 +12706,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="277" t="s">
-        <v>1587</v>
+        <v>1585</v>
       </c>
       <c r="I24" s="270" t="s">
         <v>1301</v>
@@ -10799,7 +12738,7 @@
         <v>11</v>
       </c>
       <c r="H25" s="286" t="s">
-        <v>1588</v>
+        <v>1586</v>
       </c>
       <c r="I25" s="89" t="s">
         <v>1302</v>
@@ -10831,7 +12770,7 @@
         <v>11</v>
       </c>
       <c r="H26" s="278" t="s">
-        <v>1590</v>
+        <v>1588</v>
       </c>
       <c r="I26" s="268" t="s">
         <v>1303</v>
@@ -10863,7 +12802,7 @@
         <v>11</v>
       </c>
       <c r="H27" s="277" t="s">
-        <v>1592</v>
+        <v>1590</v>
       </c>
       <c r="I27" s="87" t="s">
         <v>1304</v>
@@ -10895,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="H28" s="277" t="s">
-        <v>1591</v>
+        <v>1589</v>
       </c>
       <c r="I28" s="270" t="s">
         <v>1305</v>
@@ -10927,7 +12866,7 @@
         <v>16</v>
       </c>
       <c r="H29" s="277" t="s">
-        <v>1593</v>
+        <v>1591</v>
       </c>
       <c r="I29" s="87" t="s">
         <v>1306</v>
@@ -10959,7 +12898,7 @@
         <v>11</v>
       </c>
       <c r="H30" s="277" t="s">
-        <v>1594</v>
+        <v>1592</v>
       </c>
       <c r="I30" s="270" t="s">
         <v>1307</v>
@@ -10991,7 +12930,7 @@
         <v>16</v>
       </c>
       <c r="H31" s="277" t="s">
-        <v>1595</v>
+        <v>1593</v>
       </c>
       <c r="I31" s="87" t="s">
         <v>1308</v>
@@ -11023,7 +12962,7 @@
         <v>16</v>
       </c>
       <c r="H32" s="277" t="s">
-        <v>1597</v>
+        <v>1595</v>
       </c>
       <c r="I32" s="270" t="s">
         <v>1309</v>
@@ -11055,7 +12994,7 @@
         <v>16</v>
       </c>
       <c r="H33" s="286" t="s">
-        <v>1596</v>
+        <v>1594</v>
       </c>
       <c r="I33" s="89" t="s">
         <v>1310</v>
@@ -11087,7 +13026,7 @@
         <v>16</v>
       </c>
       <c r="H34" s="278" t="s">
-        <v>1598</v>
+        <v>1596</v>
       </c>
       <c r="I34" s="268" t="s">
         <v>1311</v>
@@ -11119,7 +13058,7 @@
         <v>11</v>
       </c>
       <c r="H35" s="277" t="s">
-        <v>1599</v>
+        <v>1597</v>
       </c>
       <c r="I35" s="87" t="s">
         <v>1312</v>
@@ -11151,7 +13090,7 @@
         <v>11</v>
       </c>
       <c r="H36" s="277" t="s">
-        <v>1600</v>
+        <v>1598</v>
       </c>
       <c r="I36" s="270" t="s">
         <v>1313</v>
@@ -11183,7 +13122,7 @@
         <v>11</v>
       </c>
       <c r="H37" s="277" t="s">
-        <v>1601</v>
+        <v>1599</v>
       </c>
       <c r="I37" s="87" t="s">
         <v>1314</v>
@@ -11215,7 +13154,7 @@
         <v>11</v>
       </c>
       <c r="H38" s="277" t="s">
-        <v>1602</v>
+        <v>1600</v>
       </c>
       <c r="I38" s="270" t="s">
         <v>1315</v>
@@ -11247,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="H39" s="277" t="s">
-        <v>1603</v>
+        <v>1601</v>
       </c>
       <c r="I39" s="87" t="s">
         <v>1316</v>
@@ -11279,7 +13218,7 @@
         <v>16</v>
       </c>
       <c r="H40" s="277" t="s">
-        <v>1604</v>
+        <v>1602</v>
       </c>
       <c r="I40" s="270" t="s">
         <v>1317</v>
@@ -11311,7 +13250,7 @@
         <v>36</v>
       </c>
       <c r="H41" s="279" t="s">
-        <v>1605</v>
+        <v>1603</v>
       </c>
       <c r="I41" s="88" t="s">
         <v>1318</v>
@@ -11343,7 +13282,7 @@
         <v>11</v>
       </c>
       <c r="H42" s="282" t="s">
-        <v>1609</v>
+        <v>1607</v>
       </c>
       <c r="I42" s="283" t="s">
         <v>106</v>
@@ -11375,7 +13314,7 @@
         <v>36</v>
       </c>
       <c r="H43" s="277" t="s">
-        <v>1608</v>
+        <v>1606</v>
       </c>
       <c r="I43" s="87" t="s">
         <v>1319</v>
@@ -11407,7 +13346,7 @@
         <v>16</v>
       </c>
       <c r="H44" s="277" t="s">
-        <v>1612</v>
+        <v>1610</v>
       </c>
       <c r="I44" s="270" t="s">
         <v>1320</v>
@@ -11439,7 +13378,7 @@
         <v>16</v>
       </c>
       <c r="H45" s="277" t="s">
-        <v>1610</v>
+        <v>1608</v>
       </c>
       <c r="I45" s="87" t="s">
         <v>1321</v>
@@ -11471,7 +13410,7 @@
         <v>16</v>
       </c>
       <c r="H46" s="277" t="s">
-        <v>1606</v>
+        <v>1604</v>
       </c>
       <c r="I46" s="270" t="s">
         <v>1322</v>
@@ -11503,7 +13442,7 @@
         <v>16</v>
       </c>
       <c r="H47" s="277" t="s">
-        <v>1613</v>
+        <v>1611</v>
       </c>
       <c r="I47" s="87" t="s">
         <v>1323</v>
@@ -11535,7 +13474,7 @@
         <v>16</v>
       </c>
       <c r="H48" s="277" t="s">
-        <v>1611</v>
+        <v>1609</v>
       </c>
       <c r="I48" s="270" t="s">
         <v>1324</v>
@@ -11567,7 +13506,7 @@
         <v>16</v>
       </c>
       <c r="H49" s="279" t="s">
-        <v>1607</v>
+        <v>1605</v>
       </c>
       <c r="I49" s="88" t="s">
         <v>1325</v>
@@ -11599,7 +13538,7 @@
         <v>36</v>
       </c>
       <c r="H50" s="282" t="s">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="I50" s="283" t="s">
         <v>1326</v>
@@ -11631,7 +13570,7 @@
         <v>36</v>
       </c>
       <c r="H51" s="277" t="s">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="I51" s="87" t="s">
         <v>1327</v>
@@ -11663,10 +13602,10 @@
         <v>16</v>
       </c>
       <c r="H52" s="277" t="s">
-        <v>1723</v>
+        <v>1721</v>
       </c>
       <c r="I52" s="270" t="s">
-        <v>1763</v>
+        <v>1761</v>
       </c>
       <c r="J52" s="271" t="s">
         <v>1393</v>
@@ -11695,7 +13634,7 @@
         <v>16</v>
       </c>
       <c r="H53" s="277" t="s">
-        <v>1614</v>
+        <v>1612</v>
       </c>
       <c r="I53" s="87" t="s">
         <v>1328</v>
@@ -11727,7 +13666,7 @@
         <v>11</v>
       </c>
       <c r="H54" s="277" t="s">
-        <v>1742</v>
+        <v>1740</v>
       </c>
       <c r="I54" s="270" t="s">
         <v>1329</v>
@@ -11759,7 +13698,7 @@
         <v>16</v>
       </c>
       <c r="H55" s="277" t="s">
-        <v>1616</v>
+        <v>1614</v>
       </c>
       <c r="I55" s="87" t="s">
         <v>1330</v>
@@ -11791,7 +13730,7 @@
         <v>16</v>
       </c>
       <c r="H56" s="277" t="s">
-        <v>1617</v>
+        <v>1615</v>
       </c>
       <c r="I56" s="270" t="s">
         <v>1331</v>
@@ -11823,7 +13762,7 @@
         <v>16</v>
       </c>
       <c r="H57" s="279" t="s">
-        <v>1615</v>
+        <v>1613</v>
       </c>
       <c r="I57" s="88" t="s">
         <v>1332</v>
@@ -11855,7 +13794,7 @@
         <v>11</v>
       </c>
       <c r="H58" s="282" t="s">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="I58" s="283" t="s">
         <v>1333</v>
@@ -11887,7 +13826,7 @@
         <v>36</v>
       </c>
       <c r="H59" s="277" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="I59" s="87" t="s">
         <v>1334</v>
@@ -11919,7 +13858,7 @@
         <v>153</v>
       </c>
       <c r="H60" s="277" t="s">
-        <v>1733</v>
+        <v>1731</v>
       </c>
       <c r="I60" s="270" t="s">
         <v>1335</v>
@@ -11951,7 +13890,7 @@
         <v>11</v>
       </c>
       <c r="H61" s="277" t="s">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="I61" s="87" t="s">
         <v>1336</v>
@@ -11983,7 +13922,7 @@
         <v>36</v>
       </c>
       <c r="H62" s="277" t="s">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="I62" s="270" t="s">
         <v>1337</v>
@@ -12015,7 +13954,7 @@
         <v>16</v>
       </c>
       <c r="H63" s="277" t="s">
-        <v>1618</v>
+        <v>1616</v>
       </c>
       <c r="I63" s="87" t="s">
         <v>1338</v>
@@ -12047,7 +13986,7 @@
         <v>36</v>
       </c>
       <c r="H64" s="277" t="s">
-        <v>1619</v>
+        <v>1617</v>
       </c>
       <c r="I64" s="270" t="s">
         <v>1339</v>
@@ -12079,7 +14018,7 @@
         <v>16</v>
       </c>
       <c r="H65" s="279" t="s">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="I65" s="88" t="s">
         <v>1340</v>
@@ -12111,10 +14050,10 @@
         <v>153</v>
       </c>
       <c r="H66" s="282" t="s">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="I66" s="283" t="s">
-        <v>1627</v>
+        <v>1625</v>
       </c>
       <c r="J66" s="284" t="s">
         <v>1407</v>
@@ -12143,10 +14082,10 @@
         <v>153</v>
       </c>
       <c r="H67" s="277" t="s">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="I67" s="87" t="s">
-        <v>1628</v>
+        <v>1626</v>
       </c>
       <c r="J67" s="99" t="s">
         <v>1408</v>
@@ -12163,7 +14102,7 @@
         <v>1502</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>1624</v>
+        <v>1622</v>
       </c>
       <c r="E68" s="88" t="s">
         <v>167</v>
@@ -12175,13 +14114,13 @@
         <v>153</v>
       </c>
       <c r="H68" s="279" t="s">
-        <v>1620</v>
+        <v>1618</v>
       </c>
       <c r="I68" s="272" t="s">
         <v>1341</v>
       </c>
       <c r="J68" s="273" t="s">
-        <v>1621</v>
+        <v>1619</v>
       </c>
     </row>
   </sheetData>
@@ -12190,6 +14129,2609 @@
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14" style="338" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="338" customWidth="1"/>
+    <col min="3" max="3" width="66" style="338" customWidth="1"/>
+    <col min="4" max="4" width="62.75" style="338" customWidth="1"/>
+    <col min="5" max="14" width="9" style="326"/>
+    <col min="15" max="16384" width="9" style="338"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="307" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="304" t="s">
+        <v>1850</v>
+      </c>
+      <c r="B1" s="305" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C1" s="305" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D1" s="305" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E1" s="306"/>
+      <c r="F1" s="306"/>
+      <c r="G1" s="306"/>
+      <c r="H1" s="306"/>
+      <c r="I1" s="306"/>
+      <c r="J1" s="306"/>
+      <c r="K1" s="306"/>
+      <c r="L1" s="306"/>
+      <c r="M1" s="306"/>
+      <c r="N1" s="306"/>
+    </row>
+    <row r="2" spans="1:14" s="313" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="308" t="s">
+        <v>1854</v>
+      </c>
+      <c r="B2" s="309" t="s">
+        <v>1855</v>
+      </c>
+      <c r="C2" s="310" t="s">
+        <v>1856</v>
+      </c>
+      <c r="D2" s="311" t="s">
+        <v>1857</v>
+      </c>
+      <c r="E2" s="312"/>
+      <c r="F2" s="312"/>
+      <c r="G2" s="312"/>
+      <c r="H2" s="312"/>
+      <c r="I2" s="312"/>
+      <c r="J2" s="312"/>
+      <c r="K2" s="312"/>
+      <c r="L2" s="312"/>
+      <c r="M2" s="312"/>
+      <c r="N2" s="312"/>
+    </row>
+    <row r="3" spans="1:14" s="318" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="314" t="s">
+        <v>1858</v>
+      </c>
+      <c r="B3" s="315" t="s">
+        <v>1859</v>
+      </c>
+      <c r="C3" s="315" t="s">
+        <v>1860</v>
+      </c>
+      <c r="D3" s="316" t="s">
+        <v>1861</v>
+      </c>
+      <c r="E3" s="317"/>
+      <c r="F3" s="317"/>
+      <c r="G3" s="317"/>
+      <c r="H3" s="317"/>
+      <c r="I3" s="317"/>
+      <c r="J3" s="317"/>
+      <c r="K3" s="317"/>
+      <c r="L3" s="317"/>
+      <c r="M3" s="317"/>
+      <c r="N3" s="317"/>
+    </row>
+    <row r="4" spans="1:14" s="322" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="319" t="s">
+        <v>1862</v>
+      </c>
+      <c r="B4" s="320" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C4" s="320" t="s">
+        <v>1864</v>
+      </c>
+      <c r="D4" s="321" t="s">
+        <v>1865</v>
+      </c>
+      <c r="E4" s="317"/>
+      <c r="F4" s="317"/>
+      <c r="G4" s="317"/>
+      <c r="H4" s="317"/>
+      <c r="I4" s="317"/>
+      <c r="J4" s="317"/>
+      <c r="K4" s="317"/>
+      <c r="L4" s="317"/>
+      <c r="M4" s="317"/>
+      <c r="N4" s="317"/>
+    </row>
+    <row r="5" spans="1:14" s="326" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="323" t="s">
+        <v>1866</v>
+      </c>
+      <c r="B5" s="324" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C5" s="324" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D5" s="325" t="s">
+        <v>1868</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="326" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="327"/>
+      <c r="B6" s="328" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C6" s="329" t="s">
+        <v>1870</v>
+      </c>
+      <c r="D6" s="330" t="s">
+        <v>1871</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="326" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="327"/>
+      <c r="B7" s="328" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C7" s="329" t="s">
+        <v>1873</v>
+      </c>
+      <c r="D7" s="330" t="s">
+        <v>1874</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="334" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="331"/>
+      <c r="B8" s="332" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C8" s="332" t="s">
+        <v>1876</v>
+      </c>
+      <c r="D8" s="333" t="s">
+        <v>1877</v>
+      </c>
+      <c r="E8" s="326"/>
+      <c r="F8" s="326"/>
+      <c r="G8" s="326"/>
+      <c r="H8" s="326"/>
+      <c r="I8" s="326"/>
+      <c r="J8" s="326"/>
+      <c r="K8" s="326"/>
+      <c r="L8" s="326"/>
+      <c r="M8" s="326"/>
+      <c r="N8" s="326"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="335" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B9" s="336" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C9" s="336" t="s">
+        <v>1879</v>
+      </c>
+      <c r="D9" s="337" t="s">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="339"/>
+      <c r="B10" s="340" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C10" s="341" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D10" s="342" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="339"/>
+      <c r="B11" s="340" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C11" s="341" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D11" s="342" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="339"/>
+      <c r="B12" s="340" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C12" s="341" t="s">
+        <v>1888</v>
+      </c>
+      <c r="D12" s="342" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="339"/>
+      <c r="B13" s="340" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C13" s="341" t="s">
+        <v>1891</v>
+      </c>
+      <c r="D13" s="343" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="339"/>
+      <c r="B14" s="340" t="s">
+        <v>1893</v>
+      </c>
+      <c r="C14" s="341" t="s">
+        <v>1894</v>
+      </c>
+      <c r="D14" s="343" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="344"/>
+      <c r="B15" s="345" t="s">
+        <v>1896</v>
+      </c>
+      <c r="C15" s="346" t="s">
+        <v>1897</v>
+      </c>
+      <c r="D15" s="347" t="s">
+        <v>1898</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="348" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B16" s="349" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C16" s="349" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D16" s="350" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="351"/>
+      <c r="B17" s="352" t="s">
+        <v>1902</v>
+      </c>
+      <c r="C17" s="352" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D17" s="353" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="351"/>
+      <c r="B18" s="352" t="s">
+        <v>1905</v>
+      </c>
+      <c r="C18" s="352" t="s">
+        <v>1906</v>
+      </c>
+      <c r="D18" s="353" t="s">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="351"/>
+      <c r="B19" s="354" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C19" s="355" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D19" s="356" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="357"/>
+      <c r="B20" s="354" t="s">
+        <v>1911</v>
+      </c>
+      <c r="C20" s="355" t="s">
+        <v>1912</v>
+      </c>
+      <c r="D20" s="356" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="358" t="s">
+        <v>1914</v>
+      </c>
+      <c r="B21" s="359" t="s">
+        <v>1863</v>
+      </c>
+      <c r="C21" s="359" t="s">
+        <v>1915</v>
+      </c>
+      <c r="D21" s="360" t="s">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="361" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B22" s="362" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C22" s="363" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D22" s="364" t="s">
+        <v>1920</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A5:A8"/>
+    <mergeCell ref="A9:A15"/>
+    <mergeCell ref="A16:A20"/>
+  </mergeCells>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E185"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.375" style="338" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="338" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="338" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="338" customWidth="1"/>
+    <col min="5" max="5" width="96.875" style="338" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="338"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="365" t="s">
+        <v>1921</v>
+      </c>
+      <c r="B1" s="365" t="s">
+        <v>1922</v>
+      </c>
+      <c r="C1" s="365" t="s">
+        <v>1923</v>
+      </c>
+      <c r="D1" s="365" t="s">
+        <v>1924</v>
+      </c>
+      <c r="E1" s="365" t="s">
+        <v>1925</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="366" t="s">
+        <v>1926</v>
+      </c>
+      <c r="B2" s="367"/>
+      <c r="C2" s="367"/>
+      <c r="D2" s="367" t="s">
+        <v>1927</v>
+      </c>
+      <c r="E2" s="367" t="s">
+        <v>1928</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="368" t="s">
+        <v>1929</v>
+      </c>
+      <c r="B3" s="369"/>
+      <c r="C3" s="369"/>
+      <c r="D3" s="369" t="s">
+        <v>1930</v>
+      </c>
+      <c r="E3" s="369" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="368" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B4" s="369"/>
+      <c r="C4" s="369"/>
+      <c r="D4" s="369" t="s">
+        <v>1933</v>
+      </c>
+      <c r="E4" s="369" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="370" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B5" s="371"/>
+      <c r="C5" s="371"/>
+      <c r="D5" s="371" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E5" s="371" t="s">
+        <v>1937</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="366" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B6" s="367" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C6" s="367"/>
+      <c r="D6" s="367" t="s">
+        <v>1940</v>
+      </c>
+      <c r="E6" s="367" t="s">
+        <v>1941</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="368" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B7" s="369" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C7" s="369"/>
+      <c r="D7" s="369" t="s">
+        <v>1943</v>
+      </c>
+      <c r="E7" s="369" t="s">
+        <v>1944</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="368" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B8" s="369" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C8" s="369"/>
+      <c r="D8" s="369" t="s">
+        <v>1946</v>
+      </c>
+      <c r="E8" s="369" t="s">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="370" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B9" s="371" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C9" s="371"/>
+      <c r="D9" s="371" t="s">
+        <v>1949</v>
+      </c>
+      <c r="E9" s="371" t="s">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="366" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B10" s="367" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C10" s="367"/>
+      <c r="D10" s="367" t="s">
+        <v>1952</v>
+      </c>
+      <c r="E10" s="367" t="s">
+        <v>1953</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="368" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B11" s="369" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C11" s="369"/>
+      <c r="D11" s="369" t="s">
+        <v>1954</v>
+      </c>
+      <c r="E11" s="369" t="s">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="368" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B12" s="369" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C12" s="369"/>
+      <c r="D12" s="369" t="s">
+        <v>1956</v>
+      </c>
+      <c r="E12" s="369" t="s">
+        <v>1957</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="370" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B13" s="371" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C13" s="371"/>
+      <c r="D13" s="371" t="s">
+        <v>1958</v>
+      </c>
+      <c r="E13" s="371" t="s">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="366" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B14" s="367" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C14" s="367"/>
+      <c r="D14" s="367" t="s">
+        <v>1961</v>
+      </c>
+      <c r="E14" s="367" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="368" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B15" s="369" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C15" s="369"/>
+      <c r="D15" s="369" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E15" s="369" t="s">
+        <v>1964</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="368" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B16" s="369" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C16" s="369"/>
+      <c r="D16" s="369" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E16" s="369" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="370" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B17" s="371" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C17" s="371"/>
+      <c r="D17" s="371" t="s">
+        <v>1967</v>
+      </c>
+      <c r="E17" s="371" t="s">
+        <v>1968</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="366" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B18" s="367" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C18" s="367"/>
+      <c r="D18" s="367" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E18" s="367" t="s">
+        <v>1971</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="368" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B19" s="369" t="s">
+        <v>1942</v>
+      </c>
+      <c r="C19" s="369"/>
+      <c r="D19" s="369" t="s">
+        <v>1972</v>
+      </c>
+      <c r="E19" s="369" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="368" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B20" s="369" t="s">
+        <v>1945</v>
+      </c>
+      <c r="C20" s="369"/>
+      <c r="D20" s="369" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E20" s="369" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="370" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B21" s="371" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C21" s="371"/>
+      <c r="D21" s="371" t="s">
+        <v>1976</v>
+      </c>
+      <c r="E21" s="371" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="366" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B22" s="367" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C22" s="367"/>
+      <c r="D22" s="367" t="s">
+        <v>1978</v>
+      </c>
+      <c r="E22" s="367" t="s">
+        <v>1979</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="368" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B23" s="369" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C23" s="369"/>
+      <c r="D23" s="369" t="s">
+        <v>1980</v>
+      </c>
+      <c r="E23" s="369" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="368" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B24" s="369" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C24" s="369"/>
+      <c r="D24" s="369" t="s">
+        <v>1982</v>
+      </c>
+      <c r="E24" s="369" t="s">
+        <v>1983</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="370" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B25" s="371" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C25" s="371"/>
+      <c r="D25" s="371" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E25" s="371" t="s">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="366" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B26" s="367" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C26" s="367"/>
+      <c r="D26" s="367" t="s">
+        <v>1986</v>
+      </c>
+      <c r="E26" s="367" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="368" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B27" s="369" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C27" s="369"/>
+      <c r="D27" s="369" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E27" s="369" t="s">
+        <v>1989</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="368" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B28" s="369" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C28" s="369"/>
+      <c r="D28" s="369" t="s">
+        <v>1990</v>
+      </c>
+      <c r="E28" s="369" t="s">
+        <v>1991</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="370" t="s">
+        <v>1930</v>
+      </c>
+      <c r="B29" s="371" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C29" s="371"/>
+      <c r="D29" s="371" t="s">
+        <v>1992</v>
+      </c>
+      <c r="E29" s="371" t="s">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="366" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B30" s="367" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C30" s="367"/>
+      <c r="D30" s="367" t="s">
+        <v>1994</v>
+      </c>
+      <c r="E30" s="367" t="s">
+        <v>1995</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="368" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B31" s="369" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C31" s="369"/>
+      <c r="D31" s="369" t="s">
+        <v>1996</v>
+      </c>
+      <c r="E31" s="369" t="s">
+        <v>1997</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="368" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B32" s="369" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C32" s="369"/>
+      <c r="D32" s="369" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E32" s="369" t="s">
+        <v>1999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="370" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B33" s="371" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C33" s="371"/>
+      <c r="D33" s="371" t="s">
+        <v>2000</v>
+      </c>
+      <c r="E33" s="371" t="s">
+        <v>2001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="366" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B34" s="367" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C34" s="367"/>
+      <c r="D34" s="367" t="s">
+        <v>2002</v>
+      </c>
+      <c r="E34" s="367" t="s">
+        <v>2003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="368" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B35" s="369" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C35" s="369"/>
+      <c r="D35" s="369" t="s">
+        <v>2004</v>
+      </c>
+      <c r="E35" s="369" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="368" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B36" s="369" t="s">
+        <v>1933</v>
+      </c>
+      <c r="C36" s="369"/>
+      <c r="D36" s="369" t="s">
+        <v>2006</v>
+      </c>
+      <c r="E36" s="369" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="370" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B37" s="371" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C37" s="371"/>
+      <c r="D37" s="371" t="s">
+        <v>2008</v>
+      </c>
+      <c r="E37" s="371" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="366" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B38" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C38" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D38" s="367" t="s">
+        <v>2011</v>
+      </c>
+      <c r="E38" s="367" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B39" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C39" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D39" s="369" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E39" s="369" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B40" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C40" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D40" s="369" t="s">
+        <v>2017</v>
+      </c>
+      <c r="E40" s="369" t="s">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B41" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C41" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D41" s="369" t="s">
+        <v>2020</v>
+      </c>
+      <c r="E41" s="369" t="s">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B42" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C42" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D42" s="369" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E42" s="369" t="s">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B43" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C43" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D43" s="369" t="s">
+        <v>2024</v>
+      </c>
+      <c r="E43" s="369" t="s">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B44" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C44" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D44" s="369" t="s">
+        <v>2026</v>
+      </c>
+      <c r="E44" s="369" t="s">
+        <v>2027</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B45" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C45" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D45" s="369" t="s">
+        <v>2028</v>
+      </c>
+      <c r="E45" s="369" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B46" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C46" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D46" s="369" t="s">
+        <v>2030</v>
+      </c>
+      <c r="E46" s="369" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B47" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C47" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D47" s="369" t="s">
+        <v>2032</v>
+      </c>
+      <c r="E47" s="369" t="s">
+        <v>2033</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B48" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C48" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D48" s="369" t="s">
+        <v>2034</v>
+      </c>
+      <c r="E48" s="369" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B49" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C49" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D49" s="369" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E49" s="369" t="s">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B50" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C50" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D50" s="369" t="s">
+        <v>2038</v>
+      </c>
+      <c r="E50" s="369" t="s">
+        <v>2039</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B51" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C51" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D51" s="369" t="s">
+        <v>2040</v>
+      </c>
+      <c r="E51" s="369" t="s">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="368" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B52" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C52" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D52" s="369" t="s">
+        <v>2042</v>
+      </c>
+      <c r="E52" s="369" t="s">
+        <v>2043</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="370" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B53" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C53" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D53" s="371" t="s">
+        <v>2044</v>
+      </c>
+      <c r="E53" s="371" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="366" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B54" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C54" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D54" s="367" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E54" s="367" t="s">
+        <v>2047</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B55" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C55" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D55" s="369" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E55" s="369" t="s">
+        <v>2049</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B56" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C56" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D56" s="369" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E56" s="369" t="s">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B57" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C57" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D57" s="369" t="s">
+        <v>2052</v>
+      </c>
+      <c r="E57" s="369" t="s">
+        <v>2053</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B58" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C58" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D58" s="369" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E58" s="369" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B59" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C59" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D59" s="369" t="s">
+        <v>2056</v>
+      </c>
+      <c r="E59" s="369" t="s">
+        <v>2057</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B60" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C60" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D60" s="369" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E60" s="369" t="s">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B61" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C61" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D61" s="369" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E61" s="369" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B62" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C62" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D62" s="369" t="s">
+        <v>2062</v>
+      </c>
+      <c r="E62" s="369" t="s">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B63" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C63" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D63" s="369" t="s">
+        <v>2064</v>
+      </c>
+      <c r="E63" s="369" t="s">
+        <v>2065</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B64" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C64" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D64" s="369" t="s">
+        <v>2066</v>
+      </c>
+      <c r="E64" s="369" t="s">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B65" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C65" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D65" s="369" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E65" s="369" t="s">
+        <v>2069</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B66" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C66" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D66" s="369" t="s">
+        <v>2070</v>
+      </c>
+      <c r="E66" s="369" t="s">
+        <v>2071</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B67" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C67" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D67" s="369" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E67" s="369" t="s">
+        <v>2073</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="368" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B68" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C68" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D68" s="369" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E68" s="369" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="370" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B69" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C69" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D69" s="371" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E69" s="371" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="366" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B70" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C70" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D70" s="367" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E70" s="367" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C71" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D71" s="369" t="s">
+        <v>2080</v>
+      </c>
+      <c r="E71" s="369" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B72" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C72" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D72" s="369" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E72" s="369" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B73" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C73" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D73" s="369" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E73" s="369" t="s">
+        <v>2085</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B74" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C74" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D74" s="369" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E74" s="369" t="s">
+        <v>2087</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B75" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C75" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D75" s="369" t="s">
+        <v>2088</v>
+      </c>
+      <c r="E75" s="369" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B76" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C76" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D76" s="369" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E76" s="369" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B77" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C77" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D77" s="369" t="s">
+        <v>2092</v>
+      </c>
+      <c r="E77" s="369" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B78" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C78" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D78" s="369" t="s">
+        <v>2094</v>
+      </c>
+      <c r="E78" s="369" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B79" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C79" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D79" s="369" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E79" s="369" t="s">
+        <v>2097</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B80" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C80" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D80" s="369" t="s">
+        <v>2098</v>
+      </c>
+      <c r="E80" s="369" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B81" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C81" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D81" s="369" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E81" s="369" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B82" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C82" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D82" s="369" t="s">
+        <v>2102</v>
+      </c>
+      <c r="E82" s="369" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B83" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C83" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D83" s="369" t="s">
+        <v>2104</v>
+      </c>
+      <c r="E83" s="369" t="s">
+        <v>2105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="368" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B84" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C84" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D84" s="369" t="s">
+        <v>2106</v>
+      </c>
+      <c r="E84" s="369" t="s">
+        <v>2107</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="370" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B85" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C85" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D85" s="371" t="s">
+        <v>2108</v>
+      </c>
+      <c r="E85" s="371" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="366" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B86" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C86" s="367" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D86" s="367" t="s">
+        <v>2110</v>
+      </c>
+      <c r="E86" s="367" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B87" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C87" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D87" s="369" t="s">
+        <v>2112</v>
+      </c>
+      <c r="E87" s="369" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B88" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C88" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D88" s="369" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E88" s="369" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B89" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C89" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D89" s="369" t="s">
+        <v>2116</v>
+      </c>
+      <c r="E89" s="369" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B90" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C90" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D90" s="369" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E90" s="369" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B91" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C91" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D91" s="369" t="s">
+        <v>2120</v>
+      </c>
+      <c r="E91" s="369" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B92" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C92" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D92" s="369" t="s">
+        <v>2122</v>
+      </c>
+      <c r="E92" s="369" t="s">
+        <v>2123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B93" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C93" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D93" s="369" t="s">
+        <v>2124</v>
+      </c>
+      <c r="E93" s="369" t="s">
+        <v>2125</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B94" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C94" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D94" s="369" t="s">
+        <v>2126</v>
+      </c>
+      <c r="E94" s="369" t="s">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B95" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C95" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D95" s="369" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E95" s="369" t="s">
+        <v>2129</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B96" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C96" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D96" s="369" t="s">
+        <v>2130</v>
+      </c>
+      <c r="E96" s="369" t="s">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B97" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C97" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D97" s="369" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E97" s="369" t="s">
+        <v>2133</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B98" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C98" s="369" t="s">
+        <v>2010</v>
+      </c>
+      <c r="D98" s="369" t="s">
+        <v>2134</v>
+      </c>
+      <c r="E98" s="369" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B99" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C99" s="369" t="s">
+        <v>2013</v>
+      </c>
+      <c r="D99" s="369" t="s">
+        <v>2136</v>
+      </c>
+      <c r="E99" s="369" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="368" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B100" s="369" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C100" s="369" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D100" s="369" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E100" s="369" t="s">
+        <v>2139</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="370" t="s">
+        <v>2019</v>
+      </c>
+      <c r="B101" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="C101" s="371" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D101" s="371" t="s">
+        <v>2008</v>
+      </c>
+      <c r="E101" s="371" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102" s="369"/>
+      <c r="B102" s="369"/>
+      <c r="C102" s="369"/>
+      <c r="D102" s="369"/>
+      <c r="E102" s="369"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103" s="369"/>
+      <c r="B103" s="369"/>
+      <c r="C103" s="369"/>
+      <c r="D103" s="369"/>
+      <c r="E103" s="369"/>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104" s="369"/>
+      <c r="B104" s="369"/>
+      <c r="C104" s="369"/>
+      <c r="D104" s="369"/>
+      <c r="E104" s="369"/>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105" s="369"/>
+      <c r="B105" s="369"/>
+      <c r="C105" s="369"/>
+      <c r="D105" s="369"/>
+      <c r="E105" s="369"/>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106" s="369"/>
+      <c r="B106" s="369"/>
+      <c r="C106" s="369"/>
+      <c r="D106" s="369"/>
+      <c r="E106" s="369"/>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107" s="369"/>
+      <c r="B107" s="369"/>
+      <c r="C107" s="369"/>
+      <c r="D107" s="369"/>
+      <c r="E107" s="369"/>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108" s="369"/>
+      <c r="B108" s="369"/>
+      <c r="C108" s="369"/>
+      <c r="D108" s="369"/>
+      <c r="E108" s="369"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109" s="369"/>
+      <c r="B109" s="369"/>
+      <c r="C109" s="369"/>
+      <c r="D109" s="369"/>
+      <c r="E109" s="369"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110" s="369"/>
+      <c r="B110" s="369"/>
+      <c r="C110" s="369"/>
+      <c r="D110" s="369"/>
+      <c r="E110" s="369"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111" s="369"/>
+      <c r="B111" s="369"/>
+      <c r="C111" s="369"/>
+      <c r="D111" s="369"/>
+      <c r="E111" s="369"/>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112" s="369"/>
+      <c r="B112" s="369"/>
+      <c r="C112" s="369"/>
+      <c r="D112" s="369"/>
+      <c r="E112" s="369"/>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113" s="369"/>
+      <c r="B113" s="369"/>
+      <c r="C113" s="369"/>
+      <c r="D113" s="369"/>
+      <c r="E113" s="369"/>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114" s="369"/>
+      <c r="B114" s="369"/>
+      <c r="C114" s="369"/>
+      <c r="D114" s="369"/>
+      <c r="E114" s="369"/>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115" s="369"/>
+      <c r="B115" s="369"/>
+      <c r="C115" s="369"/>
+      <c r="D115" s="369"/>
+      <c r="E115" s="369"/>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116" s="369"/>
+      <c r="B116" s="369"/>
+      <c r="C116" s="369"/>
+      <c r="D116" s="369"/>
+      <c r="E116" s="369"/>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117" s="369"/>
+      <c r="B117" s="369"/>
+      <c r="C117" s="369"/>
+      <c r="D117" s="369"/>
+      <c r="E117" s="369"/>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118" s="369"/>
+      <c r="B118" s="369"/>
+      <c r="C118" s="369"/>
+      <c r="D118" s="369"/>
+      <c r="E118" s="369"/>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119" s="369"/>
+      <c r="B119" s="369"/>
+      <c r="C119" s="369"/>
+      <c r="D119" s="369"/>
+      <c r="E119" s="369"/>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120" s="369"/>
+      <c r="B120" s="369"/>
+      <c r="C120" s="369"/>
+      <c r="D120" s="369"/>
+      <c r="E120" s="369"/>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121" s="369"/>
+      <c r="B121" s="369"/>
+      <c r="C121" s="369"/>
+      <c r="D121" s="369"/>
+      <c r="E121" s="369"/>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122" s="369"/>
+      <c r="B122" s="369"/>
+      <c r="C122" s="369"/>
+      <c r="D122" s="369"/>
+      <c r="E122" s="369"/>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123" s="369"/>
+      <c r="B123" s="369"/>
+      <c r="C123" s="369"/>
+      <c r="D123" s="369"/>
+      <c r="E123" s="369"/>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="369"/>
+      <c r="B124" s="369"/>
+      <c r="C124" s="369"/>
+      <c r="D124" s="369"/>
+      <c r="E124" s="369"/>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125" s="369"/>
+      <c r="B125" s="369"/>
+      <c r="C125" s="369"/>
+      <c r="D125" s="369"/>
+      <c r="E125" s="369"/>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126" s="369"/>
+      <c r="B126" s="369"/>
+      <c r="C126" s="369"/>
+      <c r="D126" s="369"/>
+      <c r="E126" s="369"/>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127" s="369"/>
+      <c r="B127" s="369"/>
+      <c r="C127" s="369"/>
+      <c r="D127" s="369"/>
+      <c r="E127" s="369"/>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128" s="369"/>
+      <c r="B128" s="369"/>
+      <c r="C128" s="369"/>
+      <c r="D128" s="369"/>
+      <c r="E128" s="369"/>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129" s="369"/>
+      <c r="B129" s="369"/>
+      <c r="C129" s="369"/>
+      <c r="D129" s="369"/>
+      <c r="E129" s="369"/>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130" s="369"/>
+      <c r="B130" s="369"/>
+      <c r="C130" s="369"/>
+      <c r="D130" s="369"/>
+      <c r="E130" s="369"/>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131" s="369"/>
+      <c r="B131" s="369"/>
+      <c r="C131" s="369"/>
+      <c r="D131" s="369"/>
+      <c r="E131" s="369"/>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132" s="369"/>
+      <c r="B132" s="369"/>
+      <c r="C132" s="369"/>
+      <c r="D132" s="369"/>
+      <c r="E132" s="369"/>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133" s="369"/>
+      <c r="B133" s="369"/>
+      <c r="C133" s="369"/>
+      <c r="D133" s="369"/>
+      <c r="E133" s="369"/>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134" s="369"/>
+      <c r="B134" s="369"/>
+      <c r="C134" s="369"/>
+      <c r="D134" s="369"/>
+      <c r="E134" s="369"/>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135" s="369"/>
+      <c r="B135" s="369"/>
+      <c r="C135" s="369"/>
+      <c r="D135" s="369"/>
+      <c r="E135" s="369"/>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136" s="369"/>
+      <c r="B136" s="369"/>
+      <c r="C136" s="369"/>
+      <c r="D136" s="369"/>
+      <c r="E136" s="369"/>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137" s="369"/>
+      <c r="B137" s="369"/>
+      <c r="C137" s="369"/>
+      <c r="D137" s="369"/>
+      <c r="E137" s="369"/>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138" s="369"/>
+      <c r="B138" s="369"/>
+      <c r="C138" s="369"/>
+      <c r="D138" s="369"/>
+      <c r="E138" s="369"/>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139" s="369"/>
+      <c r="B139" s="369"/>
+      <c r="C139" s="369"/>
+      <c r="D139" s="369"/>
+      <c r="E139" s="369"/>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140" s="369"/>
+      <c r="B140" s="369"/>
+      <c r="C140" s="369"/>
+      <c r="D140" s="369"/>
+      <c r="E140" s="369"/>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141" s="369"/>
+      <c r="B141" s="369"/>
+      <c r="C141" s="369"/>
+      <c r="D141" s="369"/>
+      <c r="E141" s="369"/>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142" s="369"/>
+      <c r="B142" s="369"/>
+      <c r="C142" s="369"/>
+      <c r="D142" s="369"/>
+      <c r="E142" s="369"/>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143" s="369"/>
+      <c r="B143" s="369"/>
+      <c r="C143" s="369"/>
+      <c r="D143" s="369"/>
+      <c r="E143" s="369"/>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144" s="369"/>
+      <c r="B144" s="369"/>
+      <c r="C144" s="369"/>
+      <c r="D144" s="369"/>
+      <c r="E144" s="369"/>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145" s="369"/>
+      <c r="B145" s="369"/>
+      <c r="C145" s="369"/>
+      <c r="D145" s="369"/>
+      <c r="E145" s="369"/>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146" s="369"/>
+      <c r="B146" s="369"/>
+      <c r="C146" s="369"/>
+      <c r="D146" s="369"/>
+      <c r="E146" s="369"/>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147" s="369"/>
+      <c r="B147" s="369"/>
+      <c r="C147" s="369"/>
+      <c r="D147" s="369"/>
+      <c r="E147" s="369"/>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148" s="369"/>
+      <c r="B148" s="369"/>
+      <c r="C148" s="369"/>
+      <c r="D148" s="369"/>
+      <c r="E148" s="369"/>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149" s="369"/>
+      <c r="B149" s="369"/>
+      <c r="C149" s="369"/>
+      <c r="D149" s="369"/>
+      <c r="E149" s="369"/>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150" s="369"/>
+      <c r="B150" s="369"/>
+      <c r="C150" s="369"/>
+      <c r="D150" s="369"/>
+      <c r="E150" s="369"/>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151" s="369"/>
+      <c r="B151" s="369"/>
+      <c r="C151" s="369"/>
+      <c r="D151" s="369"/>
+      <c r="E151" s="369"/>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152" s="369"/>
+      <c r="B152" s="369"/>
+      <c r="C152" s="369"/>
+      <c r="D152" s="369"/>
+      <c r="E152" s="369"/>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153" s="369"/>
+      <c r="B153" s="369"/>
+      <c r="C153" s="369"/>
+      <c r="D153" s="369"/>
+      <c r="E153" s="369"/>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154" s="369"/>
+      <c r="B154" s="369"/>
+      <c r="C154" s="369"/>
+      <c r="D154" s="369"/>
+      <c r="E154" s="369"/>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155" s="369"/>
+      <c r="B155" s="369"/>
+      <c r="C155" s="369"/>
+      <c r="D155" s="369"/>
+      <c r="E155" s="369"/>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156" s="369"/>
+      <c r="B156" s="369"/>
+      <c r="C156" s="369"/>
+      <c r="D156" s="369"/>
+      <c r="E156" s="369"/>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157" s="369"/>
+      <c r="B157" s="369"/>
+      <c r="C157" s="369"/>
+      <c r="D157" s="369"/>
+      <c r="E157" s="369"/>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158" s="369"/>
+      <c r="B158" s="369"/>
+      <c r="C158" s="369"/>
+      <c r="D158" s="369"/>
+      <c r="E158" s="369"/>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159" s="369"/>
+      <c r="B159" s="369"/>
+      <c r="C159" s="369"/>
+      <c r="D159" s="369"/>
+      <c r="E159" s="369"/>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160" s="369"/>
+      <c r="B160" s="369"/>
+      <c r="C160" s="369"/>
+      <c r="D160" s="369"/>
+      <c r="E160" s="369"/>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161" s="369"/>
+      <c r="B161" s="369"/>
+      <c r="C161" s="369"/>
+      <c r="D161" s="369"/>
+      <c r="E161" s="369"/>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162" s="369"/>
+      <c r="B162" s="369"/>
+      <c r="C162" s="369"/>
+      <c r="D162" s="369"/>
+      <c r="E162" s="369"/>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163" s="369"/>
+      <c r="B163" s="369"/>
+      <c r="C163" s="369"/>
+      <c r="D163" s="369"/>
+      <c r="E163" s="369"/>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164" s="369"/>
+      <c r="B164" s="369"/>
+      <c r="C164" s="369"/>
+      <c r="D164" s="369"/>
+      <c r="E164" s="369"/>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165" s="369"/>
+      <c r="B165" s="369"/>
+      <c r="C165" s="369"/>
+      <c r="D165" s="369"/>
+      <c r="E165" s="369"/>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166" s="369"/>
+      <c r="B166" s="369"/>
+      <c r="C166" s="369"/>
+      <c r="D166" s="369"/>
+      <c r="E166" s="369"/>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167" s="369"/>
+      <c r="B167" s="369"/>
+      <c r="C167" s="369"/>
+      <c r="D167" s="369"/>
+      <c r="E167" s="369"/>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168" s="369"/>
+      <c r="B168" s="369"/>
+      <c r="C168" s="369"/>
+      <c r="D168" s="369"/>
+      <c r="E168" s="369"/>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169" s="369"/>
+      <c r="B169" s="369"/>
+      <c r="C169" s="369"/>
+      <c r="D169" s="369"/>
+      <c r="E169" s="369"/>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170" s="369"/>
+      <c r="B170" s="369"/>
+      <c r="C170" s="369"/>
+      <c r="D170" s="369"/>
+      <c r="E170" s="369"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171" s="369"/>
+      <c r="B171" s="369"/>
+      <c r="C171" s="369"/>
+      <c r="D171" s="369"/>
+      <c r="E171" s="369"/>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172" s="369"/>
+      <c r="B172" s="369"/>
+      <c r="C172" s="369"/>
+      <c r="D172" s="369"/>
+      <c r="E172" s="369"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173" s="369"/>
+      <c r="B173" s="369"/>
+      <c r="C173" s="369"/>
+      <c r="D173" s="369"/>
+      <c r="E173" s="369"/>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174" s="369"/>
+      <c r="B174" s="369"/>
+      <c r="C174" s="369"/>
+      <c r="D174" s="369"/>
+      <c r="E174" s="369"/>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175" s="369"/>
+      <c r="B175" s="369"/>
+      <c r="C175" s="369"/>
+      <c r="D175" s="369"/>
+      <c r="E175" s="369"/>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176" s="369"/>
+      <c r="B176" s="369"/>
+      <c r="C176" s="369"/>
+      <c r="D176" s="369"/>
+      <c r="E176" s="369"/>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177" s="369"/>
+      <c r="B177" s="369"/>
+      <c r="C177" s="369"/>
+      <c r="D177" s="369"/>
+      <c r="E177" s="369"/>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178" s="369"/>
+      <c r="B178" s="369"/>
+      <c r="C178" s="369"/>
+      <c r="D178" s="369"/>
+      <c r="E178" s="369"/>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179" s="369"/>
+      <c r="B179" s="369"/>
+      <c r="C179" s="369"/>
+      <c r="D179" s="369"/>
+      <c r="E179" s="369"/>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180" s="369"/>
+      <c r="B180" s="369"/>
+      <c r="C180" s="369"/>
+      <c r="D180" s="369"/>
+      <c r="E180" s="369"/>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181" s="369"/>
+      <c r="B181" s="369"/>
+      <c r="C181" s="369"/>
+      <c r="D181" s="369"/>
+      <c r="E181" s="369"/>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182" s="369"/>
+      <c r="B182" s="369"/>
+      <c r="C182" s="369"/>
+      <c r="D182" s="369"/>
+      <c r="E182" s="369"/>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183" s="369"/>
+      <c r="B183" s="369"/>
+      <c r="C183" s="369"/>
+      <c r="D183" s="369"/>
+      <c r="E183" s="369"/>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184" s="369"/>
+      <c r="B184" s="369"/>
+      <c r="C184" s="369"/>
+      <c r="D184" s="369"/>
+      <c r="E184" s="369"/>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185" s="369"/>
+      <c r="B185" s="369"/>
+      <c r="C185" s="369"/>
+      <c r="D185" s="369"/>
+      <c r="E185" s="369"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="19" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
@@ -12216,16 +16758,16 @@
         <v>1</v>
       </c>
       <c r="C1" s="109" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="D1" s="274" t="s">
-        <v>1631</v>
+        <v>1629</v>
       </c>
       <c r="E1" s="274" t="s">
-        <v>1632</v>
+        <v>1630</v>
       </c>
       <c r="F1" s="274" t="s">
-        <v>1703</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="2" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12236,10 +16778,10 @@
         <v>7</v>
       </c>
       <c r="C2" s="86" t="s">
-        <v>1655</v>
+        <v>1653</v>
       </c>
       <c r="D2" s="268" t="s">
-        <v>1656</v>
+        <v>1654</v>
       </c>
       <c r="E2" s="268"/>
       <c r="F2" s="268"/>
@@ -12252,13 +16794,13 @@
         <v>12</v>
       </c>
       <c r="C3" s="87" t="s">
-        <v>1633</v>
+        <v>1631</v>
       </c>
       <c r="D3" s="87" t="s">
-        <v>1661</v>
+        <v>1659</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1839</v>
+        <v>1837</v>
       </c>
       <c r="F3" s="87"/>
     </row>
@@ -12270,10 +16812,10 @@
         <v>17</v>
       </c>
       <c r="C4" s="87" t="s">
-        <v>1657</v>
+        <v>1655</v>
       </c>
       <c r="D4" s="270" t="s">
-        <v>1658</v>
+        <v>1656</v>
       </c>
       <c r="E4" s="270"/>
       <c r="F4" s="270"/>
@@ -12286,13 +16828,13 @@
         <v>19</v>
       </c>
       <c r="C5" s="87" t="s">
-        <v>1634</v>
+        <v>1632</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>1840</v>
+        <v>1838</v>
       </c>
       <c r="E5" s="87" t="s">
-        <v>1659</v>
+        <v>1657</v>
       </c>
       <c r="F5" s="87"/>
     </row>
@@ -12304,10 +16846,10 @@
         <v>21</v>
       </c>
       <c r="C6" s="87" t="s">
-        <v>1635</v>
+        <v>1633</v>
       </c>
       <c r="D6" s="270" t="s">
-        <v>1636</v>
+        <v>1634</v>
       </c>
       <c r="E6" s="270"/>
       <c r="F6" s="270"/>
@@ -12320,10 +16862,10 @@
         <v>24</v>
       </c>
       <c r="C7" s="87" t="s">
-        <v>1637</v>
+        <v>1635</v>
       </c>
       <c r="D7" s="87" t="s">
-        <v>1662</v>
+        <v>1660</v>
       </c>
       <c r="E7" s="87"/>
       <c r="F7" s="87"/>
@@ -12336,13 +16878,13 @@
         <v>27</v>
       </c>
       <c r="C8" s="87" t="s">
-        <v>1717</v>
+        <v>1715</v>
       </c>
       <c r="D8" s="270" t="s">
-        <v>1638</v>
+        <v>1636</v>
       </c>
       <c r="E8" s="270" t="s">
-        <v>1816</v>
+        <v>1814</v>
       </c>
       <c r="F8" s="270"/>
     </row>
@@ -12354,10 +16896,10 @@
         <v>29</v>
       </c>
       <c r="C9" s="88" t="s">
-        <v>1660</v>
+        <v>1658</v>
       </c>
       <c r="D9" s="88" t="s">
-        <v>1639</v>
+        <v>1637</v>
       </c>
       <c r="E9" s="88"/>
       <c r="F9" s="88"/>
@@ -12370,10 +16912,10 @@
         <v>31</v>
       </c>
       <c r="C10" s="86" t="s">
-        <v>1640</v>
+        <v>1638</v>
       </c>
       <c r="D10" s="268" t="s">
-        <v>1641</v>
+        <v>1639</v>
       </c>
       <c r="E10" s="268"/>
       <c r="F10" s="268"/>
@@ -12386,13 +16928,13 @@
         <v>34</v>
       </c>
       <c r="C11" s="87" t="s">
-        <v>1642</v>
+        <v>1640</v>
       </c>
       <c r="D11" s="87" t="s">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1821</v>
+        <v>1819</v>
       </c>
       <c r="F11" s="87"/>
     </row>
@@ -12404,13 +16946,13 @@
         <v>38</v>
       </c>
       <c r="C12" s="87" t="s">
-        <v>1643</v>
+        <v>1641</v>
       </c>
       <c r="D12" s="270" t="s">
-        <v>1644</v>
+        <v>1642</v>
       </c>
       <c r="E12" s="270" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="F12" s="270"/>
     </row>
@@ -12422,16 +16964,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1849</v>
+        <v>1847</v>
       </c>
       <c r="D13" s="87" t="s">
-        <v>1645</v>
+        <v>1643</v>
       </c>
       <c r="E13" s="87" t="s">
-        <v>1653</v>
+        <v>1651</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>1841</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12442,13 +16984,13 @@
         <v>42</v>
       </c>
       <c r="C14" s="87" t="s">
-        <v>1646</v>
+        <v>1644</v>
       </c>
       <c r="D14" s="270" t="s">
         <v>1278</v>
       </c>
       <c r="E14" s="270" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="F14" s="270"/>
     </row>
@@ -12460,10 +17002,10 @@
         <v>44</v>
       </c>
       <c r="C15" s="87" t="s">
-        <v>1654</v>
+        <v>1652</v>
       </c>
       <c r="D15" s="87" t="s">
-        <v>1648</v>
+        <v>1646</v>
       </c>
       <c r="E15" s="87"/>
       <c r="F15" s="87"/>
@@ -12476,13 +17018,13 @@
         <v>46</v>
       </c>
       <c r="C16" s="87" t="s">
-        <v>1649</v>
+        <v>1647</v>
       </c>
       <c r="D16" s="270" t="s">
-        <v>1650</v>
+        <v>1648</v>
       </c>
       <c r="E16" s="270" t="s">
-        <v>1647</v>
+        <v>1645</v>
       </c>
       <c r="F16" s="270"/>
     </row>
@@ -12494,10 +17036,10 @@
         <v>48</v>
       </c>
       <c r="C17" s="88" t="s">
-        <v>1663</v>
+        <v>1661</v>
       </c>
       <c r="D17" s="88" t="s">
-        <v>1651</v>
+        <v>1649</v>
       </c>
       <c r="E17" s="88"/>
       <c r="F17" s="88"/>
@@ -12510,13 +17052,13 @@
         <v>50</v>
       </c>
       <c r="C18" s="86" t="s">
-        <v>1664</v>
+        <v>1662</v>
       </c>
       <c r="D18" s="268" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="E18" s="268" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="F18" s="268"/>
     </row>
@@ -12528,10 +17070,10 @@
         <v>54</v>
       </c>
       <c r="C19" s="87" t="s">
-        <v>1672</v>
+        <v>1670</v>
       </c>
       <c r="D19" s="87" t="s">
-        <v>1673</v>
+        <v>1671</v>
       </c>
       <c r="E19" s="87"/>
       <c r="F19" s="87"/>
@@ -12544,13 +17086,13 @@
         <v>56</v>
       </c>
       <c r="C20" s="87" t="s">
-        <v>1666</v>
+        <v>1664</v>
       </c>
       <c r="D20" s="270" t="s">
-        <v>1812</v>
+        <v>1810</v>
       </c>
       <c r="E20" s="270" t="s">
-        <v>1823</v>
+        <v>1821</v>
       </c>
       <c r="F20" s="270"/>
     </row>
@@ -12562,13 +17104,13 @@
         <v>58</v>
       </c>
       <c r="C21" s="87" t="s">
-        <v>1674</v>
+        <v>1672</v>
       </c>
       <c r="D21" s="87" t="s">
-        <v>1667</v>
+        <v>1665</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1819</v>
+        <v>1817</v>
       </c>
       <c r="F21" s="87"/>
     </row>
@@ -12580,13 +17122,13 @@
         <v>60</v>
       </c>
       <c r="C22" s="87" t="s">
-        <v>1668</v>
+        <v>1666</v>
       </c>
       <c r="D22" s="270" t="s">
-        <v>1669</v>
+        <v>1667</v>
       </c>
       <c r="E22" s="270" t="s">
-        <v>1820</v>
+        <v>1818</v>
       </c>
       <c r="F22" s="270"/>
     </row>
@@ -12598,10 +17140,10 @@
         <v>62</v>
       </c>
       <c r="C23" s="87" t="s">
-        <v>1670</v>
+        <v>1668</v>
       </c>
       <c r="D23" s="87" t="s">
-        <v>1671</v>
+        <v>1669</v>
       </c>
       <c r="E23" s="87"/>
       <c r="F23" s="87"/>
@@ -12614,13 +17156,13 @@
         <v>64</v>
       </c>
       <c r="C24" s="87" t="s">
-        <v>1676</v>
+        <v>1674</v>
       </c>
       <c r="D24" s="270" t="s">
-        <v>1677</v>
+        <v>1675</v>
       </c>
       <c r="E24" s="270" t="s">
-        <v>1825</v>
+        <v>1823</v>
       </c>
       <c r="F24" s="270"/>
     </row>
@@ -12632,13 +17174,13 @@
         <v>66</v>
       </c>
       <c r="C25" s="88" t="s">
-        <v>1682</v>
+        <v>1680</v>
       </c>
       <c r="D25" s="88" t="s">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="F25" s="88"/>
     </row>
@@ -12650,10 +17192,10 @@
         <v>68</v>
       </c>
       <c r="C26" s="86" t="s">
-        <v>1678</v>
+        <v>1676</v>
       </c>
       <c r="D26" s="268" t="s">
-        <v>1687</v>
+        <v>1685</v>
       </c>
       <c r="E26" s="268"/>
       <c r="F26" s="268"/>
@@ -12666,16 +17208,16 @@
         <v>71</v>
       </c>
       <c r="C27" s="87" t="s">
-        <v>1679</v>
+        <v>1677</v>
       </c>
       <c r="D27" s="87" t="s">
-        <v>1680</v>
+        <v>1678</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="F27" s="87" t="s">
-        <v>1729</v>
+        <v>1727</v>
       </c>
     </row>
     <row r="28" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -12686,10 +17228,10 @@
         <v>73</v>
       </c>
       <c r="C28" s="87" t="s">
-        <v>1681</v>
+        <v>1679</v>
       </c>
       <c r="D28" s="270" t="s">
-        <v>1688</v>
+        <v>1686</v>
       </c>
       <c r="E28" s="270"/>
       <c r="F28" s="270"/>
@@ -12708,7 +17250,7 @@
         <v>1279</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="F29" s="87"/>
     </row>
@@ -12720,10 +17262,10 @@
         <v>77</v>
       </c>
       <c r="C30" s="87" t="s">
-        <v>1683</v>
+        <v>1681</v>
       </c>
       <c r="D30" s="270" t="s">
-        <v>1684</v>
+        <v>1682</v>
       </c>
       <c r="E30" s="270"/>
       <c r="F30" s="270"/>
@@ -12736,7 +17278,7 @@
         <v>79</v>
       </c>
       <c r="C31" s="87" t="s">
-        <v>1689</v>
+        <v>1687</v>
       </c>
       <c r="D31" s="87"/>
       <c r="E31" s="87"/>
@@ -12750,10 +17292,10 @@
         <v>81</v>
       </c>
       <c r="C32" s="87" t="s">
-        <v>1685</v>
+        <v>1683</v>
       </c>
       <c r="D32" s="270" t="s">
-        <v>1686</v>
+        <v>1684</v>
       </c>
       <c r="E32" s="270"/>
       <c r="F32" s="270"/>
@@ -12766,11 +17308,11 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="D33" s="88"/>
       <c r="E33" s="88" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="F33" s="88"/>
     </row>
@@ -12782,10 +17324,10 @@
         <v>85</v>
       </c>
       <c r="C34" s="86" t="s">
-        <v>1690</v>
+        <v>1688</v>
       </c>
       <c r="D34" s="268" t="s">
-        <v>1691</v>
+        <v>1689</v>
       </c>
       <c r="E34" s="268"/>
       <c r="F34" s="268"/>
@@ -12798,10 +17340,10 @@
         <v>88</v>
       </c>
       <c r="C35" s="87" t="s">
-        <v>1692</v>
+        <v>1690</v>
       </c>
       <c r="D35" s="87" t="s">
-        <v>1693</v>
+        <v>1691</v>
       </c>
       <c r="E35" s="87"/>
       <c r="F35" s="87"/>
@@ -12814,10 +17356,10 @@
         <v>90</v>
       </c>
       <c r="C36" s="87" t="s">
-        <v>1694</v>
+        <v>1692</v>
       </c>
       <c r="D36" s="270" t="s">
-        <v>1695</v>
+        <v>1693</v>
       </c>
       <c r="E36" s="270"/>
       <c r="F36" s="270"/>
@@ -12830,13 +17372,13 @@
         <v>92</v>
       </c>
       <c r="C37" s="87" t="s">
-        <v>1696</v>
+        <v>1694</v>
       </c>
       <c r="D37" s="87" t="s">
-        <v>1697</v>
+        <v>1695</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1831</v>
+        <v>1829</v>
       </c>
       <c r="F37" s="87"/>
     </row>
@@ -12848,13 +17390,13 @@
         <v>94</v>
       </c>
       <c r="C38" s="87" t="s">
-        <v>1698</v>
+        <v>1696</v>
       </c>
       <c r="D38" s="270" t="s">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="E38" s="288" t="s">
-        <v>1846</v>
+        <v>1844</v>
       </c>
       <c r="F38" s="288"/>
     </row>
@@ -12866,13 +17408,13 @@
         <v>97</v>
       </c>
       <c r="C39" s="87" t="s">
-        <v>1699</v>
+        <v>1697</v>
       </c>
       <c r="D39" s="87" t="s">
-        <v>1700</v>
+        <v>1698</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1832</v>
+        <v>1830</v>
       </c>
       <c r="F39" s="87"/>
     </row>
@@ -12884,10 +17426,10 @@
         <v>99</v>
       </c>
       <c r="C40" s="87" t="s">
-        <v>1701</v>
+        <v>1699</v>
       </c>
       <c r="D40" s="270" t="s">
-        <v>1705</v>
+        <v>1703</v>
       </c>
       <c r="E40" s="270"/>
       <c r="F40" s="270"/>
@@ -12900,10 +17442,10 @@
         <v>101</v>
       </c>
       <c r="C41" s="88" t="s">
-        <v>1702</v>
+        <v>1700</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>1813</v>
+        <v>1811</v>
       </c>
       <c r="E41" s="88"/>
       <c r="F41" s="88"/>
@@ -12916,13 +17458,13 @@
         <v>103</v>
       </c>
       <c r="C42" s="86" t="s">
-        <v>1706</v>
+        <v>1704</v>
       </c>
       <c r="D42" s="268" t="s">
-        <v>1707</v>
+        <v>1705</v>
       </c>
       <c r="E42" s="268" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="F42" s="268"/>
     </row>
@@ -12934,10 +17476,10 @@
         <v>107</v>
       </c>
       <c r="C43" s="87" t="s">
-        <v>1716</v>
+        <v>1714</v>
       </c>
       <c r="D43" s="87" t="s">
-        <v>1708</v>
+        <v>1706</v>
       </c>
       <c r="E43" s="87"/>
       <c r="F43" s="87"/>
@@ -12950,13 +17492,13 @@
         <v>109</v>
       </c>
       <c r="C44" s="87" t="s">
-        <v>1709</v>
+        <v>1707</v>
       </c>
       <c r="D44" s="270" t="s">
-        <v>1710</v>
+        <v>1708</v>
       </c>
       <c r="E44" s="270" t="s">
-        <v>1833</v>
+        <v>1831</v>
       </c>
       <c r="F44" s="270"/>
     </row>
@@ -12968,13 +17510,13 @@
         <v>111</v>
       </c>
       <c r="C45" s="87" t="s">
-        <v>1711</v>
+        <v>1709</v>
       </c>
       <c r="D45" s="87" t="s">
-        <v>1718</v>
+        <v>1716</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>1836</v>
+        <v>1834</v>
       </c>
       <c r="F45" s="87"/>
     </row>
@@ -12986,10 +17528,10 @@
         <v>113</v>
       </c>
       <c r="C46" s="87" t="s">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="D46" s="270" t="s">
-        <v>1713</v>
+        <v>1711</v>
       </c>
       <c r="E46" s="270"/>
       <c r="F46" s="270"/>
@@ -13002,13 +17544,13 @@
         <v>115</v>
       </c>
       <c r="C47" s="87" t="s">
-        <v>1714</v>
+        <v>1712</v>
       </c>
       <c r="D47" s="87" t="s">
-        <v>1719</v>
+        <v>1717</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="F47" s="87"/>
     </row>
@@ -13020,7 +17562,7 @@
         <v>117</v>
       </c>
       <c r="C48" s="87" t="s">
-        <v>1721</v>
+        <v>1719</v>
       </c>
       <c r="D48" s="270"/>
       <c r="E48" s="270"/>
@@ -13034,13 +17576,13 @@
         <v>119</v>
       </c>
       <c r="C49" s="88" t="s">
-        <v>1715</v>
+        <v>1713</v>
       </c>
       <c r="D49" s="88" t="s">
-        <v>1722</v>
+        <v>1720</v>
       </c>
       <c r="E49" s="88" t="s">
-        <v>1837</v>
+        <v>1835</v>
       </c>
       <c r="F49" s="88"/>
     </row>
@@ -13052,14 +17594,14 @@
         <v>122</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>1817</v>
+        <v>1815</v>
       </c>
       <c r="D50" s="268"/>
       <c r="E50" s="268" t="s">
-        <v>1847</v>
+        <v>1845</v>
       </c>
       <c r="F50" s="268" t="s">
-        <v>1704</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13070,14 +17612,14 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1738</v>
+        <v>1736</v>
       </c>
       <c r="D51" s="87"/>
       <c r="E51" s="87" t="s">
-        <v>1848</v>
+        <v>1846</v>
       </c>
       <c r="F51" s="87" t="s">
-        <v>1843</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13088,14 +17630,14 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1741</v>
+        <v>1739</v>
       </c>
       <c r="D52" s="270"/>
       <c r="E52" s="270" t="s">
-        <v>1838</v>
+        <v>1836</v>
       </c>
       <c r="F52" s="270" t="s">
-        <v>1844</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -13106,7 +17648,7 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1739</v>
+        <v>1737</v>
       </c>
       <c r="D53" s="87"/>
       <c r="E53" s="87"/>
@@ -13120,7 +17662,7 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
       <c r="D54" s="270"/>
       <c r="E54" s="270"/>
@@ -13134,10 +17676,10 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="D55" s="87" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="E55" s="87"/>
       <c r="F55" s="87"/>
@@ -13150,10 +17692,10 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="D56" s="270" t="s">
-        <v>1737</v>
+        <v>1735</v>
       </c>
       <c r="E56" s="270"/>
       <c r="F56" s="270"/>
@@ -13166,10 +17708,10 @@
         <v>143</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>1754</v>
+        <v>1752</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="E57" s="88"/>
       <c r="F57" s="88"/>
@@ -13182,11 +17724,11 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="D58" s="268"/>
       <c r="E58" s="268" t="s">
-        <v>1757</v>
+        <v>1755</v>
       </c>
       <c r="F58" s="268"/>
     </row>
@@ -13198,11 +17740,11 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="D59" s="87"/>
       <c r="E59" s="87" t="s">
-        <v>1755</v>
+        <v>1753</v>
       </c>
       <c r="F59" s="87"/>
     </row>
@@ -13214,11 +17756,11 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1756</v>
+        <v>1754</v>
       </c>
       <c r="D60" s="270"/>
       <c r="E60" s="270" t="s">
-        <v>1835</v>
+        <v>1833</v>
       </c>
       <c r="F60" s="270"/>
     </row>
@@ -13230,10 +17772,10 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1758</v>
+        <v>1756</v>
       </c>
       <c r="D61" s="87" t="s">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="E61" s="87"/>
       <c r="F61" s="87"/>
@@ -13246,11 +17788,11 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1814</v>
+        <v>1812</v>
       </c>
       <c r="D62" s="270"/>
       <c r="E62" s="270" t="s">
-        <v>1815</v>
+        <v>1813</v>
       </c>
       <c r="F62" s="270"/>
     </row>
@@ -13262,10 +17804,10 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="D63" s="87" t="s">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="E63" s="87"/>
       <c r="F63" s="87"/>
@@ -13278,7 +17820,7 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="D64" s="270"/>
       <c r="E64" s="270"/>
@@ -13292,10 +17834,10 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="E65" s="88"/>
       <c r="F65" s="88"/>
@@ -13308,11 +17850,11 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1759</v>
+        <v>1757</v>
       </c>
       <c r="D66" s="268"/>
       <c r="E66" s="268" t="s">
-        <v>1834</v>
+        <v>1832</v>
       </c>
       <c r="F66" s="268"/>
     </row>
@@ -13324,11 +17866,11 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1760</v>
+        <v>1758</v>
       </c>
       <c r="D67" s="87"/>
       <c r="E67" s="87" t="s">
-        <v>1818</v>
+        <v>1816</v>
       </c>
       <c r="F67" s="87"/>
     </row>
@@ -13340,16 +17882,16 @@
         <v>1273</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1761</v>
+        <v>1759</v>
       </c>
       <c r="D68" s="272" t="s">
-        <v>1762</v>
+        <v>1760</v>
       </c>
       <c r="E68" s="272" t="s">
-        <v>1845</v>
+        <v>1843</v>
       </c>
       <c r="F68" s="272" t="s">
-        <v>1842</v>
+        <v>1840</v>
       </c>
     </row>
   </sheetData>
@@ -13401,7 +17943,7 @@
         <v>541</v>
       </c>
       <c r="G1" s="259" t="s">
-        <v>1553</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -13421,10 +17963,10 @@
         <v>1511</v>
       </c>
       <c r="F2" s="261" t="s">
-        <v>1551</v>
+        <v>1549</v>
       </c>
       <c r="G2" s="262" t="s">
-        <v>1554</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="3" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -13447,7 +17989,7 @@
         <v>542</v>
       </c>
       <c r="G3" s="170" t="s">
-        <v>1555</v>
+        <v>1553</v>
       </c>
       <c r="H3" s="263"/>
     </row>
@@ -13471,7 +18013,7 @@
         <v>544</v>
       </c>
       <c r="G4" s="170" t="s">
-        <v>1556</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="5" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -13494,12 +18036,12 @@
         <v>545</v>
       </c>
       <c r="G5" s="170" t="s">
-        <v>1557</v>
+        <v>1555</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="167" t="s">
-        <v>1539</v>
+        <v>1848</v>
       </c>
       <c r="B6" s="169" t="s">
         <v>1506</v>
@@ -13517,35 +18059,35 @@
         <v>546</v>
       </c>
       <c r="G6" s="170" t="s">
-        <v>1558</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="167" t="s">
-        <v>1540</v>
+        <v>1849</v>
       </c>
       <c r="B7" s="169" t="s">
         <v>1532</v>
       </c>
       <c r="C7" s="169" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D7" s="169" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E7" s="169" t="s">
         <v>1544</v>
       </c>
-      <c r="D7" s="169" t="s">
+      <c r="F7" s="169" t="s">
         <v>1545</v>
       </c>
-      <c r="E7" s="169" t="s">
-        <v>1546</v>
-      </c>
-      <c r="F7" s="169" t="s">
-        <v>1547</v>
-      </c>
       <c r="G7" s="170" t="s">
-        <v>1559</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="167" t="s">
-        <v>1541</v>
+        <v>1539</v>
       </c>
       <c r="B8" s="169" t="s">
         <v>1507</v>
@@ -13563,35 +18105,35 @@
         <v>1526</v>
       </c>
       <c r="G8" s="170" t="s">
-        <v>1560</v>
+        <v>1558</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="167" t="s">
-        <v>1542</v>
+        <v>1540</v>
       </c>
       <c r="B9" s="169" t="s">
         <v>1533</v>
       </c>
       <c r="C9" s="169" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D9" s="169" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E9" s="169" t="s">
         <v>1548</v>
       </c>
-      <c r="D9" s="169" t="s">
-        <v>1552</v>
-      </c>
-      <c r="E9" s="169" t="s">
-        <v>1550</v>
-      </c>
       <c r="F9" s="169" t="s">
-        <v>1549</v>
+        <v>1547</v>
       </c>
       <c r="G9" s="170" t="s">
-        <v>1561</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="175" t="s">
-        <v>1543</v>
+        <v>1541</v>
       </c>
       <c r="B10" s="176" t="s">
         <v>1534</v>
@@ -13609,7 +18151,7 @@
         <v>1530</v>
       </c>
       <c r="G10" s="178" t="s">
-        <v>1562</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -13692,10 +18234,10 @@
     <row r="20" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="1:5" ht="78.599999999999994" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="301" t="s">
-        <v>1622</v>
+        <v>1620</v>
       </c>
       <c r="B21" s="302" t="s">
-        <v>1623</v>
+        <v>1621</v>
       </c>
     </row>
   </sheetData>
@@ -16670,7 +21212,7 @@
         <v>1104</v>
       </c>
       <c r="F24" s="99" t="s">
-        <v>1805</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17110,7 +21652,7 @@
         <v>1191</v>
       </c>
       <c r="F46" s="99" t="s">
-        <v>1806</v>
+        <v>1804</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17150,7 +21692,7 @@
         <v>1198</v>
       </c>
       <c r="F48" s="99" t="s">
-        <v>1807</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -17504,7 +22046,7 @@
         <v>1267</v>
       </c>
       <c r="D66" s="86" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="E66" s="86" t="s">
         <v>1268</v>
@@ -17524,7 +22066,7 @@
         <v>1270</v>
       </c>
       <c r="D67" s="87" t="s">
-        <v>1811</v>
+        <v>1809</v>
       </c>
       <c r="E67" s="87" t="s">
         <v>1271</v>
@@ -17538,19 +22080,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="88" t="s">
+        <v>1806</v>
+      </c>
+      <c r="C68" s="88" t="s">
+        <v>1807</v>
+      </c>
+      <c r="D68" s="88" t="s">
         <v>1808</v>
       </c>
-      <c r="C68" s="88" t="s">
-        <v>1809</v>
-      </c>
-      <c r="D68" s="88" t="s">
-        <v>1810</v>
-      </c>
       <c r="E68" s="88" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
       <c r="F68" s="101" t="s">
-        <v>1810</v>
+        <v>1808</v>
       </c>
     </row>
   </sheetData>
@@ -17824,16 +22366,16 @@
         <v>40</v>
       </c>
       <c r="C13" s="253" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D13" s="254" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E13" s="140" t="s">
         <v>1563</v>
       </c>
-      <c r="D13" s="254" t="s">
+      <c r="F13" s="249" t="s">
         <v>1564</v>
-      </c>
-      <c r="E13" s="140" t="s">
-        <v>1565</v>
-      </c>
-      <c r="F13" s="249" t="s">
-        <v>1566</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18564,16 +23106,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="250" t="s">
+        <v>1762</v>
+      </c>
+      <c r="D50" s="289" t="s">
+        <v>1763</v>
+      </c>
+      <c r="E50" s="251" t="s">
         <v>1764</v>
       </c>
-      <c r="D50" s="289" t="s">
+      <c r="F50" s="252" t="s">
         <v>1765</v>
-      </c>
-      <c r="E50" s="251" t="s">
-        <v>1766</v>
-      </c>
-      <c r="F50" s="252" t="s">
-        <v>1767</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18584,16 +23126,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="253" t="s">
+        <v>1766</v>
+      </c>
+      <c r="D51" s="254" t="s">
+        <v>1767</v>
+      </c>
+      <c r="E51" s="140" t="s">
         <v>1768</v>
       </c>
-      <c r="D51" s="254" t="s">
+      <c r="F51" s="249" t="s">
         <v>1769</v>
-      </c>
-      <c r="E51" s="140" t="s">
-        <v>1770</v>
-      </c>
-      <c r="F51" s="249" t="s">
-        <v>1771</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18604,16 +23146,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="253" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D52" s="254" t="s">
+        <v>1771</v>
+      </c>
+      <c r="E52" s="140" t="s">
         <v>1772</v>
       </c>
-      <c r="D52" s="254" t="s">
+      <c r="F52" s="249" t="s">
         <v>1773</v>
-      </c>
-      <c r="E52" s="140" t="s">
-        <v>1774</v>
-      </c>
-      <c r="F52" s="249" t="s">
-        <v>1775</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -18844,16 +23386,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="253" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D64" s="254" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E64" s="140" t="s">
         <v>1776</v>
       </c>
-      <c r="D64" s="254" t="s">
+      <c r="F64" s="249" t="s">
         <v>1777</v>
-      </c>
-      <c r="E64" s="140" t="s">
-        <v>1778</v>
-      </c>
-      <c r="F64" s="249" t="s">
-        <v>1779</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18884,16 +23426,16 @@
         <v>165</v>
       </c>
       <c r="C66" s="250" t="s">
-        <v>1780</v>
+        <v>1778</v>
       </c>
       <c r="D66" s="289" t="s">
-        <v>1781</v>
+        <v>1779</v>
       </c>
       <c r="E66" s="193" t="s">
         <v>761</v>
       </c>
       <c r="F66" s="252" t="s">
-        <v>1782</v>
+        <v>1780</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -18904,10 +23446,10 @@
         <v>168</v>
       </c>
       <c r="C67" s="255" t="s">
-        <v>1783</v>
+        <v>1781</v>
       </c>
       <c r="D67" s="256" t="s">
-        <v>1784</v>
+        <v>1782</v>
       </c>
       <c r="E67" s="199" t="s">
         <v>762</v>
@@ -18924,16 +23466,16 @@
         <v>1273</v>
       </c>
       <c r="C68" s="264" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D68" s="265" t="s">
+        <v>1784</v>
+      </c>
+      <c r="E68" s="266" t="s">
         <v>1785</v>
       </c>
-      <c r="D68" s="265" t="s">
+      <c r="F68" s="267" t="s">
         <v>1786</v>
-      </c>
-      <c r="E68" s="266" t="s">
-        <v>1787</v>
-      </c>
-      <c r="F68" s="267" t="s">
-        <v>1788</v>
       </c>
     </row>
   </sheetData>
@@ -19947,7 +24489,7 @@
         <v>122</v>
       </c>
       <c r="C50" s="224" t="s">
-        <v>1789</v>
+        <v>1787</v>
       </c>
       <c r="D50" s="225" t="s">
         <v>956</v>
@@ -19967,16 +24509,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="227" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D51" s="228" t="s">
+        <v>1789</v>
+      </c>
+      <c r="E51" s="229" t="s">
         <v>1790</v>
       </c>
-      <c r="D51" s="228" t="s">
+      <c r="F51" s="219" t="s">
         <v>1791</v>
-      </c>
-      <c r="E51" s="229" t="s">
-        <v>1792</v>
-      </c>
-      <c r="F51" s="219" t="s">
-        <v>1793</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -19987,16 +24529,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="227" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D52" s="228" t="s">
+        <v>1793</v>
+      </c>
+      <c r="E52" s="229" t="s">
         <v>1794</v>
       </c>
-      <c r="D52" s="228" t="s">
+      <c r="F52" s="219" t="s">
         <v>1795</v>
-      </c>
-      <c r="E52" s="229" t="s">
-        <v>1796</v>
-      </c>
-      <c r="F52" s="219" t="s">
-        <v>1797</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -20227,7 +24769,7 @@
         <v>160</v>
       </c>
       <c r="C64" s="227" t="s">
-        <v>1798</v>
+        <v>1796</v>
       </c>
       <c r="D64" s="228" t="s">
         <v>1003</v>
@@ -20267,7 +24809,7 @@
         <v>165</v>
       </c>
       <c r="C66" s="212" t="s">
-        <v>1799</v>
+        <v>1797</v>
       </c>
       <c r="D66" s="213" t="s">
         <v>1010</v>
@@ -20287,16 +24829,16 @@
         <v>168</v>
       </c>
       <c r="C67" s="216" t="s">
-        <v>1800</v>
+        <v>1798</v>
       </c>
       <c r="D67" s="217" t="s">
         <v>1013</v>
       </c>
       <c r="E67" s="299" t="s">
-        <v>1801</v>
+        <v>1799</v>
       </c>
       <c r="F67" s="296" t="s">
-        <v>1802</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -20304,19 +24846,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="77" t="s">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C68" s="293" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="D68" s="294" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="E68" s="300" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="F68" s="297" t="s">
-        <v>1804</v>
+        <v>1802</v>
       </c>
     </row>
   </sheetData>

--- a/LunaRune66.xlsx
+++ b/LunaRune66.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8676" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Basic" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3073" uniqueCount="2141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3087" uniqueCount="2156">
   <si>
     <t>編號</t>
   </si>
@@ -5877,14 +5877,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>時間、日期、月份、時刻、時間點、曆、行事曆、日常、計時</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>遲到、延誤</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>擁擠、壓縮</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5893,10 +5885,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>時期、階段、期間、時段、早晨、上午、下午、傍晚</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>藉口・歸咎</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -5934,10 +5922,6 @@
   </si>
   <si>
     <t>時機、契機、巧合</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>錯過、不合時宜</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -6303,10 +6287,6 @@
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
-    <t>星火為禍、日月為星、明星沒有</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
     <t>意識歸魂而潛意識歸夢</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
@@ -6336,14 +6316,6 @@
   </si>
   <si>
     <t>鑽石為鑽、月光石是石</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>日光為光、日月為星、日一個單字是星或時</t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
-  <si>
-    <t>月光為暗、日月為星、月一個單字是星或時</t>
     <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
@@ -6381,18 +6353,6 @@
         <family val="2"/>
         <scheme val="major"/>
       </rPr>
-      <t>項目</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="3"/>
-        <rFont val="Calibri Light"/>
-        <family val="2"/>
-        <scheme val="major"/>
-      </rPr>
       <t>內容</t>
     </r>
   </si>
@@ -6409,210 +6369,15 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>全域</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>語法分層</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>詞彙層</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>卡片位置層</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>治理層</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>時間修飾層</t>
-    </r>
-  </si>
-  <si>
     <t>後層時間的月相交互只作修飾，不覆蓋符文本義。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>單卡</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>治理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>解牌方式</t>
-    </r>
-  </si>
-  <si>
     <t>符文本義＋卡牌方向＋月相交互</t>
   </si>
   <si>
     <t>月相交互只作低權重時間修飾。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>兩卡</t>
-    </r>
-  </si>
-  <si>
     <t>治理解牌方式</t>
   </si>
   <si>
@@ -6622,1322 +6387,978 @@
     <t>交互描述兩個主題因果如何作用，不單獨決定吉凶。</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>三卡</t>
-    </r>
-  </si>
-  <si>
-    <t>源＋轉＋合＋月相交互</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>形成「源起、過程、顯化」的完整圖景。</t>
-    </r>
-  </si>
-  <si>
     <t>源</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>啟動點、潛因、內在狀態</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>回答事情從何而起。</t>
-    </r>
-  </si>
-  <si>
     <t>轉</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>過程中介、能量互動、挑戰與助力</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>回答事情如何轉化。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>合</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>結果顯化、整合方向、當下建議</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>不是絕對宿命判決。</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>五卡</t>
-    </r>
-  </si>
-  <si>
-    <t>過去＋現在＋未來顯化＋周圍環境＋自己心境＋月相交互</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>不是「兩卡＋三卡」的拼接。</t>
-    </r>
-  </si>
-  <si>
-    <t>過去</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>過去、成因、既有條件</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>回答「現在為何形成」。</t>
-    </r>
-  </si>
-  <si>
-    <t>現在</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>當前核心狀態</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>五卡主句與主要判讀中心。</t>
-    </r>
-  </si>
-  <si>
-    <t>未來顯化</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>若目前條件延續，最可能的發展趨勢</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>不是絕對結果。</t>
-    </r>
-  </si>
-  <si>
-    <t>環境</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>他人、環境、制度、現實限制與外部助力</t>
-    </r>
-  </si>
-  <si>
-    <t>周圍環境的狀態</t>
-  </si>
-  <si>
-    <t>心境</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>本人立場、期待、恐懼、動機與主觀認知</t>
-    </r>
-  </si>
-  <si>
-    <t>自己心境的狀態</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>關係優先</t>
-    </r>
-  </si>
-  <si>
-    <t>過去→現在→未來→環境→心境</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>只計算具有語義關係的卡對，不要求五張彼此全連。</t>
-    </r>
-  </si>
-  <si>
     <t>OW3gs</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1–6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>因的描述層</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>＋</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">7–11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>果的判定層＋月相交互</t>
-    </r>
-  </si>
-  <si>
-    <t>用符文模型完整形容事件，十一張牌不是等權並列。</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1–6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>因的描述層</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>背景</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 2.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>現在</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 3.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>資源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 4.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>意向</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 5.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>外部擾動</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 6.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>尚未成形因素</t>
-    </r>
-  </si>
-  <si>
-    <t>分析產生問題的可能狀態</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">7–11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>果的判定層</t>
-    </r>
-  </si>
-  <si>
-    <t>建議：7.成因 8.現在 9.未來 10.環境 11.心境</t>
-  </si>
-  <si>
-    <t>建議該怎麼做的治理原則。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>讀取順序</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>先讀</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 7–11 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>再掃描</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 1–6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>→</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>最後套月相交互</t>
-    </r>
-  </si>
-  <si>
     <t>治理原則為分成兩個模型。鑑古知今為原則。</t>
   </si>
   <si>
     <t>額外說明</t>
   </si>
   <si>
+    <t>重在模型的關聯，而非把抽牌維度提高的複雜化。</t>
+  </si>
+  <si>
+    <t>描述兩個符文語義主題的共鳴、互補、衝突與語氣張力</t>
+  </si>
+  <si>
+    <t>月符沙盒專用，因符文關係為平等。</t>
+  </si>
+  <si>
+    <t>月相交互</t>
+  </si>
+  <si>
+    <t>額外小幅低權重</t>
+  </si>
+  <si>
+    <t>卡片月相跟真實月相的交互作用</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>關係/模式</t>
+  </si>
+  <si>
+    <t>解釋/訊息</t>
+  </si>
+  <si>
+    <t>↑</t>
+  </si>
+  <si>
+    <t>正位</t>
+  </si>
+  <si>
+    <t>能量順行｜主題自然流動、力量顯現、外顯無礙</t>
+  </si>
+  <si>
+    <t>＋</t>
+  </si>
+  <si>
+    <t>半正位</t>
+  </si>
+  <si>
+    <t>初生漸顯｜潛能正在凝聚、尚未完全流動，代表準備與激活</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>半逆位</t>
+  </si>
+  <si>
+    <t>釋放收束｜能量正在退潮、進入整合期，是轉化與療癒階段</t>
+  </si>
+  <si>
+    <t>↓</t>
+  </si>
+  <si>
+    <t>逆位</t>
+  </si>
+  <si>
+    <t>能量阻滯｜主題反向顯現、力量扭曲、潛藏或危機感浮現</t>
+  </si>
+  <si>
+    <t>新月☉</t>
+  </si>
+  <si>
+    <t>正位（↑）</t>
+  </si>
+  <si>
+    <t>種子發芽</t>
+  </si>
+  <si>
+    <t>內在意圖與宇宙準備一致，適合啟動靜默中的創造</t>
+  </si>
+  <si>
+    <t>半正位（＋）</t>
+  </si>
+  <si>
+    <t>光尚未現</t>
+  </si>
+  <si>
+    <t>內在想動但時機未到，建議靜觀其變，等待契機</t>
+  </si>
+  <si>
+    <t>半逆位（—）</t>
+  </si>
+  <si>
+    <t>內潛釋放</t>
+  </si>
+  <si>
+    <t>正在釋放舊的創傷種子，是蛻變的準備期</t>
+  </si>
+  <si>
+    <t>逆位（↓）</t>
+  </si>
+  <si>
+    <t>種子阻塞</t>
+  </si>
+  <si>
+    <t>潛意識被壓抑，黑暗中難見光，需自我淨化與釋放</t>
+  </si>
+  <si>
+    <t>上弦△</t>
+  </si>
+  <si>
+    <t>行動之力</t>
+  </si>
+  <si>
+    <t>內外一致推進，適合主動出擊，逐步構建理想</t>
+  </si>
+  <si>
+    <t>焦躁之芽</t>
+  </si>
+  <si>
+    <t>內心躁動但實際力道尚不足，建議規劃而非急行</t>
+  </si>
+  <si>
+    <t>回收嘗試</t>
+  </si>
+  <si>
+    <t>曾嘗試某事未果，現在正在撤回與調整策略</t>
+  </si>
+  <si>
+    <t>阻斷行動</t>
+  </si>
+  <si>
+    <t>外力推動但你卻抗拒行動，可能因恐懼或拖延</t>
+  </si>
+  <si>
+    <t>滿月●</t>
+  </si>
+  <si>
+    <t>顯化高峰</t>
+  </si>
+  <si>
+    <t>內外完全共振，是展現、收穫與綻放的時刻</t>
+  </si>
+  <si>
+    <t>光中迷失</t>
+  </si>
+  <si>
+    <t>雖處高峰但焦點不明，可能能量過盛造成混亂</t>
+  </si>
+  <si>
+    <t>光後退場</t>
+  </si>
+  <si>
+    <t>繁盛之後開始退 潮，是總結與整合的契機</t>
+  </si>
+  <si>
+    <t>反射之光</t>
+  </si>
+  <si>
+    <t>事情表面光鮮但內裡不實，建議內觀真實感受</t>
+  </si>
+  <si>
+    <t>下弦▼</t>
+  </si>
+  <si>
+    <t>釋放清明</t>
+  </si>
+  <si>
+    <t>內在與宇宙都進入收束，適合整理與放下</t>
+  </si>
+  <si>
+    <t>整理未完</t>
+  </si>
+  <si>
+    <t>你開始整理但仍有執著，建議覺察仍卡住之處</t>
+  </si>
+  <si>
+    <t>釋放完成</t>
+  </si>
+  <si>
+    <t>你正好順勢放手，是準備迎接新週期的轉點</t>
+  </si>
+  <si>
+    <t>固執難釋</t>
+  </si>
+  <si>
+    <t>該放的未放，可能陷入重複舊模式的循環中</t>
+  </si>
+  <si>
+    <t>流暢合鳴</t>
+  </si>
+  <si>
+    <t>雙主題順行，宇宙與內在共振，是最強顯化組合之~</t>
+  </si>
+  <si>
+    <t>引導激活</t>
+  </si>
+  <si>
+    <t>你已行動，但另一主題尚待展現，是領導與帶動的結構</t>
+  </si>
+  <si>
+    <t>前行與整合</t>
+  </si>
+  <si>
+    <t>行動中帶有反思或療癒意味，是從創傷中推進的力量</t>
+  </si>
+  <si>
+    <t>前行與牽絆</t>
+  </si>
+  <si>
+    <t>你行進中卻被另一能量拉住，代表矛盾與修正功課</t>
+  </si>
+  <si>
+    <t>準備與照映</t>
+  </si>
+  <si>
+    <t>尚未動身的你，看見他人或外界已經啟動，是激勵與感應</t>
+  </si>
+  <si>
+    <t>潛能交疊</t>
+  </si>
+  <si>
+    <t>兩能量都在蓄勢待發，強烈暗示蘊含巨大突破可能</t>
+  </si>
+  <si>
+    <t>啟動回收交錯</t>
+  </si>
+  <si>
+    <t>有些還沒開始，有些已進入整合，是交叉能量場</t>
+  </si>
+  <si>
+    <t>內外緊張</t>
+  </si>
+  <si>
+    <t>準備階段受到阻力，需辨識內在恐懼或外在制約</t>
+  </si>
+  <si>
+    <t>內整外行</t>
+  </si>
+  <si>
+    <t>你已完成內在釋放，準備讓顯化能量帶動轉變</t>
+  </si>
+  <si>
+    <t>整合啟動序列</t>
+  </si>
+  <si>
+    <t>如同從療癒中走向重生，是自然節奏的過渡</t>
+  </si>
+  <si>
+    <t>雙向轉化</t>
+  </si>
+  <si>
+    <t>兩主題都在整合與釋放，為內在極佳的重建機會</t>
+  </si>
+  <si>
+    <t>殘餘影響</t>
+  </si>
+  <si>
+    <t>你已準備放手，但過往殘影仍在干擾，建議深層釋放</t>
+  </si>
+  <si>
+    <t>阻力轉化</t>
+  </si>
+  <si>
+    <t>你的陰影或課題正被顯化的能量反映出來，適合內觀</t>
+  </si>
+  <si>
+    <t>危機激化</t>
+  </si>
+  <si>
+    <t>混亂與潛能交錯，可能進入情緒／能量波動期</t>
+  </si>
+  <si>
+    <t>解構療癒</t>
+  </si>
+  <si>
+    <t>從混亂轉入療癒，代表自我解體與重組過程</t>
+  </si>
+  <si>
+    <t>雙重阻滯</t>
+  </si>
+  <si>
+    <t>兩個主題都處於逆流，建議停下腳步，進行深度清理</t>
+  </si>
+  <si>
+    <t>正</t>
+  </si>
+  <si>
+    <t>順行顯化</t>
+  </si>
+  <si>
+    <t>內外三位一致，強烈顯化循環，是展現與實現的命運契機</t>
+  </si>
+  <si>
+    <t>半正</t>
+  </si>
+  <si>
+    <t>穩定激活</t>
+  </si>
+  <si>
+    <t>行動穩定推進中，結果仍在醞釀與調整階段，提醒你保持耐心與信任。</t>
+  </si>
+  <si>
+    <t>半逆</t>
+  </si>
+  <si>
+    <t>尚未完成</t>
+  </si>
+  <si>
+    <t>內外一致但結尾偏弱，表示需要補強或延伸支持系統。</t>
+  </si>
+  <si>
+    <t>逆</t>
+  </si>
+  <si>
+    <t>明顯受阻</t>
+  </si>
+  <si>
+    <t>儘管起步順利，中後段力量突然斷裂，可能遭遇突發干擾或未察覺的內在抗拒。</t>
+  </si>
+  <si>
+    <t>領航共振</t>
+  </si>
+  <si>
+    <t>你已在穩定前行之路上，過程帶動他人或局勢逐步啟動，結果象徵良好回響與共振顯化。</t>
+  </si>
+  <si>
+    <t>漸進合流</t>
+  </si>
+  <si>
+    <t>穩定出發並正在推動變化，最終抵達一個尚未完全顯化但趨勢良好的節點，建議保持節奏。</t>
+  </si>
+  <si>
+    <t>外顯內縮</t>
+  </si>
+  <si>
+    <t>雖然整體能量持續展開，但結尾傾向收斂與整合，可能需要重新聚焦或調整方向。</t>
+  </si>
+  <si>
+    <t>外順內裂</t>
+  </si>
+  <si>
+    <t>起始順利並逐步啟動，但最終可能因忽略內在訊號或潛在隱憂而出現能量反轉。</t>
+  </si>
+  <si>
+    <t>前行整合</t>
+  </si>
+  <si>
+    <t>穩定出發後進入內在整合階段，最終重新對齊初衷，是帶有覺察與調整後的顯化。</t>
+  </si>
+  <si>
+    <t>穩中有伏</t>
+  </si>
+  <si>
+    <t>外在穩定推進，但過程內收、結果尚未完全打開，象徵能量正在重新聚焦，建議不急於顯現。</t>
+  </si>
+  <si>
+    <t>穩定退潮</t>
+  </si>
+  <si>
+    <t>起點穩固，但整體能量逐步收束，暗示你可能正在完成一段歷程或進入沉潛期。</t>
+  </si>
+  <si>
+    <t>外強內崩</t>
+  </si>
+  <si>
+    <t>雖然你以堅定姿態開始，但內在整合不穩，最終導致力量崩潰或情勢逆轉，需正視內在裂縫。</t>
+  </si>
+  <si>
+    <t>內斷外續</t>
+  </si>
+  <si>
+    <t>中段遭遇阻力但整體仍推進，提醒過程中需正視陰影課題。</t>
+  </si>
+  <si>
+    <t>穩中現憂</t>
+  </si>
+  <si>
+    <t>雖然最終看似可見轉機，但中途的反轉仍可能留下未處理的陰影或疑慮，需逐步釐清。</t>
+  </si>
+  <si>
+    <t>逆後整合</t>
+  </si>
+  <si>
+    <t>經歷中段挫折後進入能量收束，表示你開始試圖整理錯誤或修補破裂狀態。</t>
+  </si>
+  <si>
+    <t>反轉崩解</t>
+  </si>
+  <si>
+    <t>雖有良好起步，但命運之力遭遇劇烈反彈，情勢進一步惡化，需重新評估整體方向。</t>
+  </si>
+  <si>
+    <t>漸啟顯化</t>
+  </si>
+  <si>
+    <t>從醞釀走向實踐，最終達到完整顯化，是潛能被喚醒後的強力展現期。</t>
+  </si>
+  <si>
+    <t>引導未竟</t>
+  </si>
+  <si>
+    <t>雖有外力支持，但最終顯化尚不穩定，象徵你正被引領但還未全然開展。</t>
+  </si>
+  <si>
+    <t>力量反饋</t>
+  </si>
+  <si>
+    <t>實踐後產生回收效應，過程激烈但結尾進入反思與內在調整，需消化過多輸出。</t>
+  </si>
+  <si>
+    <t>承壓逆襲</t>
+  </si>
+  <si>
+    <t>外界壓力或主動行動過早啟動，導致結果無法承受能量負荷，最終產生逆轉或瓦解。</t>
+  </si>
+  <si>
+    <t>潛力爆發</t>
+  </si>
+  <si>
+    <t>雙重醞釀疊加後導致能量突破，是從靜默轉向顯現的關鍵躍進點。</t>
+  </si>
+  <si>
+    <t>穩定擴展</t>
+  </si>
+  <si>
+    <t>雖然進展不快，但穩定累積能量，整體狀態正在朝顯化前緩慢移動。</t>
+  </si>
+  <si>
+    <t>雙重內整</t>
+  </si>
+  <si>
+    <t>所有能量仍集中於內部醞釀與整合，顯示尚需時間消化轉變，不宜急行。</t>
+  </si>
+  <si>
+    <t>遲未轉化</t>
+  </si>
+  <si>
+    <t>醞釀過久而未能突破，能量卡滯導致反轉或錯失時機，需警惕停滯。</t>
+  </si>
+  <si>
+    <t>調和甦醒</t>
+  </si>
+  <si>
+    <t>初始潛能尚未展開，中段進入整合，最終由內而外重新對齊，是靜轉動的契機。</t>
+  </si>
+  <si>
+    <t>轉向萌動</t>
+  </si>
+  <si>
+    <t>你正在從內部調整過渡，能量逐步往外推展，象徵變化正在醞釀中。</t>
+  </si>
+  <si>
+    <t>靜能潛流</t>
+  </si>
+  <si>
+    <t>雙重內聚導致顯化遲緩，此時重點不在結果，而在內在建構與情緒沉澱。</t>
+  </si>
+  <si>
+    <t>未果回折</t>
+  </si>
+  <si>
+    <t>雖有起步之意，但能量過程無法外放，最終進入停滯或反向，提醒你重審動機與方法。</t>
+  </si>
+  <si>
+    <t>陰中返陽</t>
+  </si>
+  <si>
+    <t>儘管中段受阻，你仍可能轉化壓力為動力，結果迎來正面顯現，是逆勢中的突破之機。</t>
+  </si>
+  <si>
+    <t>調和未果</t>
+  </si>
+  <si>
+    <t>原本的行動被打斷，雖試圖重啟，但能量仍顯薄弱，結果顯示需更多支持與耐性。</t>
+  </si>
+  <si>
+    <t>崩後整理</t>
+  </si>
+  <si>
+    <t>結構中斷後進入內整期，此時不宜急行，而要關注殘餘能量與情緒的重新歸位。</t>
+  </si>
+  <si>
+    <t>錯失良機</t>
+  </si>
+  <si>
+    <t>醞釀之力未能及時展開，內外阻力接連出現，導致整體逆轉，提醒你勿忽略時機感。</t>
+  </si>
+  <si>
+    <t>內整外展</t>
+  </si>
+  <si>
+    <t>經歷內在整合後開始外顯推進，最終達成成果，是從療癒走向顯化的實踐循環。</t>
+  </si>
+  <si>
+    <t>穩定恢復</t>
+  </si>
+  <si>
+    <t>你已從整合期中重建力量，當下正處於逐步展現的過渡階段，能量趨穩但仍在累積。</t>
+  </si>
+  <si>
+    <t>收整停歇</t>
+  </si>
+  <si>
+    <t>行動後你選擇退後一步，讓自己沉澱與修復，代表一種主動的收束與守成。</t>
+  </si>
+  <si>
+    <t>明進暗退</t>
+  </si>
+  <si>
+    <t>雖曾推進但內在仍有未解之處，最終結果可能反轉，提示過程中忽略了潛藏的情緒或關鍵細節。</t>
+  </si>
+  <si>
+    <t>轉折開啟</t>
+  </si>
+  <si>
+    <t>從整理中緩步提昇，能量逐漸轉向顯現，是柔性的進展節奏。</t>
+  </si>
+  <si>
+    <t>緩步醞釀</t>
+  </si>
+  <si>
+    <t>雙方能量皆未完全展開，整體處於準備與醞釀交疊的狀態，需耐心等待時機成熟。</t>
+  </si>
+  <si>
+    <t>反覆沉整</t>
+  </si>
+  <si>
+    <t>正在進行多層整合，能量上下起伏，代表反覆調整與內在回應。</t>
+  </si>
+  <si>
+    <t>動念挫敗</t>
+  </si>
+  <si>
+    <t>雖有出發意願，但行動未全然落地，最終因干擾或動搖導致退卻與終止。</t>
+  </si>
+  <si>
+    <t>準備出擊</t>
+  </si>
+  <si>
+    <t>潛能尚未完全覺醒，過程穩定發酵，是蓄力期後即將啟動的關鍵轉點。</t>
+  </si>
+  <si>
+    <t>潛勢待發</t>
+  </si>
+  <si>
+    <t>能量仍聚於內部調和，雖有萌動之兆，仍需觀察並等待更明確的啟動信號。</t>
+  </si>
+  <si>
+    <t>內潛反芻</t>
+  </si>
+  <si>
+    <t>三重整合暗示深層轉化期，雖未見表面動靜，但內在運作劇烈，建議靜守蛻變。</t>
+  </si>
+  <si>
+    <t>能量斷裂</t>
+  </si>
+  <si>
+    <t>整合未竟便遭受打擊，代表潛勢尚未穩固就被外力或自我否定截斷，需謹慎。</t>
+  </si>
+  <si>
+    <t>錯線復明</t>
+  </si>
+  <si>
+    <t>雖經挫折與混亂，但仍可能在過程中覺醒新的方向，重返有序的顯化路徑。</t>
+  </si>
+  <si>
+    <t>漸返有序</t>
+  </si>
+  <si>
+    <t>從內部整合轉向混沌後，正在努力重組秩序，象徵你開始試圖恢復掌控權。</t>
+  </si>
+  <si>
+    <t>疲勞整合</t>
+  </si>
+  <si>
+    <t>消耗與混亂交錯之後進入內省與療癒，這是一段身心重整的過渡期。</t>
+  </si>
+  <si>
+    <t>崩解退場</t>
+  </si>
+  <si>
+    <t>雙重壓力導致崩潰結果，代表當前局勢已無法支撐，需要終止或徹底退出。</t>
+  </si>
+  <si>
+    <t>療癒轉化</t>
+  </si>
+  <si>
+    <t>開場困難但力量漸升，是從創傷中走向覺醒的重建模式。</t>
+  </si>
+  <si>
+    <t>轉穩待啟</t>
+  </si>
+  <si>
+    <t>雖然已突破逆境，但仍需穩定醞釀，象徵進入恢復後的積蓄期。</t>
+  </si>
+  <si>
+    <t>陰影整合</t>
+  </si>
+  <si>
+    <t>力量被重新召回後，你選擇內省與調整，代表逆境後的深層整合與修復。</t>
+  </si>
+  <si>
+    <t>復甦未果</t>
+  </si>
+  <si>
+    <t>即使中段有所突破，但整體仍未脫離阻力圈，結果顯示復甦尚未徹底成功。</t>
+  </si>
+  <si>
+    <t>援引突破</t>
+  </si>
+  <si>
+    <t>你正從低谷中回升，外部助力將協助你重建自信與行動，突破當前瓶頸。</t>
+  </si>
+  <si>
+    <t>修補進展</t>
+  </si>
+  <si>
+    <t>雖未徹底恢復，但正在接受支持與引導，能量慢慢流動，有機會逐步恢復動能。</t>
+  </si>
+  <si>
+    <t>半明半昧</t>
+  </si>
+  <si>
+    <t>你正處於陰影與希望交界，內心仍有波動，但整體趨勢向調整與收束前進。</t>
+  </si>
+  <si>
+    <t>激盪未解</t>
+  </si>
+  <si>
+    <t>嘗試修復但未見成效，內外矛盾依然存在，可能需要更長期的處理與覺察。</t>
+  </si>
+  <si>
+    <t>解構重生</t>
+  </si>
+  <si>
+    <t>雖從混亂中開始，但你選擇整合與釋放，最終將迎來更新的顯化，是重生的徵兆。</t>
+  </si>
+  <si>
+    <t>漸進修補</t>
+  </si>
+  <si>
+    <t>你正從崩裂狀態中恢復，雖未完全顯化，但新的希望正在醞釀。</t>
+  </si>
+  <si>
+    <t>殘餘清理</t>
+  </si>
+  <si>
+    <t>持續面對過去創傷與未解議題，是一段深度清掃與修復的時期。</t>
+  </si>
+  <si>
+    <t>影纏未散</t>
+  </si>
+  <si>
+    <t>雖努力整合但陰影仍未退散，顯示你尚未真正放下，循環可能重演。</t>
+  </si>
+  <si>
+    <t>阻中現光</t>
+  </si>
+  <si>
+    <t>即使歷經多重阻力，你仍可能由內而外產生突破，是暗處覓光之路。</t>
+  </si>
+  <si>
+    <t>破舊立新</t>
+  </si>
+  <si>
+    <t>雙重逆境促成覺醒的動力，代表你正在重新建立新的行動路線與心態。</t>
+  </si>
+  <si>
+    <t>清算回潮</t>
+  </si>
+  <si>
+    <t>累積的卡滯正在退潮，你逐漸回到整合狀態，是深層療癒期的後段。</t>
+  </si>
+  <si>
+    <t>兩個主題都處於逆流，建議停下腳步，進行深度清理與自我審視。</t>
+  </si>
+  <si>
+    <t>符文演算法</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>項目</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>綜合</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>原理</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>例外解說</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>會有搞笑狀況</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>花枝是動物名</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽到花卡跟枝卡，不是該吃花枝了！當然也可以延伸啦！</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>額外意思</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>抽到四卡連續叫做 鏡花水月</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>表示會有幻出現嗎</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>額外意思</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>水土是地方，延伸到地之符文</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>關鍵詞延伸</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>全域</t>
+  </si>
+  <si>
+    <t>詞彙層 → 卡片位置層 → 治理層 → 時間修飾層</t>
+  </si>
+  <si>
+    <t>單卡</t>
+  </si>
+  <si>
+    <t>兩卡</t>
+  </si>
+  <si>
+    <t>三卡</t>
+  </si>
+  <si>
+    <t>啟動點、潛因、內在狀態</t>
+  </si>
+  <si>
+    <t>回答事情從何而起。</t>
+  </si>
+  <si>
+    <t>回答事情如何轉化。</t>
+  </si>
+  <si>
+    <t>合</t>
+  </si>
+  <si>
+    <t>結果顯化、整合方向、當下建議</t>
+  </si>
+  <si>
+    <t>不是絕對宿命判決。</t>
+  </si>
+  <si>
+    <t>五卡</t>
+  </si>
+  <si>
+    <t>1–6 因的描述層 ＋7–11 果的判定層＋月相交互</t>
+  </si>
+  <si>
+    <t>1–6 因的描述層</t>
+  </si>
+  <si>
+    <t>7–11 果的判定層</t>
+  </si>
+  <si>
+    <t>讀取順序</t>
+  </si>
+  <si>
+    <t>符文交互</t>
+  </si>
+  <si>
+    <t>真實月相是低權重時間情境修飾。</t>
+  </si>
+  <si>
+    <t>源兩張+轉兩張+合兩張。共6張。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>五卡的基本規則，共五張。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>先讀成因分析，後讀判斷分析，最後套月相交互</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
     <t>有時候跟每日符文交替比照，會很有意思。</t>
-  </si>
-  <si>
-    <t>重在模型的關聯，而非把抽牌維度提高的複雜化。</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>符文交互</t>
-    </r>
-  </si>
-  <si>
-    <t>描述兩個符文語義主題的共鳴、互補、衝突與語氣張力</t>
-  </si>
-  <si>
-    <t>月符沙盒專用，因符文關係為平等。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>分析產生問題的可能狀態，以雙卡跟三卡綜合判斷</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>建議該怎麼做的治理原則。以五卡方式來判斷</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>用符文組合模型完整形容事件，十一張牌不是等權並列。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>源（因）＋轉（意外因素）＋合（果）＋月相交互</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>過去的成因</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>由雙卡組合而成</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外變化</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>由單卡來告知</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>現在狀況</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>由雙卡組合而成</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>三項統一</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>模組應用</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙卡跟三卡的共同語意延伸</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是「兩卡＋三卡」的拼接，是組合。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>可能有意外的變因轉化</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>形成「源起、變因、顯化」的完整圖景。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙卡組合有時候會有例外</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外放一個因素就夠了。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>是現在以後可能的結論</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>意外是一個因素，所以單張而非雙張</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>兩張過去成因＋一個意外變化＋兩張現在狀況＋月相交互</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>呈現：雙卡＋單卡＋雙卡 的組合</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
   <si>
     <t>月相交互</t>
-  </si>
-  <si>
-    <t>額外小幅低權重</t>
-  </si>
-  <si>
-    <t>卡片月相跟真實月相的交互作用</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="3"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>真實月相是低權重時間情境修飾。</t>
-    </r>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>關係/模式</t>
-  </si>
-  <si>
-    <t>解釋/訊息</t>
-  </si>
-  <si>
-    <t>↑</t>
-  </si>
-  <si>
-    <t>正位</t>
-  </si>
-  <si>
-    <t>能量順行｜主題自然流動、力量顯現、外顯無礙</t>
-  </si>
-  <si>
-    <t>＋</t>
-  </si>
-  <si>
-    <t>半正位</t>
-  </si>
-  <si>
-    <t>初生漸顯｜潛能正在凝聚、尚未完全流動，代表準備與激活</t>
-  </si>
-  <si>
-    <t>—</t>
-  </si>
-  <si>
-    <t>半逆位</t>
-  </si>
-  <si>
-    <t>釋放收束｜能量正在退潮、進入整合期，是轉化與療癒階段</t>
-  </si>
-  <si>
-    <t>↓</t>
-  </si>
-  <si>
-    <t>逆位</t>
-  </si>
-  <si>
-    <t>能量阻滯｜主題反向顯現、力量扭曲、潛藏或危機感浮現</t>
-  </si>
-  <si>
-    <t>新月☉</t>
-  </si>
-  <si>
-    <t>正位（↑）</t>
-  </si>
-  <si>
-    <t>種子發芽</t>
-  </si>
-  <si>
-    <t>內在意圖與宇宙準備一致，適合啟動靜默中的創造</t>
-  </si>
-  <si>
-    <t>半正位（＋）</t>
-  </si>
-  <si>
-    <t>光尚未現</t>
-  </si>
-  <si>
-    <t>內在想動但時機未到，建議靜觀其變，等待契機</t>
-  </si>
-  <si>
-    <t>半逆位（—）</t>
-  </si>
-  <si>
-    <t>內潛釋放</t>
-  </si>
-  <si>
-    <t>正在釋放舊的創傷種子，是蛻變的準備期</t>
-  </si>
-  <si>
-    <t>逆位（↓）</t>
-  </si>
-  <si>
-    <t>種子阻塞</t>
-  </si>
-  <si>
-    <t>潛意識被壓抑，黑暗中難見光，需自我淨化與釋放</t>
-  </si>
-  <si>
-    <t>上弦△</t>
-  </si>
-  <si>
-    <t>行動之力</t>
-  </si>
-  <si>
-    <t>內外一致推進，適合主動出擊，逐步構建理想</t>
-  </si>
-  <si>
-    <t>焦躁之芽</t>
-  </si>
-  <si>
-    <t>內心躁動但實際力道尚不足，建議規劃而非急行</t>
-  </si>
-  <si>
-    <t>回收嘗試</t>
-  </si>
-  <si>
-    <t>曾嘗試某事未果，現在正在撤回與調整策略</t>
-  </si>
-  <si>
-    <t>阻斷行動</t>
-  </si>
-  <si>
-    <t>外力推動但你卻抗拒行動，可能因恐懼或拖延</t>
-  </si>
-  <si>
-    <t>滿月●</t>
-  </si>
-  <si>
-    <t>顯化高峰</t>
-  </si>
-  <si>
-    <t>內外完全共振，是展現、收穫與綻放的時刻</t>
-  </si>
-  <si>
-    <t>光中迷失</t>
-  </si>
-  <si>
-    <t>雖處高峰但焦點不明，可能能量過盛造成混亂</t>
-  </si>
-  <si>
-    <t>光後退場</t>
-  </si>
-  <si>
-    <t>繁盛之後開始退 潮，是總結與整合的契機</t>
-  </si>
-  <si>
-    <t>反射之光</t>
-  </si>
-  <si>
-    <t>事情表面光鮮但內裡不實，建議內觀真實感受</t>
-  </si>
-  <si>
-    <t>下弦▼</t>
-  </si>
-  <si>
-    <t>釋放清明</t>
-  </si>
-  <si>
-    <t>內在與宇宙都進入收束，適合整理與放下</t>
-  </si>
-  <si>
-    <t>整理未完</t>
-  </si>
-  <si>
-    <t>你開始整理但仍有執著，建議覺察仍卡住之處</t>
-  </si>
-  <si>
-    <t>釋放完成</t>
-  </si>
-  <si>
-    <t>你正好順勢放手，是準備迎接新週期的轉點</t>
-  </si>
-  <si>
-    <t>固執難釋</t>
-  </si>
-  <si>
-    <t>該放的未放，可能陷入重複舊模式的循環中</t>
-  </si>
-  <si>
-    <t>流暢合鳴</t>
-  </si>
-  <si>
-    <t>雙主題順行，宇宙與內在共振，是最強顯化組合之~</t>
-  </si>
-  <si>
-    <t>引導激活</t>
-  </si>
-  <si>
-    <t>你已行動，但另一主題尚待展現，是領導與帶動的結構</t>
-  </si>
-  <si>
-    <t>前行與整合</t>
-  </si>
-  <si>
-    <t>行動中帶有反思或療癒意味，是從創傷中推進的力量</t>
-  </si>
-  <si>
-    <t>前行與牽絆</t>
-  </si>
-  <si>
-    <t>你行進中卻被另一能量拉住，代表矛盾與修正功課</t>
-  </si>
-  <si>
-    <t>準備與照映</t>
-  </si>
-  <si>
-    <t>尚未動身的你，看見他人或外界已經啟動，是激勵與感應</t>
-  </si>
-  <si>
-    <t>潛能交疊</t>
-  </si>
-  <si>
-    <t>兩能量都在蓄勢待發，強烈暗示蘊含巨大突破可能</t>
-  </si>
-  <si>
-    <t>啟動回收交錯</t>
-  </si>
-  <si>
-    <t>有些還沒開始，有些已進入整合，是交叉能量場</t>
-  </si>
-  <si>
-    <t>內外緊張</t>
-  </si>
-  <si>
-    <t>準備階段受到阻力，需辨識內在恐懼或外在制約</t>
-  </si>
-  <si>
-    <t>內整外行</t>
-  </si>
-  <si>
-    <t>你已完成內在釋放，準備讓顯化能量帶動轉變</t>
-  </si>
-  <si>
-    <t>整合啟動序列</t>
-  </si>
-  <si>
-    <t>如同從療癒中走向重生，是自然節奏的過渡</t>
-  </si>
-  <si>
-    <t>雙向轉化</t>
-  </si>
-  <si>
-    <t>兩主題都在整合與釋放，為內在極佳的重建機會</t>
-  </si>
-  <si>
-    <t>殘餘影響</t>
-  </si>
-  <si>
-    <t>你已準備放手，但過往殘影仍在干擾，建議深層釋放</t>
-  </si>
-  <si>
-    <t>阻力轉化</t>
-  </si>
-  <si>
-    <t>你的陰影或課題正被顯化的能量反映出來，適合內觀</t>
-  </si>
-  <si>
-    <t>危機激化</t>
-  </si>
-  <si>
-    <t>混亂與潛能交錯，可能進入情緒／能量波動期</t>
-  </si>
-  <si>
-    <t>解構療癒</t>
-  </si>
-  <si>
-    <t>從混亂轉入療癒，代表自我解體與重組過程</t>
-  </si>
-  <si>
-    <t>雙重阻滯</t>
-  </si>
-  <si>
-    <t>兩個主題都處於逆流，建議停下腳步，進行深度清理</t>
-  </si>
-  <si>
-    <t>正</t>
-  </si>
-  <si>
-    <t>順行顯化</t>
-  </si>
-  <si>
-    <t>內外三位一致，強烈顯化循環，是展現與實現的命運契機</t>
-  </si>
-  <si>
-    <t>半正</t>
-  </si>
-  <si>
-    <t>穩定激活</t>
-  </si>
-  <si>
-    <t>行動穩定推進中，結果仍在醞釀與調整階段，提醒你保持耐心與信任。</t>
-  </si>
-  <si>
-    <t>半逆</t>
-  </si>
-  <si>
-    <t>尚未完成</t>
-  </si>
-  <si>
-    <t>內外一致但結尾偏弱，表示需要補強或延伸支持系統。</t>
-  </si>
-  <si>
-    <t>逆</t>
-  </si>
-  <si>
-    <t>明顯受阻</t>
-  </si>
-  <si>
-    <t>儘管起步順利，中後段力量突然斷裂，可能遭遇突發干擾或未察覺的內在抗拒。</t>
-  </si>
-  <si>
-    <t>領航共振</t>
-  </si>
-  <si>
-    <t>你已在穩定前行之路上，過程帶動他人或局勢逐步啟動，結果象徵良好回響與共振顯化。</t>
-  </si>
-  <si>
-    <t>漸進合流</t>
-  </si>
-  <si>
-    <t>穩定出發並正在推動變化，最終抵達一個尚未完全顯化但趨勢良好的節點，建議保持節奏。</t>
-  </si>
-  <si>
-    <t>外顯內縮</t>
-  </si>
-  <si>
-    <t>雖然整體能量持續展開，但結尾傾向收斂與整合，可能需要重新聚焦或調整方向。</t>
-  </si>
-  <si>
-    <t>外順內裂</t>
-  </si>
-  <si>
-    <t>起始順利並逐步啟動，但最終可能因忽略內在訊號或潛在隱憂而出現能量反轉。</t>
-  </si>
-  <si>
-    <t>前行整合</t>
-  </si>
-  <si>
-    <t>穩定出發後進入內在整合階段，最終重新對齊初衷，是帶有覺察與調整後的顯化。</t>
-  </si>
-  <si>
-    <t>穩中有伏</t>
-  </si>
-  <si>
-    <t>外在穩定推進，但過程內收、結果尚未完全打開，象徵能量正在重新聚焦，建議不急於顯現。</t>
-  </si>
-  <si>
-    <t>穩定退潮</t>
-  </si>
-  <si>
-    <t>起點穩固，但整體能量逐步收束，暗示你可能正在完成一段歷程或進入沉潛期。</t>
-  </si>
-  <si>
-    <t>外強內崩</t>
-  </si>
-  <si>
-    <t>雖然你以堅定姿態開始，但內在整合不穩，最終導致力量崩潰或情勢逆轉，需正視內在裂縫。</t>
-  </si>
-  <si>
-    <t>內斷外續</t>
-  </si>
-  <si>
-    <t>中段遭遇阻力但整體仍推進，提醒過程中需正視陰影課題。</t>
-  </si>
-  <si>
-    <t>穩中現憂</t>
-  </si>
-  <si>
-    <t>雖然最終看似可見轉機，但中途的反轉仍可能留下未處理的陰影或疑慮，需逐步釐清。</t>
-  </si>
-  <si>
-    <t>逆後整合</t>
-  </si>
-  <si>
-    <t>經歷中段挫折後進入能量收束，表示你開始試圖整理錯誤或修補破裂狀態。</t>
-  </si>
-  <si>
-    <t>反轉崩解</t>
-  </si>
-  <si>
-    <t>雖有良好起步，但命運之力遭遇劇烈反彈，情勢進一步惡化，需重新評估整體方向。</t>
-  </si>
-  <si>
-    <t>漸啟顯化</t>
-  </si>
-  <si>
-    <t>從醞釀走向實踐，最終達到完整顯化，是潛能被喚醒後的強力展現期。</t>
-  </si>
-  <si>
-    <t>引導未竟</t>
-  </si>
-  <si>
-    <t>雖有外力支持，但最終顯化尚不穩定，象徵你正被引領但還未全然開展。</t>
-  </si>
-  <si>
-    <t>力量反饋</t>
-  </si>
-  <si>
-    <t>實踐後產生回收效應，過程激烈但結尾進入反思與內在調整，需消化過多輸出。</t>
-  </si>
-  <si>
-    <t>承壓逆襲</t>
-  </si>
-  <si>
-    <t>外界壓力或主動行動過早啟動，導致結果無法承受能量負荷，最終產生逆轉或瓦解。</t>
-  </si>
-  <si>
-    <t>潛力爆發</t>
-  </si>
-  <si>
-    <t>雙重醞釀疊加後導致能量突破，是從靜默轉向顯現的關鍵躍進點。</t>
-  </si>
-  <si>
-    <t>穩定擴展</t>
-  </si>
-  <si>
-    <t>雖然進展不快，但穩定累積能量，整體狀態正在朝顯化前緩慢移動。</t>
-  </si>
-  <si>
-    <t>雙重內整</t>
-  </si>
-  <si>
-    <t>所有能量仍集中於內部醞釀與整合，顯示尚需時間消化轉變，不宜急行。</t>
-  </si>
-  <si>
-    <t>遲未轉化</t>
-  </si>
-  <si>
-    <t>醞釀過久而未能突破，能量卡滯導致反轉或錯失時機，需警惕停滯。</t>
-  </si>
-  <si>
-    <t>調和甦醒</t>
-  </si>
-  <si>
-    <t>初始潛能尚未展開，中段進入整合，最終由內而外重新對齊，是靜轉動的契機。</t>
-  </si>
-  <si>
-    <t>轉向萌動</t>
-  </si>
-  <si>
-    <t>你正在從內部調整過渡，能量逐步往外推展，象徵變化正在醞釀中。</t>
-  </si>
-  <si>
-    <t>靜能潛流</t>
-  </si>
-  <si>
-    <t>雙重內聚導致顯化遲緩，此時重點不在結果，而在內在建構與情緒沉澱。</t>
-  </si>
-  <si>
-    <t>未果回折</t>
-  </si>
-  <si>
-    <t>雖有起步之意，但能量過程無法外放，最終進入停滯或反向，提醒你重審動機與方法。</t>
-  </si>
-  <si>
-    <t>陰中返陽</t>
-  </si>
-  <si>
-    <t>儘管中段受阻，你仍可能轉化壓力為動力，結果迎來正面顯現，是逆勢中的突破之機。</t>
-  </si>
-  <si>
-    <t>調和未果</t>
-  </si>
-  <si>
-    <t>原本的行動被打斷，雖試圖重啟，但能量仍顯薄弱，結果顯示需更多支持與耐性。</t>
-  </si>
-  <si>
-    <t>崩後整理</t>
-  </si>
-  <si>
-    <t>結構中斷後進入內整期，此時不宜急行，而要關注殘餘能量與情緒的重新歸位。</t>
-  </si>
-  <si>
-    <t>錯失良機</t>
-  </si>
-  <si>
-    <t>醞釀之力未能及時展開，內外阻力接連出現，導致整體逆轉，提醒你勿忽略時機感。</t>
-  </si>
-  <si>
-    <t>內整外展</t>
-  </si>
-  <si>
-    <t>經歷內在整合後開始外顯推進，最終達成成果，是從療癒走向顯化的實踐循環。</t>
-  </si>
-  <si>
-    <t>穩定恢復</t>
-  </si>
-  <si>
-    <t>你已從整合期中重建力量，當下正處於逐步展現的過渡階段，能量趨穩但仍在累積。</t>
-  </si>
-  <si>
-    <t>收整停歇</t>
-  </si>
-  <si>
-    <t>行動後你選擇退後一步，讓自己沉澱與修復，代表一種主動的收束與守成。</t>
-  </si>
-  <si>
-    <t>明進暗退</t>
-  </si>
-  <si>
-    <t>雖曾推進但內在仍有未解之處，最終結果可能反轉，提示過程中忽略了潛藏的情緒或關鍵細節。</t>
-  </si>
-  <si>
-    <t>轉折開啟</t>
-  </si>
-  <si>
-    <t>從整理中緩步提昇，能量逐漸轉向顯現，是柔性的進展節奏。</t>
-  </si>
-  <si>
-    <t>緩步醞釀</t>
-  </si>
-  <si>
-    <t>雙方能量皆未完全展開，整體處於準備與醞釀交疊的狀態，需耐心等待時機成熟。</t>
-  </si>
-  <si>
-    <t>反覆沉整</t>
-  </si>
-  <si>
-    <t>正在進行多層整合，能量上下起伏，代表反覆調整與內在回應。</t>
-  </si>
-  <si>
-    <t>動念挫敗</t>
-  </si>
-  <si>
-    <t>雖有出發意願，但行動未全然落地，最終因干擾或動搖導致退卻與終止。</t>
-  </si>
-  <si>
-    <t>準備出擊</t>
-  </si>
-  <si>
-    <t>潛能尚未完全覺醒，過程穩定發酵，是蓄力期後即將啟動的關鍵轉點。</t>
-  </si>
-  <si>
-    <t>潛勢待發</t>
-  </si>
-  <si>
-    <t>能量仍聚於內部調和，雖有萌動之兆，仍需觀察並等待更明確的啟動信號。</t>
-  </si>
-  <si>
-    <t>內潛反芻</t>
-  </si>
-  <si>
-    <t>三重整合暗示深層轉化期，雖未見表面動靜，但內在運作劇烈，建議靜守蛻變。</t>
-  </si>
-  <si>
-    <t>能量斷裂</t>
-  </si>
-  <si>
-    <t>整合未竟便遭受打擊，代表潛勢尚未穩固就被外力或自我否定截斷，需謹慎。</t>
-  </si>
-  <si>
-    <t>錯線復明</t>
-  </si>
-  <si>
-    <t>雖經挫折與混亂，但仍可能在過程中覺醒新的方向，重返有序的顯化路徑。</t>
-  </si>
-  <si>
-    <t>漸返有序</t>
-  </si>
-  <si>
-    <t>從內部整合轉向混沌後，正在努力重組秩序，象徵你開始試圖恢復掌控權。</t>
-  </si>
-  <si>
-    <t>疲勞整合</t>
-  </si>
-  <si>
-    <t>消耗與混亂交錯之後進入內省與療癒，這是一段身心重整的過渡期。</t>
-  </si>
-  <si>
-    <t>崩解退場</t>
-  </si>
-  <si>
-    <t>雙重壓力導致崩潰結果，代表當前局勢已無法支撐，需要終止或徹底退出。</t>
-  </si>
-  <si>
-    <t>療癒轉化</t>
-  </si>
-  <si>
-    <t>開場困難但力量漸升，是從創傷中走向覺醒的重建模式。</t>
-  </si>
-  <si>
-    <t>轉穩待啟</t>
-  </si>
-  <si>
-    <t>雖然已突破逆境，但仍需穩定醞釀，象徵進入恢復後的積蓄期。</t>
-  </si>
-  <si>
-    <t>陰影整合</t>
-  </si>
-  <si>
-    <t>力量被重新召回後，你選擇內省與調整，代表逆境後的深層整合與修復。</t>
-  </si>
-  <si>
-    <t>復甦未果</t>
-  </si>
-  <si>
-    <t>即使中段有所突破，但整體仍未脫離阻力圈，結果顯示復甦尚未徹底成功。</t>
-  </si>
-  <si>
-    <t>援引突破</t>
-  </si>
-  <si>
-    <t>你正從低谷中回升，外部助力將協助你重建自信與行動，突破當前瓶頸。</t>
-  </si>
-  <si>
-    <t>修補進展</t>
-  </si>
-  <si>
-    <t>雖未徹底恢復，但正在接受支持與引導，能量慢慢流動，有機會逐步恢復動能。</t>
-  </si>
-  <si>
-    <t>半明半昧</t>
-  </si>
-  <si>
-    <t>你正處於陰影與希望交界，內心仍有波動，但整體趨勢向調整與收束前進。</t>
-  </si>
-  <si>
-    <t>激盪未解</t>
-  </si>
-  <si>
-    <t>嘗試修復但未見成效，內外矛盾依然存在，可能需要更長期的處理與覺察。</t>
-  </si>
-  <si>
-    <t>解構重生</t>
-  </si>
-  <si>
-    <t>雖從混亂中開始，但你選擇整合與釋放，最終將迎來更新的顯化，是重生的徵兆。</t>
-  </si>
-  <si>
-    <t>漸進修補</t>
-  </si>
-  <si>
-    <t>你正從崩裂狀態中恢復，雖未完全顯化，但新的希望正在醞釀。</t>
-  </si>
-  <si>
-    <t>殘餘清理</t>
-  </si>
-  <si>
-    <t>持續面對過去創傷與未解議題，是一段深度清掃與修復的時期。</t>
-  </si>
-  <si>
-    <t>影纏未散</t>
-  </si>
-  <si>
-    <t>雖努力整合但陰影仍未退散，顯示你尚未真正放下，循環可能重演。</t>
-  </si>
-  <si>
-    <t>阻中現光</t>
-  </si>
-  <si>
-    <t>即使歷經多重阻力，你仍可能由內而外產生突破，是暗處覓光之路。</t>
-  </si>
-  <si>
-    <t>破舊立新</t>
-  </si>
-  <si>
-    <t>雙重逆境促成覺醒的動力，代表你正在重新建立新的行動路線與心態。</t>
-  </si>
-  <si>
-    <t>清算回潮</t>
-  </si>
-  <si>
-    <t>累積的卡滯正在退潮，你逐漸回到整合狀態，是深層療癒期的後段。</t>
-  </si>
-  <si>
-    <t>兩個主題都處於逆流，建議停下腳步，進行深度清理與自我審視。</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>列於最後當小修正</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>天時關係所以可能稍強可能稍弱</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙卡特殊比重</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>風向是描述走向而不是解釋風的本質</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>不是兩者都有，是只有向之符文</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>日月當空屬明、清明屬辰</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>所有的時間範圍</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>錯過、不合時宜、遲到、延誤</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>天時</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>時期、階段、期間、所有時期特定名詞</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期、月份、時刻、曆、行事曆、日常</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>月光為暗、日月為時、月一個單字是星或時、日月當空屬明</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>日光為光、日月為時、日一個單字是星或時</t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
+  <si>
+    <t>星火為禍、明星沒有</t>
+    <phoneticPr fontId="19" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="34" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8145,20 +7566,6 @@
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="3"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -8170,6 +7577,14 @@
       <name val="新細明體"/>
       <family val="1"/>
       <charset val="136"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri Light"/>
+      <family val="3"/>
+      <charset val="136"/>
+      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="26">
@@ -9457,14 +8872,14 @@
     <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="372">
+  <cellXfs count="380">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -10033,138 +9448,15 @@
     </xf>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="11" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="39" xfId="11" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="14" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="39" xfId="12" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="39" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="20" borderId="16" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="0" xfId="12" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="20" borderId="39" xfId="12" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="14" xfId="13" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="39" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="16" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="0" xfId="13" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="39" xfId="13" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="13" xfId="13" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="11" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="78" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="29" fillId="21" borderId="11" xfId="13" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="2" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="6" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="12" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="3" xfId="14" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="36" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="36" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="42" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="44" xfId="14" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="40" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="23" borderId="45" xfId="14" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="2" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="2" xfId="15" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="37" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="41" xfId="15" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="3" xfId="15" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="36" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="36" xfId="15" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="42" xfId="15" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="42" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="4" xfId="15" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="38" xfId="15" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="38" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="24" borderId="43" xfId="15" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="14" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="6" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="80" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="36" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="42" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="40" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="40" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="19" borderId="45" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="81" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="2" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="37" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="41" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="4" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="38" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="38" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="43" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="25" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="82" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -10173,6 +9465,141 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="84" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="79" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="32" fillId="17" borderId="39" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="14" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="39" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="16" xfId="12" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="14" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="39" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="16" xfId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="13" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="11" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="78" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="36" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="42" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="37" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="41" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="36" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="42" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="38" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="43" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="36" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="42" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="40" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="40" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="45" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="2" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="37" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="41" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="44" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="40" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="40" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="45" xfId="17" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="37" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="41" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="38" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="43" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="37" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="41" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="38" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="38" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="43" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="37" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="41" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="36" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="42" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="38" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="43" xfId="4" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="2" xfId="14" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="3" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="4" xfId="14" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="2" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="3" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="4" xfId="15" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="14" xfId="16" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="80" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="81" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="18">
     <cellStyle name="20% - 輔色1" xfId="7"/>
@@ -13605,7 +13032,7 @@
         <v>1721</v>
       </c>
       <c r="I52" s="270" t="s">
-        <v>1761</v>
+        <v>1757</v>
       </c>
       <c r="J52" s="271" t="s">
         <v>1393</v>
@@ -13666,7 +13093,7 @@
         <v>11</v>
       </c>
       <c r="H54" s="277" t="s">
-        <v>1740</v>
+        <v>1737</v>
       </c>
       <c r="I54" s="270" t="s">
         <v>1329</v>
@@ -14135,29 +13562,29 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N22"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14" style="338" customWidth="1"/>
-    <col min="2" max="2" width="20.25" style="338" customWidth="1"/>
-    <col min="3" max="3" width="66" style="338" customWidth="1"/>
-    <col min="4" max="4" width="62.75" style="338" customWidth="1"/>
-    <col min="5" max="14" width="9" style="326"/>
-    <col min="15" max="16384" width="9" style="338"/>
+    <col min="1" max="1" width="14" style="315" customWidth="1"/>
+    <col min="2" max="2" width="20.25" style="315" customWidth="1"/>
+    <col min="3" max="3" width="64" style="315" customWidth="1"/>
+    <col min="4" max="4" width="62.75" style="315" customWidth="1"/>
+    <col min="5" max="14" width="9" style="313"/>
+    <col min="15" max="16384" width="9" style="315"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="307" customFormat="1" ht="24" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A1" s="304" t="s">
-        <v>1850</v>
-      </c>
-      <c r="B1" s="305" t="s">
-        <v>1851</v>
+        <v>1843</v>
+      </c>
+      <c r="B1" s="323" t="s">
+        <v>2084</v>
       </c>
       <c r="C1" s="305" t="s">
-        <v>1852</v>
+        <v>1844</v>
       </c>
       <c r="D1" s="305" t="s">
-        <v>1853</v>
+        <v>1845</v>
       </c>
       <c r="E1" s="306"/>
       <c r="F1" s="306"/>
@@ -14170,312 +13597,360 @@
       <c r="M1" s="306"/>
       <c r="N1" s="306"/>
     </row>
-    <row r="2" spans="1:14" s="313" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="308" t="s">
+    <row r="2" spans="1:14" s="309" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="324" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B2" s="325" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C2" s="325" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D2" s="326" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E2" s="308"/>
+      <c r="F2" s="308"/>
+      <c r="G2" s="308"/>
+      <c r="H2" s="308"/>
+      <c r="I2" s="308"/>
+      <c r="J2" s="308"/>
+      <c r="K2" s="308"/>
+      <c r="L2" s="308"/>
+      <c r="M2" s="308"/>
+      <c r="N2" s="308"/>
+    </row>
+    <row r="3" spans="1:14" s="311" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="327" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B3" s="328" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C3" s="328" t="s">
+        <v>1847</v>
+      </c>
+      <c r="D3" s="329" t="s">
+        <v>1848</v>
+      </c>
+      <c r="E3" s="310"/>
+      <c r="F3" s="310"/>
+      <c r="G3" s="310"/>
+      <c r="H3" s="310"/>
+      <c r="I3" s="310"/>
+      <c r="J3" s="310"/>
+      <c r="K3" s="310"/>
+      <c r="L3" s="310"/>
+      <c r="M3" s="310"/>
+      <c r="N3" s="310"/>
+    </row>
+    <row r="4" spans="1:14" s="312" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="330" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B4" s="331" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C4" s="331" t="s">
+        <v>1850</v>
+      </c>
+      <c r="D4" s="332" t="s">
+        <v>1851</v>
+      </c>
+      <c r="E4" s="310"/>
+      <c r="F4" s="310"/>
+      <c r="G4" s="310"/>
+      <c r="H4" s="310"/>
+      <c r="I4" s="310"/>
+      <c r="J4" s="310"/>
+      <c r="K4" s="310"/>
+      <c r="L4" s="310"/>
+      <c r="M4" s="310"/>
+      <c r="N4" s="310"/>
+    </row>
+    <row r="5" spans="1:14" s="313" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="371" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B5" s="353" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C5" s="353" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D5" s="354" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="313" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="372"/>
+      <c r="B6" s="333" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C6" s="333" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D6" s="334" t="s">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="313" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="372"/>
+      <c r="B7" s="333" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C7" s="333" t="s">
+        <v>2133</v>
+      </c>
+      <c r="D7" s="334" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="314" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="373"/>
+      <c r="B8" s="355" t="s">
+        <v>2105</v>
+      </c>
+      <c r="C8" s="355" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D8" s="356" t="s">
+        <v>2107</v>
+      </c>
+      <c r="E8" s="313"/>
+      <c r="F8" s="313"/>
+      <c r="G8" s="313"/>
+      <c r="H8" s="313"/>
+      <c r="I8" s="313"/>
+      <c r="J8" s="313"/>
+      <c r="K8" s="313"/>
+      <c r="L8" s="313"/>
+      <c r="M8" s="313"/>
+      <c r="N8" s="313"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="374" t="s">
+        <v>2108</v>
+      </c>
+      <c r="B9" s="335" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C9" s="335" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D9" s="336" t="s">
+        <v>2132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="375"/>
+      <c r="B10" s="337" t="s">
+        <v>2123</v>
+      </c>
+      <c r="C10" s="337" t="s">
+        <v>2124</v>
+      </c>
+      <c r="D10" s="338" t="s">
+        <v>2135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="375"/>
+      <c r="B11" s="337" t="s">
+        <v>2125</v>
+      </c>
+      <c r="C11" s="337" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D11" s="338" t="s">
+        <v>2136</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="375"/>
+      <c r="B12" s="337" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C12" s="337" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D12" s="338" t="s">
+        <v>2137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="375"/>
+      <c r="B13" s="337" t="s">
+        <v>2129</v>
+      </c>
+      <c r="C13" s="337" t="s">
+        <v>2138</v>
+      </c>
+      <c r="D13" s="338" t="s">
+        <v>2140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="375"/>
+      <c r="B14" s="337" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C14" s="337" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D14" s="338"/>
+    </row>
+    <row r="15" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="376"/>
+      <c r="B15" s="339" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C15" s="339" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D15" s="340" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="377" t="s">
         <v>1854</v>
       </c>
-      <c r="B2" s="309" t="s">
+      <c r="B16" s="357" t="s">
+        <v>2086</v>
+      </c>
+      <c r="C16" s="357" t="s">
+        <v>2109</v>
+      </c>
+      <c r="D16" s="358" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="378"/>
+      <c r="B17" s="341" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C17" s="341" t="s">
+        <v>2115</v>
+      </c>
+      <c r="D17" s="342" t="s">
+        <v>2119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="378"/>
+      <c r="B18" s="341" t="s">
+        <v>2111</v>
+      </c>
+      <c r="C18" s="341" t="s">
+        <v>2116</v>
+      </c>
+      <c r="D18" s="342" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="378"/>
+      <c r="B19" s="343" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C19" s="344" t="s">
+        <v>2117</v>
+      </c>
+      <c r="D19" s="345" t="s">
         <v>1855</v>
       </c>
-      <c r="C2" s="310" t="s">
+    </row>
+    <row r="20" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="379"/>
+      <c r="B20" s="359" t="s">
         <v>1856</v>
       </c>
-      <c r="D2" s="311" t="s">
+      <c r="C20" s="360" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D20" s="361" t="s">
         <v>1857</v>
       </c>
-      <c r="E2" s="312"/>
-      <c r="F2" s="312"/>
-      <c r="G2" s="312"/>
-      <c r="H2" s="312"/>
-      <c r="I2" s="312"/>
-      <c r="J2" s="312"/>
-      <c r="K2" s="312"/>
-      <c r="L2" s="312"/>
-      <c r="M2" s="312"/>
-      <c r="N2" s="312"/>
-    </row>
-    <row r="3" spans="1:14" s="318" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="314" t="s">
+    </row>
+    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="346" t="s">
+        <v>2113</v>
+      </c>
+      <c r="B21" s="347" t="s">
+        <v>1849</v>
+      </c>
+      <c r="C21" s="347" t="s">
         <v>1858</v>
       </c>
-      <c r="B3" s="315" t="s">
+      <c r="D21" s="348" t="s">
         <v>1859</v>
       </c>
-      <c r="C3" s="315" t="s">
+    </row>
+    <row r="22" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="349" t="s">
         <v>1860</v>
       </c>
-      <c r="D3" s="316" t="s">
+      <c r="B22" s="350" t="s">
         <v>1861</v>
       </c>
-      <c r="E3" s="317"/>
-      <c r="F3" s="317"/>
-      <c r="G3" s="317"/>
-      <c r="H3" s="317"/>
-      <c r="I3" s="317"/>
-      <c r="J3" s="317"/>
-      <c r="K3" s="317"/>
-      <c r="L3" s="317"/>
-      <c r="M3" s="317"/>
-      <c r="N3" s="317"/>
-    </row>
-    <row r="4" spans="1:14" s="322" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="319" t="s">
+      <c r="C22" s="351" t="s">
         <v>1862</v>
       </c>
-      <c r="B4" s="320" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C4" s="320" t="s">
-        <v>1864</v>
-      </c>
-      <c r="D4" s="321" t="s">
-        <v>1865</v>
-      </c>
-      <c r="E4" s="317"/>
-      <c r="F4" s="317"/>
-      <c r="G4" s="317"/>
-      <c r="H4" s="317"/>
-      <c r="I4" s="317"/>
-      <c r="J4" s="317"/>
-      <c r="K4" s="317"/>
-      <c r="L4" s="317"/>
-      <c r="M4" s="317"/>
-      <c r="N4" s="317"/>
-    </row>
-    <row r="5" spans="1:14" s="326" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="323" t="s">
-        <v>1866</v>
-      </c>
-      <c r="B5" s="324" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C5" s="324" t="s">
-        <v>1867</v>
-      </c>
-      <c r="D5" s="325" t="s">
-        <v>1868</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" s="326" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="327"/>
-      <c r="B6" s="328" t="s">
-        <v>1869</v>
-      </c>
-      <c r="C6" s="329" t="s">
-        <v>1870</v>
-      </c>
-      <c r="D6" s="330" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="326" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="327"/>
-      <c r="B7" s="328" t="s">
-        <v>1872</v>
-      </c>
-      <c r="C7" s="329" t="s">
-        <v>1873</v>
-      </c>
-      <c r="D7" s="330" t="s">
-        <v>1874</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" s="334" customFormat="1" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="331"/>
-      <c r="B8" s="332" t="s">
-        <v>1875</v>
-      </c>
-      <c r="C8" s="332" t="s">
-        <v>1876</v>
-      </c>
-      <c r="D8" s="333" t="s">
-        <v>1877</v>
-      </c>
-      <c r="E8" s="326"/>
-      <c r="F8" s="326"/>
-      <c r="G8" s="326"/>
-      <c r="H8" s="326"/>
-      <c r="I8" s="326"/>
-      <c r="J8" s="326"/>
-      <c r="K8" s="326"/>
-      <c r="L8" s="326"/>
-      <c r="M8" s="326"/>
-      <c r="N8" s="326"/>
-    </row>
-    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="335" t="s">
-        <v>1878</v>
-      </c>
-      <c r="B9" s="336" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C9" s="336" t="s">
-        <v>1879</v>
-      </c>
-      <c r="D9" s="337" t="s">
-        <v>1880</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="339"/>
-      <c r="B10" s="340" t="s">
-        <v>1881</v>
-      </c>
-      <c r="C10" s="341" t="s">
-        <v>1882</v>
-      </c>
-      <c r="D10" s="342" t="s">
-        <v>1883</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="339"/>
-      <c r="B11" s="340" t="s">
-        <v>1884</v>
-      </c>
-      <c r="C11" s="341" t="s">
-        <v>1885</v>
-      </c>
-      <c r="D11" s="342" t="s">
-        <v>1886</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="339"/>
-      <c r="B12" s="340" t="s">
-        <v>1887</v>
-      </c>
-      <c r="C12" s="341" t="s">
-        <v>1888</v>
-      </c>
-      <c r="D12" s="342" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="339"/>
-      <c r="B13" s="340" t="s">
-        <v>1890</v>
-      </c>
-      <c r="C13" s="341" t="s">
-        <v>1891</v>
-      </c>
-      <c r="D13" s="343" t="s">
-        <v>1892</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="339"/>
-      <c r="B14" s="340" t="s">
-        <v>1893</v>
-      </c>
-      <c r="C14" s="341" t="s">
-        <v>1894</v>
-      </c>
-      <c r="D14" s="343" t="s">
-        <v>1895</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="344"/>
-      <c r="B15" s="345" t="s">
-        <v>1896</v>
-      </c>
-      <c r="C15" s="346" t="s">
-        <v>1897</v>
-      </c>
-      <c r="D15" s="347" t="s">
-        <v>1898</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="348" t="s">
-        <v>1899</v>
-      </c>
-      <c r="B16" s="349" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C16" s="349" t="s">
-        <v>1900</v>
-      </c>
-      <c r="D16" s="350" t="s">
-        <v>1901</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="351"/>
-      <c r="B17" s="352" t="s">
-        <v>1902</v>
-      </c>
-      <c r="C17" s="352" t="s">
-        <v>1903</v>
-      </c>
-      <c r="D17" s="353" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="351"/>
-      <c r="B18" s="352" t="s">
-        <v>1905</v>
-      </c>
-      <c r="C18" s="352" t="s">
-        <v>1906</v>
-      </c>
-      <c r="D18" s="353" t="s">
-        <v>1907</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="351"/>
-      <c r="B19" s="354" t="s">
-        <v>1908</v>
-      </c>
-      <c r="C19" s="355" t="s">
-        <v>1909</v>
-      </c>
-      <c r="D19" s="356" t="s">
-        <v>1910</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="357"/>
-      <c r="B20" s="354" t="s">
-        <v>1911</v>
-      </c>
-      <c r="C20" s="355" t="s">
-        <v>1912</v>
-      </c>
-      <c r="D20" s="356" t="s">
-        <v>1913</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="358" t="s">
-        <v>1914</v>
-      </c>
-      <c r="B21" s="359" t="s">
-        <v>1863</v>
-      </c>
-      <c r="C21" s="359" t="s">
-        <v>1915</v>
-      </c>
-      <c r="D21" s="360" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="361" t="s">
-        <v>1917</v>
-      </c>
-      <c r="B22" s="362" t="s">
-        <v>1918</v>
-      </c>
-      <c r="C22" s="363" t="s">
-        <v>1919</v>
-      </c>
-      <c r="D22" s="364" t="s">
-        <v>1920</v>
+      <c r="D22" s="352" t="s">
+        <v>2114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="362" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B23" s="363" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C23" s="363" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D23" s="364" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="365"/>
+      <c r="B24" s="366" t="s">
+        <v>2091</v>
+      </c>
+      <c r="C24" s="366" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D24" s="367" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="368"/>
+      <c r="B25" s="369" t="s">
+        <v>2094</v>
+      </c>
+      <c r="C25" s="369" t="s">
+        <v>2095</v>
+      </c>
+      <c r="D25" s="370" t="s">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="368"/>
+      <c r="B26" s="369" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C26" s="369" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D26" s="370" t="s">
+        <v>2146</v>
       </c>
     </row>
   </sheetData>
@@ -14494,2238 +13969,2238 @@
   <dimension ref="A1:E185"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.375" style="338" customWidth="1"/>
-    <col min="2" max="2" width="13.875" style="338" customWidth="1"/>
-    <col min="3" max="3" width="11.75" style="338" customWidth="1"/>
-    <col min="4" max="4" width="12.625" style="338" customWidth="1"/>
-    <col min="5" max="5" width="96.875" style="338" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="338"/>
+    <col min="1" max="1" width="11.375" style="315" customWidth="1"/>
+    <col min="2" max="2" width="13.875" style="315" customWidth="1"/>
+    <col min="3" max="3" width="11.75" style="315" customWidth="1"/>
+    <col min="4" max="4" width="12.625" style="315" customWidth="1"/>
+    <col min="5" max="5" width="96.875" style="315" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="315"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="365" t="s">
+      <c r="A1" s="316" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B1" s="316" t="s">
+        <v>1864</v>
+      </c>
+      <c r="C1" s="316" t="s">
+        <v>1865</v>
+      </c>
+      <c r="D1" s="316" t="s">
+        <v>1866</v>
+      </c>
+      <c r="E1" s="316" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="317" t="s">
+        <v>1868</v>
+      </c>
+      <c r="B2" s="318"/>
+      <c r="C2" s="318"/>
+      <c r="D2" s="318" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E2" s="318" t="s">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="319" t="s">
+        <v>1871</v>
+      </c>
+      <c r="B3" s="320"/>
+      <c r="C3" s="320"/>
+      <c r="D3" s="320" t="s">
+        <v>1872</v>
+      </c>
+      <c r="E3" s="320" t="s">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="319" t="s">
+        <v>1874</v>
+      </c>
+      <c r="B4" s="320"/>
+      <c r="C4" s="320"/>
+      <c r="D4" s="320" t="s">
+        <v>1875</v>
+      </c>
+      <c r="E4" s="320" t="s">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="321" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B5" s="322"/>
+      <c r="C5" s="322"/>
+      <c r="D5" s="322" t="s">
+        <v>1878</v>
+      </c>
+      <c r="E5" s="322" t="s">
+        <v>1879</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="317" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B6" s="318" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C6" s="318"/>
+      <c r="D6" s="318" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E6" s="318" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="319" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B7" s="320" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C7" s="320"/>
+      <c r="D7" s="320" t="s">
+        <v>1885</v>
+      </c>
+      <c r="E7" s="320" t="s">
+        <v>1886</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="319" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B8" s="320" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C8" s="320"/>
+      <c r="D8" s="320" t="s">
+        <v>1888</v>
+      </c>
+      <c r="E8" s="320" t="s">
+        <v>1889</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="321" t="s">
+        <v>1880</v>
+      </c>
+      <c r="B9" s="322" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C9" s="322"/>
+      <c r="D9" s="322" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E9" s="322" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="317" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B10" s="318" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C10" s="318"/>
+      <c r="D10" s="318" t="s">
+        <v>1894</v>
+      </c>
+      <c r="E10" s="318" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="319" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B11" s="320" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C11" s="320"/>
+      <c r="D11" s="320" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E11" s="320" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="319" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B12" s="320" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C12" s="320"/>
+      <c r="D12" s="320" t="s">
+        <v>1898</v>
+      </c>
+      <c r="E12" s="320" t="s">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="321" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B13" s="322" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C13" s="322"/>
+      <c r="D13" s="322" t="s">
+        <v>1900</v>
+      </c>
+      <c r="E13" s="322" t="s">
+        <v>1901</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="317" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B14" s="318" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C14" s="318"/>
+      <c r="D14" s="318" t="s">
+        <v>1903</v>
+      </c>
+      <c r="E14" s="318" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="319" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B15" s="320" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C15" s="320"/>
+      <c r="D15" s="320" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E15" s="320" t="s">
+        <v>1906</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="319" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B16" s="320" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C16" s="320"/>
+      <c r="D16" s="320" t="s">
+        <v>1907</v>
+      </c>
+      <c r="E16" s="320" t="s">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="321" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B17" s="322" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C17" s="322"/>
+      <c r="D17" s="322" t="s">
+        <v>1909</v>
+      </c>
+      <c r="E17" s="322" t="s">
+        <v>1910</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="317" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B18" s="318" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C18" s="318"/>
+      <c r="D18" s="318" t="s">
+        <v>1912</v>
+      </c>
+      <c r="E18" s="318" t="s">
+        <v>1913</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="319" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B19" s="320" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C19" s="320"/>
+      <c r="D19" s="320" t="s">
+        <v>1914</v>
+      </c>
+      <c r="E19" s="320" t="s">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="319" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B20" s="320" t="s">
+        <v>1887</v>
+      </c>
+      <c r="C20" s="320"/>
+      <c r="D20" s="320" t="s">
+        <v>1916</v>
+      </c>
+      <c r="E20" s="320" t="s">
+        <v>1917</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="321" t="s">
+        <v>1911</v>
+      </c>
+      <c r="B21" s="322" t="s">
+        <v>1890</v>
+      </c>
+      <c r="C21" s="322"/>
+      <c r="D21" s="322" t="s">
+        <v>1918</v>
+      </c>
+      <c r="E21" s="322" t="s">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="317" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B22" s="318" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C22" s="318"/>
+      <c r="D22" s="318" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E22" s="318" t="s">
         <v>1921</v>
       </c>
-      <c r="B1" s="365" t="s">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="319" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B23" s="320" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C23" s="320"/>
+      <c r="D23" s="320" t="s">
         <v>1922</v>
       </c>
-      <c r="C1" s="365" t="s">
+      <c r="E23" s="320" t="s">
         <v>1923</v>
       </c>
-      <c r="D1" s="365" t="s">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="319" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B24" s="320" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C24" s="320"/>
+      <c r="D24" s="320" t="s">
         <v>1924</v>
       </c>
-      <c r="E1" s="365" t="s">
+      <c r="E24" s="320" t="s">
         <v>1925</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="366" t="s">
+    <row r="25" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="321" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B25" s="322" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C25" s="322"/>
+      <c r="D25" s="322" t="s">
         <v>1926</v>
       </c>
-      <c r="B2" s="367"/>
-      <c r="C2" s="367"/>
-      <c r="D2" s="367" t="s">
+      <c r="E25" s="322" t="s">
         <v>1927</v>
       </c>
-      <c r="E2" s="367" t="s">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="317" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B26" s="318" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C26" s="318"/>
+      <c r="D26" s="318" t="s">
         <v>1928</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="368" t="s">
+      <c r="E26" s="318" t="s">
         <v>1929</v>
       </c>
-      <c r="B3" s="369"/>
-      <c r="C3" s="369"/>
-      <c r="D3" s="369" t="s">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="319" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B27" s="320" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C27" s="320"/>
+      <c r="D27" s="320" t="s">
         <v>1930</v>
       </c>
-      <c r="E3" s="369" t="s">
+      <c r="E27" s="320" t="s">
         <v>1931</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="368" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="319" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B28" s="320" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C28" s="320"/>
+      <c r="D28" s="320" t="s">
         <v>1932</v>
       </c>
-      <c r="B4" s="369"/>
-      <c r="C4" s="369"/>
-      <c r="D4" s="369" t="s">
+      <c r="E28" s="320" t="s">
         <v>1933</v>
       </c>
-      <c r="E4" s="369" t="s">
+    </row>
+    <row r="29" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="321" t="s">
+        <v>1872</v>
+      </c>
+      <c r="B29" s="322" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C29" s="322"/>
+      <c r="D29" s="322" t="s">
         <v>1934</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="370" t="s">
+      <c r="E29" s="322" t="s">
         <v>1935</v>
       </c>
-      <c r="B5" s="371"/>
-      <c r="C5" s="371"/>
-      <c r="D5" s="371" t="s">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="317" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B30" s="318" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C30" s="318"/>
+      <c r="D30" s="318" t="s">
         <v>1936</v>
       </c>
-      <c r="E5" s="371" t="s">
+      <c r="E30" s="318" t="s">
         <v>1937</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="366" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="319" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B31" s="320" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C31" s="320"/>
+      <c r="D31" s="320" t="s">
         <v>1938</v>
       </c>
-      <c r="B6" s="367" t="s">
+      <c r="E31" s="320" t="s">
         <v>1939</v>
       </c>
-      <c r="C6" s="367"/>
-      <c r="D6" s="367" t="s">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="319" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B32" s="320" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C32" s="320"/>
+      <c r="D32" s="320" t="s">
         <v>1940</v>
       </c>
-      <c r="E6" s="367" t="s">
+      <c r="E32" s="320" t="s">
         <v>1941</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="368" t="s">
-        <v>1938</v>
-      </c>
-      <c r="B7" s="369" t="s">
+    <row r="33" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="321" t="s">
+        <v>1875</v>
+      </c>
+      <c r="B33" s="322" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C33" s="322"/>
+      <c r="D33" s="322" t="s">
         <v>1942</v>
       </c>
-      <c r="C7" s="369"/>
-      <c r="D7" s="369" t="s">
+      <c r="E33" s="322" t="s">
         <v>1943</v>
       </c>
-      <c r="E7" s="369" t="s">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="317" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B34" s="318" t="s">
+        <v>1869</v>
+      </c>
+      <c r="C34" s="318"/>
+      <c r="D34" s="318" t="s">
         <v>1944</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="368" t="s">
-        <v>1938</v>
-      </c>
-      <c r="B8" s="369" t="s">
+      <c r="E34" s="318" t="s">
         <v>1945</v>
       </c>
-      <c r="C8" s="369"/>
-      <c r="D8" s="369" t="s">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="319" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B35" s="320" t="s">
+        <v>1872</v>
+      </c>
+      <c r="C35" s="320"/>
+      <c r="D35" s="320" t="s">
         <v>1946</v>
       </c>
-      <c r="E8" s="369" t="s">
+      <c r="E35" s="320" t="s">
         <v>1947</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="370" t="s">
-        <v>1938</v>
-      </c>
-      <c r="B9" s="371" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="319" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B36" s="320" t="s">
+        <v>1875</v>
+      </c>
+      <c r="C36" s="320"/>
+      <c r="D36" s="320" t="s">
         <v>1948</v>
       </c>
-      <c r="C9" s="371"/>
-      <c r="D9" s="371" t="s">
+      <c r="E36" s="320" t="s">
         <v>1949</v>
       </c>
-      <c r="E9" s="371" t="s">
+    </row>
+    <row r="37" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="321" t="s">
+        <v>1878</v>
+      </c>
+      <c r="B37" s="322" t="s">
+        <v>1878</v>
+      </c>
+      <c r="C37" s="322"/>
+      <c r="D37" s="322" t="s">
         <v>1950</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="366" t="s">
+      <c r="E37" s="322" t="s">
         <v>1951</v>
       </c>
-      <c r="B10" s="367" t="s">
-        <v>1939</v>
-      </c>
-      <c r="C10" s="367"/>
-      <c r="D10" s="367" t="s">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="317" t="s">
         <v>1952</v>
       </c>
-      <c r="E10" s="367" t="s">
+      <c r="B38" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C38" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D38" s="318" t="s">
         <v>1953</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="368" t="s">
-        <v>1951</v>
-      </c>
-      <c r="B11" s="369" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C11" s="369"/>
-      <c r="D11" s="369" t="s">
+      <c r="E38" s="318" t="s">
         <v>1954</v>
       </c>
-      <c r="E11" s="369" t="s">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B39" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C39" s="320" t="s">
         <v>1955</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="368" t="s">
-        <v>1951</v>
-      </c>
-      <c r="B12" s="369" t="s">
-        <v>1945</v>
-      </c>
-      <c r="C12" s="369"/>
-      <c r="D12" s="369" t="s">
+      <c r="D39" s="320" t="s">
         <v>1956</v>
       </c>
-      <c r="E12" s="369" t="s">
+      <c r="E39" s="320" t="s">
         <v>1957</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="370" t="s">
-        <v>1951</v>
-      </c>
-      <c r="B13" s="371" t="s">
-        <v>1948</v>
-      </c>
-      <c r="C13" s="371"/>
-      <c r="D13" s="371" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B40" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C40" s="320" t="s">
         <v>1958</v>
       </c>
-      <c r="E13" s="371" t="s">
+      <c r="D40" s="320" t="s">
         <v>1959</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="366" t="s">
+      <c r="E40" s="320" t="s">
         <v>1960</v>
       </c>
-      <c r="B14" s="367" t="s">
-        <v>1939</v>
-      </c>
-      <c r="C14" s="367"/>
-      <c r="D14" s="367" t="s">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B41" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C41" s="320" t="s">
         <v>1961</v>
       </c>
-      <c r="E14" s="367" t="s">
+      <c r="D41" s="320" t="s">
         <v>1962</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="368" t="s">
-        <v>1960</v>
-      </c>
-      <c r="B15" s="369" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C15" s="369"/>
-      <c r="D15" s="369" t="s">
+      <c r="E41" s="320" t="s">
         <v>1963</v>
       </c>
-      <c r="E15" s="369" t="s">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B42" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C42" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D42" s="320" t="s">
         <v>1964</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="368" t="s">
-        <v>1960</v>
-      </c>
-      <c r="B16" s="369" t="s">
-        <v>1945</v>
-      </c>
-      <c r="C16" s="369"/>
-      <c r="D16" s="369" t="s">
+      <c r="E42" s="320" t="s">
         <v>1965</v>
       </c>
-      <c r="E16" s="369" t="s">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B43" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C43" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D43" s="320" t="s">
         <v>1966</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="370" t="s">
-        <v>1960</v>
-      </c>
-      <c r="B17" s="371" t="s">
-        <v>1948</v>
-      </c>
-      <c r="C17" s="371"/>
-      <c r="D17" s="371" t="s">
+      <c r="E43" s="320" t="s">
         <v>1967</v>
       </c>
-      <c r="E17" s="371" t="s">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B44" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C44" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D44" s="320" t="s">
         <v>1968</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="366" t="s">
+      <c r="E44" s="320" t="s">
         <v>1969</v>
       </c>
-      <c r="B18" s="367" t="s">
-        <v>1939</v>
-      </c>
-      <c r="C18" s="367"/>
-      <c r="D18" s="367" t="s">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B45" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C45" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D45" s="320" t="s">
         <v>1970</v>
       </c>
-      <c r="E18" s="367" t="s">
+      <c r="E45" s="320" t="s">
         <v>1971</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="368" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B19" s="369" t="s">
-        <v>1942</v>
-      </c>
-      <c r="C19" s="369"/>
-      <c r="D19" s="369" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B46" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C46" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D46" s="320" t="s">
         <v>1972</v>
       </c>
-      <c r="E19" s="369" t="s">
+      <c r="E46" s="320" t="s">
         <v>1973</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="368" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B20" s="369" t="s">
-        <v>1945</v>
-      </c>
-      <c r="C20" s="369"/>
-      <c r="D20" s="369" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B47" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C47" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D47" s="320" t="s">
         <v>1974</v>
       </c>
-      <c r="E20" s="369" t="s">
+      <c r="E47" s="320" t="s">
         <v>1975</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="370" t="s">
-        <v>1969</v>
-      </c>
-      <c r="B21" s="371" t="s">
-        <v>1948</v>
-      </c>
-      <c r="C21" s="371"/>
-      <c r="D21" s="371" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B48" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C48" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D48" s="320" t="s">
         <v>1976</v>
       </c>
-      <c r="E21" s="371" t="s">
+      <c r="E48" s="320" t="s">
         <v>1977</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="366" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B22" s="367" t="s">
-        <v>1927</v>
-      </c>
-      <c r="C22" s="367"/>
-      <c r="D22" s="367" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B49" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C49" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D49" s="320" t="s">
         <v>1978</v>
       </c>
-      <c r="E22" s="367" t="s">
+      <c r="E49" s="320" t="s">
         <v>1979</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="368" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B23" s="369" t="s">
-        <v>1930</v>
-      </c>
-      <c r="C23" s="369"/>
-      <c r="D23" s="369" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B50" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C50" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D50" s="320" t="s">
         <v>1980</v>
       </c>
-      <c r="E23" s="369" t="s">
+      <c r="E50" s="320" t="s">
         <v>1981</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="368" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B24" s="369" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C24" s="369"/>
-      <c r="D24" s="369" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B51" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C51" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D51" s="320" t="s">
         <v>1982</v>
       </c>
-      <c r="E24" s="369" t="s">
+      <c r="E51" s="320" t="s">
         <v>1983</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="370" t="s">
-        <v>1927</v>
-      </c>
-      <c r="B25" s="371" t="s">
-        <v>1936</v>
-      </c>
-      <c r="C25" s="371"/>
-      <c r="D25" s="371" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="319" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B52" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C52" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D52" s="320" t="s">
         <v>1984</v>
       </c>
-      <c r="E25" s="371" t="s">
+      <c r="E52" s="320" t="s">
         <v>1985</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="366" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B26" s="367" t="s">
-        <v>1927</v>
-      </c>
-      <c r="C26" s="367"/>
-      <c r="D26" s="367" t="s">
+    <row r="53" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="321" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B53" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C53" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D53" s="322" t="s">
         <v>1986</v>
       </c>
-      <c r="E26" s="367" t="s">
+      <c r="E53" s="322" t="s">
         <v>1987</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="368" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B27" s="369" t="s">
-        <v>1930</v>
-      </c>
-      <c r="C27" s="369"/>
-      <c r="D27" s="369" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="317" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B54" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C54" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D54" s="318" t="s">
         <v>1988</v>
       </c>
-      <c r="E27" s="369" t="s">
+      <c r="E54" s="318" t="s">
         <v>1989</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="368" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B28" s="369" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C28" s="369"/>
-      <c r="D28" s="369" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B55" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C55" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D55" s="320" t="s">
         <v>1990</v>
       </c>
-      <c r="E28" s="369" t="s">
+      <c r="E55" s="320" t="s">
         <v>1991</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="370" t="s">
-        <v>1930</v>
-      </c>
-      <c r="B29" s="371" t="s">
-        <v>1936</v>
-      </c>
-      <c r="C29" s="371"/>
-      <c r="D29" s="371" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B56" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C56" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D56" s="320" t="s">
         <v>1992</v>
       </c>
-      <c r="E29" s="371" t="s">
+      <c r="E56" s="320" t="s">
         <v>1993</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="366" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B30" s="367" t="s">
-        <v>1927</v>
-      </c>
-      <c r="C30" s="367"/>
-      <c r="D30" s="367" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B57" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C57" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D57" s="320" t="s">
         <v>1994</v>
       </c>
-      <c r="E30" s="367" t="s">
+      <c r="E57" s="320" t="s">
         <v>1995</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="368" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B31" s="369" t="s">
-        <v>1930</v>
-      </c>
-      <c r="C31" s="369"/>
-      <c r="D31" s="369" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B58" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C58" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D58" s="320" t="s">
         <v>1996</v>
       </c>
-      <c r="E31" s="369" t="s">
+      <c r="E58" s="320" t="s">
         <v>1997</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="368" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B32" s="369" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C32" s="369"/>
-      <c r="D32" s="369" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B59" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C59" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D59" s="320" t="s">
         <v>1998</v>
       </c>
-      <c r="E32" s="369" t="s">
+      <c r="E59" s="320" t="s">
         <v>1999</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="370" t="s">
-        <v>1933</v>
-      </c>
-      <c r="B33" s="371" t="s">
-        <v>1936</v>
-      </c>
-      <c r="C33" s="371"/>
-      <c r="D33" s="371" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B60" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C60" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D60" s="320" t="s">
         <v>2000</v>
       </c>
-      <c r="E33" s="371" t="s">
+      <c r="E60" s="320" t="s">
         <v>2001</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="366" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B34" s="367" t="s">
-        <v>1927</v>
-      </c>
-      <c r="C34" s="367"/>
-      <c r="D34" s="367" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B61" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C61" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D61" s="320" t="s">
         <v>2002</v>
       </c>
-      <c r="E34" s="367" t="s">
+      <c r="E61" s="320" t="s">
         <v>2003</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="368" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B35" s="369" t="s">
-        <v>1930</v>
-      </c>
-      <c r="C35" s="369"/>
-      <c r="D35" s="369" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B62" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C62" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D62" s="320" t="s">
         <v>2004</v>
       </c>
-      <c r="E35" s="369" t="s">
+      <c r="E62" s="320" t="s">
         <v>2005</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="368" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B36" s="369" t="s">
-        <v>1933</v>
-      </c>
-      <c r="C36" s="369"/>
-      <c r="D36" s="369" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B63" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C63" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D63" s="320" t="s">
         <v>2006</v>
       </c>
-      <c r="E36" s="369" t="s">
+      <c r="E63" s="320" t="s">
         <v>2007</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="370" t="s">
-        <v>1936</v>
-      </c>
-      <c r="B37" s="371" t="s">
-        <v>1936</v>
-      </c>
-      <c r="C37" s="371"/>
-      <c r="D37" s="371" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B64" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C64" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D64" s="320" t="s">
         <v>2008</v>
       </c>
-      <c r="E37" s="371" t="s">
+      <c r="E64" s="320" t="s">
         <v>2009</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="366" t="s">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B65" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C65" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D65" s="320" t="s">
         <v>2010</v>
       </c>
-      <c r="B38" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C38" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D38" s="367" t="s">
+      <c r="E65" s="320" t="s">
         <v>2011</v>
       </c>
-      <c r="E38" s="367" t="s">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B66" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C66" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D66" s="320" t="s">
         <v>2012</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B39" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C39" s="369" t="s">
+      <c r="E66" s="320" t="s">
         <v>2013</v>
       </c>
-      <c r="D39" s="369" t="s">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B67" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C67" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D67" s="320" t="s">
         <v>2014</v>
       </c>
-      <c r="E39" s="369" t="s">
+      <c r="E67" s="320" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B40" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C40" s="369" t="s">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68" s="319" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B68" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C68" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D68" s="320" t="s">
         <v>2016</v>
       </c>
-      <c r="D40" s="369" t="s">
+      <c r="E68" s="320" t="s">
         <v>2017</v>
       </c>
-      <c r="E40" s="369" t="s">
+    </row>
+    <row r="69" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="321" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B69" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C69" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D69" s="322" t="s">
         <v>2018</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B41" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C41" s="369" t="s">
+      <c r="E69" s="322" t="s">
         <v>2019</v>
       </c>
-      <c r="D41" s="369" t="s">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70" s="317" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B70" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C70" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D70" s="318" t="s">
         <v>2020</v>
       </c>
-      <c r="E41" s="369" t="s">
+      <c r="E70" s="318" t="s">
         <v>2021</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B42" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C42" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D42" s="369" t="s">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B71" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C71" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D71" s="320" t="s">
         <v>2022</v>
       </c>
-      <c r="E42" s="369" t="s">
+      <c r="E71" s="320" t="s">
         <v>2023</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B43" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C43" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D43" s="369" t="s">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B72" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C72" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D72" s="320" t="s">
         <v>2024</v>
       </c>
-      <c r="E43" s="369" t="s">
+      <c r="E72" s="320" t="s">
         <v>2025</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B44" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C44" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D44" s="369" t="s">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B73" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C73" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D73" s="320" t="s">
         <v>2026</v>
       </c>
-      <c r="E44" s="369" t="s">
+      <c r="E73" s="320" t="s">
         <v>2027</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B45" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C45" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D45" s="369" t="s">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B74" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C74" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D74" s="320" t="s">
         <v>2028</v>
       </c>
-      <c r="E45" s="369" t="s">
+      <c r="E74" s="320" t="s">
         <v>2029</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B46" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C46" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D46" s="369" t="s">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B75" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C75" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D75" s="320" t="s">
         <v>2030</v>
       </c>
-      <c r="E46" s="369" t="s">
+      <c r="E75" s="320" t="s">
         <v>2031</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B47" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C47" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D47" s="369" t="s">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B76" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C76" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D76" s="320" t="s">
         <v>2032</v>
       </c>
-      <c r="E47" s="369" t="s">
+      <c r="E76" s="320" t="s">
         <v>2033</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B48" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C48" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D48" s="369" t="s">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B77" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C77" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D77" s="320" t="s">
         <v>2034</v>
       </c>
-      <c r="E48" s="369" t="s">
+      <c r="E77" s="320" t="s">
         <v>2035</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B49" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C49" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D49" s="369" t="s">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B78" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C78" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D78" s="320" t="s">
         <v>2036</v>
       </c>
-      <c r="E49" s="369" t="s">
+      <c r="E78" s="320" t="s">
         <v>2037</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B50" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C50" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D50" s="369" t="s">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B79" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C79" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D79" s="320" t="s">
         <v>2038</v>
       </c>
-      <c r="E50" s="369" t="s">
+      <c r="E79" s="320" t="s">
         <v>2039</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B51" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C51" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D51" s="369" t="s">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B80" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C80" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D80" s="320" t="s">
         <v>2040</v>
       </c>
-      <c r="E51" s="369" t="s">
+      <c r="E80" s="320" t="s">
         <v>2041</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" s="368" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B52" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C52" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D52" s="369" t="s">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B81" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C81" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D81" s="320" t="s">
         <v>2042</v>
       </c>
-      <c r="E52" s="369" t="s">
+      <c r="E81" s="320" t="s">
         <v>2043</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="370" t="s">
-        <v>2010</v>
-      </c>
-      <c r="B53" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C53" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D53" s="371" t="s">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B82" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C82" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D82" s="320" t="s">
         <v>2044</v>
       </c>
-      <c r="E53" s="371" t="s">
+      <c r="E82" s="320" t="s">
         <v>2045</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A54" s="366" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B54" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C54" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D54" s="367" t="s">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B83" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C83" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D83" s="320" t="s">
         <v>2046</v>
       </c>
-      <c r="E54" s="367" t="s">
+      <c r="E83" s="320" t="s">
         <v>2047</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B55" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C55" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D55" s="369" t="s">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84" s="319" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B84" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C84" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D84" s="320" t="s">
         <v>2048</v>
       </c>
-      <c r="E55" s="369" t="s">
+      <c r="E84" s="320" t="s">
         <v>2049</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B56" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C56" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D56" s="369" t="s">
+    <row r="85" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="321" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B85" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C85" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D85" s="322" t="s">
         <v>2050</v>
       </c>
-      <c r="E56" s="369" t="s">
+      <c r="E85" s="322" t="s">
         <v>2051</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B57" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C57" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D57" s="369" t="s">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86" s="317" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B86" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C86" s="318" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D86" s="318" t="s">
         <v>2052</v>
       </c>
-      <c r="E57" s="369" t="s">
+      <c r="E86" s="318" t="s">
         <v>2053</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B58" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C58" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D58" s="369" t="s">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B87" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C87" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D87" s="320" t="s">
         <v>2054</v>
       </c>
-      <c r="E58" s="369" t="s">
+      <c r="E87" s="320" t="s">
         <v>2055</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B59" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C59" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D59" s="369" t="s">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B88" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C88" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D88" s="320" t="s">
         <v>2056</v>
       </c>
-      <c r="E59" s="369" t="s">
+      <c r="E88" s="320" t="s">
         <v>2057</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B60" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C60" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D60" s="369" t="s">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B89" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C89" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D89" s="320" t="s">
         <v>2058</v>
       </c>
-      <c r="E60" s="369" t="s">
+      <c r="E89" s="320" t="s">
         <v>2059</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B61" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C61" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D61" s="369" t="s">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B90" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C90" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D90" s="320" t="s">
         <v>2060</v>
       </c>
-      <c r="E61" s="369" t="s">
+      <c r="E90" s="320" t="s">
         <v>2061</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B62" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C62" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D62" s="369" t="s">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B91" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C91" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D91" s="320" t="s">
         <v>2062</v>
       </c>
-      <c r="E62" s="369" t="s">
+      <c r="E91" s="320" t="s">
         <v>2063</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B63" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C63" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D63" s="369" t="s">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B92" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C92" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D92" s="320" t="s">
         <v>2064</v>
       </c>
-      <c r="E63" s="369" t="s">
+      <c r="E92" s="320" t="s">
         <v>2065</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B64" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C64" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D64" s="369" t="s">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B93" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C93" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D93" s="320" t="s">
         <v>2066</v>
       </c>
-      <c r="E64" s="369" t="s">
+      <c r="E93" s="320" t="s">
         <v>2067</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A65" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B65" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C65" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D65" s="369" t="s">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B94" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C94" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D94" s="320" t="s">
         <v>2068</v>
       </c>
-      <c r="E65" s="369" t="s">
+      <c r="E94" s="320" t="s">
         <v>2069</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A66" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B66" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C66" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D66" s="369" t="s">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B95" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C95" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D95" s="320" t="s">
         <v>2070</v>
       </c>
-      <c r="E66" s="369" t="s">
+      <c r="E95" s="320" t="s">
         <v>2071</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B67" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C67" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D67" s="369" t="s">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B96" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C96" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D96" s="320" t="s">
         <v>2072</v>
       </c>
-      <c r="E67" s="369" t="s">
+      <c r="E96" s="320" t="s">
         <v>2073</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="368" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B68" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C68" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D68" s="369" t="s">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B97" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C97" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D97" s="320" t="s">
         <v>2074</v>
       </c>
-      <c r="E68" s="369" t="s">
+      <c r="E97" s="320" t="s">
         <v>2075</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="370" t="s">
-        <v>2013</v>
-      </c>
-      <c r="B69" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C69" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D69" s="371" t="s">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B98" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C98" s="320" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D98" s="320" t="s">
         <v>2076</v>
       </c>
-      <c r="E69" s="371" t="s">
+      <c r="E98" s="320" t="s">
         <v>2077</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" s="366" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B70" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C70" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D70" s="367" t="s">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B99" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C99" s="320" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D99" s="320" t="s">
         <v>2078</v>
       </c>
-      <c r="E70" s="367" t="s">
+      <c r="E99" s="320" t="s">
         <v>2079</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B71" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C71" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D71" s="369" t="s">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100" s="319" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B100" s="320" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C100" s="320" t="s">
+        <v>1958</v>
+      </c>
+      <c r="D100" s="320" t="s">
         <v>2080</v>
       </c>
-      <c r="E71" s="369" t="s">
+      <c r="E100" s="320" t="s">
         <v>2081</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A72" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B72" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C72" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D72" s="369" t="s">
+    <row r="101" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="321" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B101" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="C101" s="322" t="s">
+        <v>1961</v>
+      </c>
+      <c r="D101" s="322" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E101" s="322" t="s">
         <v>2082</v>
       </c>
-      <c r="E72" s="369" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B73" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C73" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D73" s="369" t="s">
-        <v>2084</v>
-      </c>
-      <c r="E73" s="369" t="s">
-        <v>2085</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A74" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B74" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C74" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D74" s="369" t="s">
-        <v>2086</v>
-      </c>
-      <c r="E74" s="369" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B75" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C75" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D75" s="369" t="s">
-        <v>2088</v>
-      </c>
-      <c r="E75" s="369" t="s">
-        <v>2089</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B76" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C76" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D76" s="369" t="s">
-        <v>2090</v>
-      </c>
-      <c r="E76" s="369" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A77" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B77" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C77" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D77" s="369" t="s">
-        <v>2092</v>
-      </c>
-      <c r="E77" s="369" t="s">
-        <v>2093</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A78" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B78" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C78" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D78" s="369" t="s">
-        <v>2094</v>
-      </c>
-      <c r="E78" s="369" t="s">
-        <v>2095</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A79" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B79" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C79" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D79" s="369" t="s">
-        <v>2096</v>
-      </c>
-      <c r="E79" s="369" t="s">
-        <v>2097</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A80" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B80" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C80" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D80" s="369" t="s">
-        <v>2098</v>
-      </c>
-      <c r="E80" s="369" t="s">
-        <v>2099</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B81" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C81" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D81" s="369" t="s">
-        <v>2100</v>
-      </c>
-      <c r="E81" s="369" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B82" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C82" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D82" s="369" t="s">
-        <v>2102</v>
-      </c>
-      <c r="E82" s="369" t="s">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A83" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B83" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C83" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D83" s="369" t="s">
-        <v>2104</v>
-      </c>
-      <c r="E83" s="369" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="368" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B84" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C84" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D84" s="369" t="s">
-        <v>2106</v>
-      </c>
-      <c r="E84" s="369" t="s">
-        <v>2107</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="370" t="s">
-        <v>2016</v>
-      </c>
-      <c r="B85" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C85" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D85" s="371" t="s">
-        <v>2108</v>
-      </c>
-      <c r="E85" s="371" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A86" s="366" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B86" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C86" s="367" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D86" s="367" t="s">
-        <v>2110</v>
-      </c>
-      <c r="E86" s="367" t="s">
-        <v>2111</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A87" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B87" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C87" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D87" s="369" t="s">
-        <v>2112</v>
-      </c>
-      <c r="E87" s="369" t="s">
-        <v>2113</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A88" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B88" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C88" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D88" s="369" t="s">
-        <v>2114</v>
-      </c>
-      <c r="E88" s="369" t="s">
-        <v>2115</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A89" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B89" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="C89" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D89" s="369" t="s">
-        <v>2116</v>
-      </c>
-      <c r="E89" s="369" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A90" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B90" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C90" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D90" s="369" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E90" s="369" t="s">
-        <v>2119</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A91" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B91" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C91" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D91" s="369" t="s">
-        <v>2120</v>
-      </c>
-      <c r="E91" s="369" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A92" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B92" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C92" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D92" s="369" t="s">
-        <v>2122</v>
-      </c>
-      <c r="E92" s="369" t="s">
-        <v>2123</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A93" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B93" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="C93" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D93" s="369" t="s">
-        <v>2124</v>
-      </c>
-      <c r="E93" s="369" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A94" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B94" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C94" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D94" s="369" t="s">
-        <v>2126</v>
-      </c>
-      <c r="E94" s="369" t="s">
-        <v>2127</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A95" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B95" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C95" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D95" s="369" t="s">
-        <v>2128</v>
-      </c>
-      <c r="E95" s="369" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A96" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B96" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C96" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D96" s="369" t="s">
-        <v>2130</v>
-      </c>
-      <c r="E96" s="369" t="s">
-        <v>2131</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A97" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B97" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C97" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D97" s="369" t="s">
-        <v>2132</v>
-      </c>
-      <c r="E97" s="369" t="s">
-        <v>2133</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A98" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B98" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C98" s="369" t="s">
-        <v>2010</v>
-      </c>
-      <c r="D98" s="369" t="s">
-        <v>2134</v>
-      </c>
-      <c r="E98" s="369" t="s">
-        <v>2135</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A99" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B99" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C99" s="369" t="s">
-        <v>2013</v>
-      </c>
-      <c r="D99" s="369" t="s">
-        <v>2136</v>
-      </c>
-      <c r="E99" s="369" t="s">
-        <v>2137</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="368" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B100" s="369" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C100" s="369" t="s">
-        <v>2016</v>
-      </c>
-      <c r="D100" s="369" t="s">
-        <v>2138</v>
-      </c>
-      <c r="E100" s="369" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" ht="15.6" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="370" t="s">
-        <v>2019</v>
-      </c>
-      <c r="B101" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="C101" s="371" t="s">
-        <v>2019</v>
-      </c>
-      <c r="D101" s="371" t="s">
-        <v>2008</v>
-      </c>
-      <c r="E101" s="371" t="s">
-        <v>2140</v>
-      </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="369"/>
-      <c r="B102" s="369"/>
-      <c r="C102" s="369"/>
-      <c r="D102" s="369"/>
-      <c r="E102" s="369"/>
+      <c r="A102" s="320"/>
+      <c r="B102" s="320"/>
+      <c r="C102" s="320"/>
+      <c r="D102" s="320"/>
+      <c r="E102" s="320"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="369"/>
-      <c r="B103" s="369"/>
-      <c r="C103" s="369"/>
-      <c r="D103" s="369"/>
-      <c r="E103" s="369"/>
+      <c r="A103" s="320"/>
+      <c r="B103" s="320"/>
+      <c r="C103" s="320"/>
+      <c r="D103" s="320"/>
+      <c r="E103" s="320"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="369"/>
-      <c r="B104" s="369"/>
-      <c r="C104" s="369"/>
-      <c r="D104" s="369"/>
-      <c r="E104" s="369"/>
+      <c r="A104" s="320"/>
+      <c r="B104" s="320"/>
+      <c r="C104" s="320"/>
+      <c r="D104" s="320"/>
+      <c r="E104" s="320"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A105" s="369"/>
-      <c r="B105" s="369"/>
-      <c r="C105" s="369"/>
-      <c r="D105" s="369"/>
-      <c r="E105" s="369"/>
+      <c r="A105" s="320"/>
+      <c r="B105" s="320"/>
+      <c r="C105" s="320"/>
+      <c r="D105" s="320"/>
+      <c r="E105" s="320"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="369"/>
-      <c r="B106" s="369"/>
-      <c r="C106" s="369"/>
-      <c r="D106" s="369"/>
-      <c r="E106" s="369"/>
+      <c r="A106" s="320"/>
+      <c r="B106" s="320"/>
+      <c r="C106" s="320"/>
+      <c r="D106" s="320"/>
+      <c r="E106" s="320"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="369"/>
-      <c r="B107" s="369"/>
-      <c r="C107" s="369"/>
-      <c r="D107" s="369"/>
-      <c r="E107" s="369"/>
+      <c r="A107" s="320"/>
+      <c r="B107" s="320"/>
+      <c r="C107" s="320"/>
+      <c r="D107" s="320"/>
+      <c r="E107" s="320"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A108" s="369"/>
-      <c r="B108" s="369"/>
-      <c r="C108" s="369"/>
-      <c r="D108" s="369"/>
-      <c r="E108" s="369"/>
+      <c r="A108" s="320"/>
+      <c r="B108" s="320"/>
+      <c r="C108" s="320"/>
+      <c r="D108" s="320"/>
+      <c r="E108" s="320"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="369"/>
-      <c r="B109" s="369"/>
-      <c r="C109" s="369"/>
-      <c r="D109" s="369"/>
-      <c r="E109" s="369"/>
+      <c r="A109" s="320"/>
+      <c r="B109" s="320"/>
+      <c r="C109" s="320"/>
+      <c r="D109" s="320"/>
+      <c r="E109" s="320"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="369"/>
-      <c r="B110" s="369"/>
-      <c r="C110" s="369"/>
-      <c r="D110" s="369"/>
-      <c r="E110" s="369"/>
+      <c r="A110" s="320"/>
+      <c r="B110" s="320"/>
+      <c r="C110" s="320"/>
+      <c r="D110" s="320"/>
+      <c r="E110" s="320"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="369"/>
-      <c r="B111" s="369"/>
-      <c r="C111" s="369"/>
-      <c r="D111" s="369"/>
-      <c r="E111" s="369"/>
+      <c r="A111" s="320"/>
+      <c r="B111" s="320"/>
+      <c r="C111" s="320"/>
+      <c r="D111" s="320"/>
+      <c r="E111" s="320"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A112" s="369"/>
-      <c r="B112" s="369"/>
-      <c r="C112" s="369"/>
-      <c r="D112" s="369"/>
-      <c r="E112" s="369"/>
+      <c r="A112" s="320"/>
+      <c r="B112" s="320"/>
+      <c r="C112" s="320"/>
+      <c r="D112" s="320"/>
+      <c r="E112" s="320"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A113" s="369"/>
-      <c r="B113" s="369"/>
-      <c r="C113" s="369"/>
-      <c r="D113" s="369"/>
-      <c r="E113" s="369"/>
+      <c r="A113" s="320"/>
+      <c r="B113" s="320"/>
+      <c r="C113" s="320"/>
+      <c r="D113" s="320"/>
+      <c r="E113" s="320"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A114" s="369"/>
-      <c r="B114" s="369"/>
-      <c r="C114" s="369"/>
-      <c r="D114" s="369"/>
-      <c r="E114" s="369"/>
+      <c r="A114" s="320"/>
+      <c r="B114" s="320"/>
+      <c r="C114" s="320"/>
+      <c r="D114" s="320"/>
+      <c r="E114" s="320"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A115" s="369"/>
-      <c r="B115" s="369"/>
-      <c r="C115" s="369"/>
-      <c r="D115" s="369"/>
-      <c r="E115" s="369"/>
+      <c r="A115" s="320"/>
+      <c r="B115" s="320"/>
+      <c r="C115" s="320"/>
+      <c r="D115" s="320"/>
+      <c r="E115" s="320"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A116" s="369"/>
-      <c r="B116" s="369"/>
-      <c r="C116" s="369"/>
-      <c r="D116" s="369"/>
-      <c r="E116" s="369"/>
+      <c r="A116" s="320"/>
+      <c r="B116" s="320"/>
+      <c r="C116" s="320"/>
+      <c r="D116" s="320"/>
+      <c r="E116" s="320"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A117" s="369"/>
-      <c r="B117" s="369"/>
-      <c r="C117" s="369"/>
-      <c r="D117" s="369"/>
-      <c r="E117" s="369"/>
+      <c r="A117" s="320"/>
+      <c r="B117" s="320"/>
+      <c r="C117" s="320"/>
+      <c r="D117" s="320"/>
+      <c r="E117" s="320"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A118" s="369"/>
-      <c r="B118" s="369"/>
-      <c r="C118" s="369"/>
-      <c r="D118" s="369"/>
-      <c r="E118" s="369"/>
+      <c r="A118" s="320"/>
+      <c r="B118" s="320"/>
+      <c r="C118" s="320"/>
+      <c r="D118" s="320"/>
+      <c r="E118" s="320"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A119" s="369"/>
-      <c r="B119" s="369"/>
-      <c r="C119" s="369"/>
-      <c r="D119" s="369"/>
-      <c r="E119" s="369"/>
+      <c r="A119" s="320"/>
+      <c r="B119" s="320"/>
+      <c r="C119" s="320"/>
+      <c r="D119" s="320"/>
+      <c r="E119" s="320"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A120" s="369"/>
-      <c r="B120" s="369"/>
-      <c r="C120" s="369"/>
-      <c r="D120" s="369"/>
-      <c r="E120" s="369"/>
+      <c r="A120" s="320"/>
+      <c r="B120" s="320"/>
+      <c r="C120" s="320"/>
+      <c r="D120" s="320"/>
+      <c r="E120" s="320"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A121" s="369"/>
-      <c r="B121" s="369"/>
-      <c r="C121" s="369"/>
-      <c r="D121" s="369"/>
-      <c r="E121" s="369"/>
+      <c r="A121" s="320"/>
+      <c r="B121" s="320"/>
+      <c r="C121" s="320"/>
+      <c r="D121" s="320"/>
+      <c r="E121" s="320"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A122" s="369"/>
-      <c r="B122" s="369"/>
-      <c r="C122" s="369"/>
-      <c r="D122" s="369"/>
-      <c r="E122" s="369"/>
+      <c r="A122" s="320"/>
+      <c r="B122" s="320"/>
+      <c r="C122" s="320"/>
+      <c r="D122" s="320"/>
+      <c r="E122" s="320"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A123" s="369"/>
-      <c r="B123" s="369"/>
-      <c r="C123" s="369"/>
-      <c r="D123" s="369"/>
-      <c r="E123" s="369"/>
+      <c r="A123" s="320"/>
+      <c r="B123" s="320"/>
+      <c r="C123" s="320"/>
+      <c r="D123" s="320"/>
+      <c r="E123" s="320"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="369"/>
-      <c r="B124" s="369"/>
-      <c r="C124" s="369"/>
-      <c r="D124" s="369"/>
-      <c r="E124" s="369"/>
+      <c r="A124" s="320"/>
+      <c r="B124" s="320"/>
+      <c r="C124" s="320"/>
+      <c r="D124" s="320"/>
+      <c r="E124" s="320"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A125" s="369"/>
-      <c r="B125" s="369"/>
-      <c r="C125" s="369"/>
-      <c r="D125" s="369"/>
-      <c r="E125" s="369"/>
+      <c r="A125" s="320"/>
+      <c r="B125" s="320"/>
+      <c r="C125" s="320"/>
+      <c r="D125" s="320"/>
+      <c r="E125" s="320"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A126" s="369"/>
-      <c r="B126" s="369"/>
-      <c r="C126" s="369"/>
-      <c r="D126" s="369"/>
-      <c r="E126" s="369"/>
+      <c r="A126" s="320"/>
+      <c r="B126" s="320"/>
+      <c r="C126" s="320"/>
+      <c r="D126" s="320"/>
+      <c r="E126" s="320"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A127" s="369"/>
-      <c r="B127" s="369"/>
-      <c r="C127" s="369"/>
-      <c r="D127" s="369"/>
-      <c r="E127" s="369"/>
+      <c r="A127" s="320"/>
+      <c r="B127" s="320"/>
+      <c r="C127" s="320"/>
+      <c r="D127" s="320"/>
+      <c r="E127" s="320"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A128" s="369"/>
-      <c r="B128" s="369"/>
-      <c r="C128" s="369"/>
-      <c r="D128" s="369"/>
-      <c r="E128" s="369"/>
+      <c r="A128" s="320"/>
+      <c r="B128" s="320"/>
+      <c r="C128" s="320"/>
+      <c r="D128" s="320"/>
+      <c r="E128" s="320"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A129" s="369"/>
-      <c r="B129" s="369"/>
-      <c r="C129" s="369"/>
-      <c r="D129" s="369"/>
-      <c r="E129" s="369"/>
+      <c r="A129" s="320"/>
+      <c r="B129" s="320"/>
+      <c r="C129" s="320"/>
+      <c r="D129" s="320"/>
+      <c r="E129" s="320"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A130" s="369"/>
-      <c r="B130" s="369"/>
-      <c r="C130" s="369"/>
-      <c r="D130" s="369"/>
-      <c r="E130" s="369"/>
+      <c r="A130" s="320"/>
+      <c r="B130" s="320"/>
+      <c r="C130" s="320"/>
+      <c r="D130" s="320"/>
+      <c r="E130" s="320"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A131" s="369"/>
-      <c r="B131" s="369"/>
-      <c r="C131" s="369"/>
-      <c r="D131" s="369"/>
-      <c r="E131" s="369"/>
+      <c r="A131" s="320"/>
+      <c r="B131" s="320"/>
+      <c r="C131" s="320"/>
+      <c r="D131" s="320"/>
+      <c r="E131" s="320"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A132" s="369"/>
-      <c r="B132" s="369"/>
-      <c r="C132" s="369"/>
-      <c r="D132" s="369"/>
-      <c r="E132" s="369"/>
+      <c r="A132" s="320"/>
+      <c r="B132" s="320"/>
+      <c r="C132" s="320"/>
+      <c r="D132" s="320"/>
+      <c r="E132" s="320"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A133" s="369"/>
-      <c r="B133" s="369"/>
-      <c r="C133" s="369"/>
-      <c r="D133" s="369"/>
-      <c r="E133" s="369"/>
+      <c r="A133" s="320"/>
+      <c r="B133" s="320"/>
+      <c r="C133" s="320"/>
+      <c r="D133" s="320"/>
+      <c r="E133" s="320"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A134" s="369"/>
-      <c r="B134" s="369"/>
-      <c r="C134" s="369"/>
-      <c r="D134" s="369"/>
-      <c r="E134" s="369"/>
+      <c r="A134" s="320"/>
+      <c r="B134" s="320"/>
+      <c r="C134" s="320"/>
+      <c r="D134" s="320"/>
+      <c r="E134" s="320"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A135" s="369"/>
-      <c r="B135" s="369"/>
-      <c r="C135" s="369"/>
-      <c r="D135" s="369"/>
-      <c r="E135" s="369"/>
+      <c r="A135" s="320"/>
+      <c r="B135" s="320"/>
+      <c r="C135" s="320"/>
+      <c r="D135" s="320"/>
+      <c r="E135" s="320"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A136" s="369"/>
-      <c r="B136" s="369"/>
-      <c r="C136" s="369"/>
-      <c r="D136" s="369"/>
-      <c r="E136" s="369"/>
+      <c r="A136" s="320"/>
+      <c r="B136" s="320"/>
+      <c r="C136" s="320"/>
+      <c r="D136" s="320"/>
+      <c r="E136" s="320"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A137" s="369"/>
-      <c r="B137" s="369"/>
-      <c r="C137" s="369"/>
-      <c r="D137" s="369"/>
-      <c r="E137" s="369"/>
+      <c r="A137" s="320"/>
+      <c r="B137" s="320"/>
+      <c r="C137" s="320"/>
+      <c r="D137" s="320"/>
+      <c r="E137" s="320"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A138" s="369"/>
-      <c r="B138" s="369"/>
-      <c r="C138" s="369"/>
-      <c r="D138" s="369"/>
-      <c r="E138" s="369"/>
+      <c r="A138" s="320"/>
+      <c r="B138" s="320"/>
+      <c r="C138" s="320"/>
+      <c r="D138" s="320"/>
+      <c r="E138" s="320"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A139" s="369"/>
-      <c r="B139" s="369"/>
-      <c r="C139" s="369"/>
-      <c r="D139" s="369"/>
-      <c r="E139" s="369"/>
+      <c r="A139" s="320"/>
+      <c r="B139" s="320"/>
+      <c r="C139" s="320"/>
+      <c r="D139" s="320"/>
+      <c r="E139" s="320"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A140" s="369"/>
-      <c r="B140" s="369"/>
-      <c r="C140" s="369"/>
-      <c r="D140" s="369"/>
-      <c r="E140" s="369"/>
+      <c r="A140" s="320"/>
+      <c r="B140" s="320"/>
+      <c r="C140" s="320"/>
+      <c r="D140" s="320"/>
+      <c r="E140" s="320"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A141" s="369"/>
-      <c r="B141" s="369"/>
-      <c r="C141" s="369"/>
-      <c r="D141" s="369"/>
-      <c r="E141" s="369"/>
+      <c r="A141" s="320"/>
+      <c r="B141" s="320"/>
+      <c r="C141" s="320"/>
+      <c r="D141" s="320"/>
+      <c r="E141" s="320"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A142" s="369"/>
-      <c r="B142" s="369"/>
-      <c r="C142" s="369"/>
-      <c r="D142" s="369"/>
-      <c r="E142" s="369"/>
+      <c r="A142" s="320"/>
+      <c r="B142" s="320"/>
+      <c r="C142" s="320"/>
+      <c r="D142" s="320"/>
+      <c r="E142" s="320"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A143" s="369"/>
-      <c r="B143" s="369"/>
-      <c r="C143" s="369"/>
-      <c r="D143" s="369"/>
-      <c r="E143" s="369"/>
+      <c r="A143" s="320"/>
+      <c r="B143" s="320"/>
+      <c r="C143" s="320"/>
+      <c r="D143" s="320"/>
+      <c r="E143" s="320"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A144" s="369"/>
-      <c r="B144" s="369"/>
-      <c r="C144" s="369"/>
-      <c r="D144" s="369"/>
-      <c r="E144" s="369"/>
+      <c r="A144" s="320"/>
+      <c r="B144" s="320"/>
+      <c r="C144" s="320"/>
+      <c r="D144" s="320"/>
+      <c r="E144" s="320"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A145" s="369"/>
-      <c r="B145" s="369"/>
-      <c r="C145" s="369"/>
-      <c r="D145" s="369"/>
-      <c r="E145" s="369"/>
+      <c r="A145" s="320"/>
+      <c r="B145" s="320"/>
+      <c r="C145" s="320"/>
+      <c r="D145" s="320"/>
+      <c r="E145" s="320"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A146" s="369"/>
-      <c r="B146" s="369"/>
-      <c r="C146" s="369"/>
-      <c r="D146" s="369"/>
-      <c r="E146" s="369"/>
+      <c r="A146" s="320"/>
+      <c r="B146" s="320"/>
+      <c r="C146" s="320"/>
+      <c r="D146" s="320"/>
+      <c r="E146" s="320"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A147" s="369"/>
-      <c r="B147" s="369"/>
-      <c r="C147" s="369"/>
-      <c r="D147" s="369"/>
-      <c r="E147" s="369"/>
+      <c r="A147" s="320"/>
+      <c r="B147" s="320"/>
+      <c r="C147" s="320"/>
+      <c r="D147" s="320"/>
+      <c r="E147" s="320"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A148" s="369"/>
-      <c r="B148" s="369"/>
-      <c r="C148" s="369"/>
-      <c r="D148" s="369"/>
-      <c r="E148" s="369"/>
+      <c r="A148" s="320"/>
+      <c r="B148" s="320"/>
+      <c r="C148" s="320"/>
+      <c r="D148" s="320"/>
+      <c r="E148" s="320"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A149" s="369"/>
-      <c r="B149" s="369"/>
-      <c r="C149" s="369"/>
-      <c r="D149" s="369"/>
-      <c r="E149" s="369"/>
+      <c r="A149" s="320"/>
+      <c r="B149" s="320"/>
+      <c r="C149" s="320"/>
+      <c r="D149" s="320"/>
+      <c r="E149" s="320"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A150" s="369"/>
-      <c r="B150" s="369"/>
-      <c r="C150" s="369"/>
-      <c r="D150" s="369"/>
-      <c r="E150" s="369"/>
+      <c r="A150" s="320"/>
+      <c r="B150" s="320"/>
+      <c r="C150" s="320"/>
+      <c r="D150" s="320"/>
+      <c r="E150" s="320"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A151" s="369"/>
-      <c r="B151" s="369"/>
-      <c r="C151" s="369"/>
-      <c r="D151" s="369"/>
-      <c r="E151" s="369"/>
+      <c r="A151" s="320"/>
+      <c r="B151" s="320"/>
+      <c r="C151" s="320"/>
+      <c r="D151" s="320"/>
+      <c r="E151" s="320"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A152" s="369"/>
-      <c r="B152" s="369"/>
-      <c r="C152" s="369"/>
-      <c r="D152" s="369"/>
-      <c r="E152" s="369"/>
+      <c r="A152" s="320"/>
+      <c r="B152" s="320"/>
+      <c r="C152" s="320"/>
+      <c r="D152" s="320"/>
+      <c r="E152" s="320"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A153" s="369"/>
-      <c r="B153" s="369"/>
-      <c r="C153" s="369"/>
-      <c r="D153" s="369"/>
-      <c r="E153" s="369"/>
+      <c r="A153" s="320"/>
+      <c r="B153" s="320"/>
+      <c r="C153" s="320"/>
+      <c r="D153" s="320"/>
+      <c r="E153" s="320"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A154" s="369"/>
-      <c r="B154" s="369"/>
-      <c r="C154" s="369"/>
-      <c r="D154" s="369"/>
-      <c r="E154" s="369"/>
+      <c r="A154" s="320"/>
+      <c r="B154" s="320"/>
+      <c r="C154" s="320"/>
+      <c r="D154" s="320"/>
+      <c r="E154" s="320"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A155" s="369"/>
-      <c r="B155" s="369"/>
-      <c r="C155" s="369"/>
-      <c r="D155" s="369"/>
-      <c r="E155" s="369"/>
+      <c r="A155" s="320"/>
+      <c r="B155" s="320"/>
+      <c r="C155" s="320"/>
+      <c r="D155" s="320"/>
+      <c r="E155" s="320"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A156" s="369"/>
-      <c r="B156" s="369"/>
-      <c r="C156" s="369"/>
-      <c r="D156" s="369"/>
-      <c r="E156" s="369"/>
+      <c r="A156" s="320"/>
+      <c r="B156" s="320"/>
+      <c r="C156" s="320"/>
+      <c r="D156" s="320"/>
+      <c r="E156" s="320"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A157" s="369"/>
-      <c r="B157" s="369"/>
-      <c r="C157" s="369"/>
-      <c r="D157" s="369"/>
-      <c r="E157" s="369"/>
+      <c r="A157" s="320"/>
+      <c r="B157" s="320"/>
+      <c r="C157" s="320"/>
+      <c r="D157" s="320"/>
+      <c r="E157" s="320"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A158" s="369"/>
-      <c r="B158" s="369"/>
-      <c r="C158" s="369"/>
-      <c r="D158" s="369"/>
-      <c r="E158" s="369"/>
+      <c r="A158" s="320"/>
+      <c r="B158" s="320"/>
+      <c r="C158" s="320"/>
+      <c r="D158" s="320"/>
+      <c r="E158" s="320"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A159" s="369"/>
-      <c r="B159" s="369"/>
-      <c r="C159" s="369"/>
-      <c r="D159" s="369"/>
-      <c r="E159" s="369"/>
+      <c r="A159" s="320"/>
+      <c r="B159" s="320"/>
+      <c r="C159" s="320"/>
+      <c r="D159" s="320"/>
+      <c r="E159" s="320"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A160" s="369"/>
-      <c r="B160" s="369"/>
-      <c r="C160" s="369"/>
-      <c r="D160" s="369"/>
-      <c r="E160" s="369"/>
+      <c r="A160" s="320"/>
+      <c r="B160" s="320"/>
+      <c r="C160" s="320"/>
+      <c r="D160" s="320"/>
+      <c r="E160" s="320"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A161" s="369"/>
-      <c r="B161" s="369"/>
-      <c r="C161" s="369"/>
-      <c r="D161" s="369"/>
-      <c r="E161" s="369"/>
+      <c r="A161" s="320"/>
+      <c r="B161" s="320"/>
+      <c r="C161" s="320"/>
+      <c r="D161" s="320"/>
+      <c r="E161" s="320"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A162" s="369"/>
-      <c r="B162" s="369"/>
-      <c r="C162" s="369"/>
-      <c r="D162" s="369"/>
-      <c r="E162" s="369"/>
+      <c r="A162" s="320"/>
+      <c r="B162" s="320"/>
+      <c r="C162" s="320"/>
+      <c r="D162" s="320"/>
+      <c r="E162" s="320"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A163" s="369"/>
-      <c r="B163" s="369"/>
-      <c r="C163" s="369"/>
-      <c r="D163" s="369"/>
-      <c r="E163" s="369"/>
+      <c r="A163" s="320"/>
+      <c r="B163" s="320"/>
+      <c r="C163" s="320"/>
+      <c r="D163" s="320"/>
+      <c r="E163" s="320"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A164" s="369"/>
-      <c r="B164" s="369"/>
-      <c r="C164" s="369"/>
-      <c r="D164" s="369"/>
-      <c r="E164" s="369"/>
+      <c r="A164" s="320"/>
+      <c r="B164" s="320"/>
+      <c r="C164" s="320"/>
+      <c r="D164" s="320"/>
+      <c r="E164" s="320"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A165" s="369"/>
-      <c r="B165" s="369"/>
-      <c r="C165" s="369"/>
-      <c r="D165" s="369"/>
-      <c r="E165" s="369"/>
+      <c r="A165" s="320"/>
+      <c r="B165" s="320"/>
+      <c r="C165" s="320"/>
+      <c r="D165" s="320"/>
+      <c r="E165" s="320"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A166" s="369"/>
-      <c r="B166" s="369"/>
-      <c r="C166" s="369"/>
-      <c r="D166" s="369"/>
-      <c r="E166" s="369"/>
+      <c r="A166" s="320"/>
+      <c r="B166" s="320"/>
+      <c r="C166" s="320"/>
+      <c r="D166" s="320"/>
+      <c r="E166" s="320"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A167" s="369"/>
-      <c r="B167" s="369"/>
-      <c r="C167" s="369"/>
-      <c r="D167" s="369"/>
-      <c r="E167" s="369"/>
+      <c r="A167" s="320"/>
+      <c r="B167" s="320"/>
+      <c r="C167" s="320"/>
+      <c r="D167" s="320"/>
+      <c r="E167" s="320"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A168" s="369"/>
-      <c r="B168" s="369"/>
-      <c r="C168" s="369"/>
-      <c r="D168" s="369"/>
-      <c r="E168" s="369"/>
+      <c r="A168" s="320"/>
+      <c r="B168" s="320"/>
+      <c r="C168" s="320"/>
+      <c r="D168" s="320"/>
+      <c r="E168" s="320"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A169" s="369"/>
-      <c r="B169" s="369"/>
-      <c r="C169" s="369"/>
-      <c r="D169" s="369"/>
-      <c r="E169" s="369"/>
+      <c r="A169" s="320"/>
+      <c r="B169" s="320"/>
+      <c r="C169" s="320"/>
+      <c r="D169" s="320"/>
+      <c r="E169" s="320"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A170" s="369"/>
-      <c r="B170" s="369"/>
-      <c r="C170" s="369"/>
-      <c r="D170" s="369"/>
-      <c r="E170" s="369"/>
+      <c r="A170" s="320"/>
+      <c r="B170" s="320"/>
+      <c r="C170" s="320"/>
+      <c r="D170" s="320"/>
+      <c r="E170" s="320"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A171" s="369"/>
-      <c r="B171" s="369"/>
-      <c r="C171" s="369"/>
-      <c r="D171" s="369"/>
-      <c r="E171" s="369"/>
+      <c r="A171" s="320"/>
+      <c r="B171" s="320"/>
+      <c r="C171" s="320"/>
+      <c r="D171" s="320"/>
+      <c r="E171" s="320"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A172" s="369"/>
-      <c r="B172" s="369"/>
-      <c r="C172" s="369"/>
-      <c r="D172" s="369"/>
-      <c r="E172" s="369"/>
+      <c r="A172" s="320"/>
+      <c r="B172" s="320"/>
+      <c r="C172" s="320"/>
+      <c r="D172" s="320"/>
+      <c r="E172" s="320"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A173" s="369"/>
-      <c r="B173" s="369"/>
-      <c r="C173" s="369"/>
-      <c r="D173" s="369"/>
-      <c r="E173" s="369"/>
+      <c r="A173" s="320"/>
+      <c r="B173" s="320"/>
+      <c r="C173" s="320"/>
+      <c r="D173" s="320"/>
+      <c r="E173" s="320"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A174" s="369"/>
-      <c r="B174" s="369"/>
-      <c r="C174" s="369"/>
-      <c r="D174" s="369"/>
-      <c r="E174" s="369"/>
+      <c r="A174" s="320"/>
+      <c r="B174" s="320"/>
+      <c r="C174" s="320"/>
+      <c r="D174" s="320"/>
+      <c r="E174" s="320"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A175" s="369"/>
-      <c r="B175" s="369"/>
-      <c r="C175" s="369"/>
-      <c r="D175" s="369"/>
-      <c r="E175" s="369"/>
+      <c r="A175" s="320"/>
+      <c r="B175" s="320"/>
+      <c r="C175" s="320"/>
+      <c r="D175" s="320"/>
+      <c r="E175" s="320"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A176" s="369"/>
-      <c r="B176" s="369"/>
-      <c r="C176" s="369"/>
-      <c r="D176" s="369"/>
-      <c r="E176" s="369"/>
+      <c r="A176" s="320"/>
+      <c r="B176" s="320"/>
+      <c r="C176" s="320"/>
+      <c r="D176" s="320"/>
+      <c r="E176" s="320"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A177" s="369"/>
-      <c r="B177" s="369"/>
-      <c r="C177" s="369"/>
-      <c r="D177" s="369"/>
-      <c r="E177" s="369"/>
+      <c r="A177" s="320"/>
+      <c r="B177" s="320"/>
+      <c r="C177" s="320"/>
+      <c r="D177" s="320"/>
+      <c r="E177" s="320"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A178" s="369"/>
-      <c r="B178" s="369"/>
-      <c r="C178" s="369"/>
-      <c r="D178" s="369"/>
-      <c r="E178" s="369"/>
+      <c r="A178" s="320"/>
+      <c r="B178" s="320"/>
+      <c r="C178" s="320"/>
+      <c r="D178" s="320"/>
+      <c r="E178" s="320"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A179" s="369"/>
-      <c r="B179" s="369"/>
-      <c r="C179" s="369"/>
-      <c r="D179" s="369"/>
-      <c r="E179" s="369"/>
+      <c r="A179" s="320"/>
+      <c r="B179" s="320"/>
+      <c r="C179" s="320"/>
+      <c r="D179" s="320"/>
+      <c r="E179" s="320"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A180" s="369"/>
-      <c r="B180" s="369"/>
-      <c r="C180" s="369"/>
-      <c r="D180" s="369"/>
-      <c r="E180" s="369"/>
+      <c r="A180" s="320"/>
+      <c r="B180" s="320"/>
+      <c r="C180" s="320"/>
+      <c r="D180" s="320"/>
+      <c r="E180" s="320"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A181" s="369"/>
-      <c r="B181" s="369"/>
-      <c r="C181" s="369"/>
-      <c r="D181" s="369"/>
-      <c r="E181" s="369"/>
+      <c r="A181" s="320"/>
+      <c r="B181" s="320"/>
+      <c r="C181" s="320"/>
+      <c r="D181" s="320"/>
+      <c r="E181" s="320"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A182" s="369"/>
-      <c r="B182" s="369"/>
-      <c r="C182" s="369"/>
-      <c r="D182" s="369"/>
-      <c r="E182" s="369"/>
+      <c r="A182" s="320"/>
+      <c r="B182" s="320"/>
+      <c r="C182" s="320"/>
+      <c r="D182" s="320"/>
+      <c r="E182" s="320"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A183" s="369"/>
-      <c r="B183" s="369"/>
-      <c r="C183" s="369"/>
-      <c r="D183" s="369"/>
-      <c r="E183" s="369"/>
+      <c r="A183" s="320"/>
+      <c r="B183" s="320"/>
+      <c r="C183" s="320"/>
+      <c r="D183" s="320"/>
+      <c r="E183" s="320"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A184" s="369"/>
-      <c r="B184" s="369"/>
-      <c r="C184" s="369"/>
-      <c r="D184" s="369"/>
-      <c r="E184" s="369"/>
+      <c r="A184" s="320"/>
+      <c r="B184" s="320"/>
+      <c r="C184" s="320"/>
+      <c r="D184" s="320"/>
+      <c r="E184" s="320"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A185" s="369"/>
-      <c r="B185" s="369"/>
-      <c r="C185" s="369"/>
-      <c r="D185" s="369"/>
-      <c r="E185" s="369"/>
+      <c r="A185" s="320"/>
+      <c r="B185" s="320"/>
+      <c r="C185" s="320"/>
+      <c r="D185" s="320"/>
+      <c r="E185" s="320"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -16800,7 +16275,7 @@
         <v>1659</v>
       </c>
       <c r="E3" s="87" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="F3" s="87"/>
     </row>
@@ -16831,7 +16306,7 @@
         <v>1632</v>
       </c>
       <c r="D5" s="87" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
       <c r="E5" s="87" t="s">
         <v>1657</v>
@@ -16884,7 +16359,7 @@
         <v>1636</v>
       </c>
       <c r="E8" s="270" t="s">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="F8" s="270"/>
     </row>
@@ -16934,7 +16409,7 @@
         <v>1650</v>
       </c>
       <c r="E11" s="87" t="s">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="F11" s="87"/>
     </row>
@@ -16952,7 +16427,7 @@
         <v>1642</v>
       </c>
       <c r="E12" s="270" t="s">
-        <v>1820</v>
+        <v>1816</v>
       </c>
       <c r="F12" s="270"/>
     </row>
@@ -16964,7 +16439,7 @@
         <v>40</v>
       </c>
       <c r="C13" s="87" t="s">
-        <v>1847</v>
+        <v>1840</v>
       </c>
       <c r="D13" s="87" t="s">
         <v>1643</v>
@@ -16973,7 +16448,7 @@
         <v>1651</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>1839</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="14" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17058,7 +16533,7 @@
         <v>1663</v>
       </c>
       <c r="E18" s="268" t="s">
-        <v>1816</v>
+        <v>1812</v>
       </c>
       <c r="F18" s="268"/>
     </row>
@@ -17089,10 +16564,10 @@
         <v>1664</v>
       </c>
       <c r="D20" s="270" t="s">
-        <v>1810</v>
+        <v>1806</v>
       </c>
       <c r="E20" s="270" t="s">
-        <v>1821</v>
+        <v>1817</v>
       </c>
       <c r="F20" s="270"/>
     </row>
@@ -17110,7 +16585,7 @@
         <v>1665</v>
       </c>
       <c r="E21" s="87" t="s">
-        <v>1817</v>
+        <v>1813</v>
       </c>
       <c r="F21" s="87"/>
     </row>
@@ -17128,7 +16603,7 @@
         <v>1667</v>
       </c>
       <c r="E22" s="270" t="s">
-        <v>1818</v>
+        <v>1814</v>
       </c>
       <c r="F22" s="270"/>
     </row>
@@ -17162,7 +16637,7 @@
         <v>1675</v>
       </c>
       <c r="E24" s="270" t="s">
-        <v>1823</v>
+        <v>1819</v>
       </c>
       <c r="F24" s="270"/>
     </row>
@@ -17180,7 +16655,7 @@
         <v>1673</v>
       </c>
       <c r="E25" s="88" t="s">
-        <v>1822</v>
+        <v>1818</v>
       </c>
       <c r="F25" s="88"/>
     </row>
@@ -17214,7 +16689,7 @@
         <v>1678</v>
       </c>
       <c r="E27" s="87" t="s">
-        <v>1827</v>
+        <v>1823</v>
       </c>
       <c r="F27" s="87" t="s">
         <v>1727</v>
@@ -17250,7 +16725,7 @@
         <v>1279</v>
       </c>
       <c r="E29" s="87" t="s">
-        <v>1824</v>
+        <v>1820</v>
       </c>
       <c r="F29" s="87"/>
     </row>
@@ -17308,11 +16783,11 @@
         <v>83</v>
       </c>
       <c r="C33" s="88" t="s">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="D33" s="88"/>
       <c r="E33" s="88" t="s">
-        <v>1828</v>
+        <v>1824</v>
       </c>
       <c r="F33" s="88"/>
     </row>
@@ -17378,7 +16853,7 @@
         <v>1695</v>
       </c>
       <c r="E37" s="87" t="s">
-        <v>1829</v>
+        <v>1825</v>
       </c>
       <c r="F37" s="87"/>
     </row>
@@ -17396,7 +16871,7 @@
         <v>1718</v>
       </c>
       <c r="E38" s="288" t="s">
-        <v>1844</v>
+        <v>1839</v>
       </c>
       <c r="F38" s="288"/>
     </row>
@@ -17414,7 +16889,7 @@
         <v>1698</v>
       </c>
       <c r="E39" s="87" t="s">
-        <v>1830</v>
+        <v>1826</v>
       </c>
       <c r="F39" s="87"/>
     </row>
@@ -17445,7 +16920,7 @@
         <v>1700</v>
       </c>
       <c r="D41" s="88" t="s">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="E41" s="88"/>
       <c r="F41" s="88"/>
@@ -17464,7 +16939,7 @@
         <v>1705</v>
       </c>
       <c r="E42" s="268" t="s">
-        <v>1826</v>
+        <v>1822</v>
       </c>
       <c r="F42" s="268"/>
     </row>
@@ -17498,7 +16973,7 @@
         <v>1708</v>
       </c>
       <c r="E44" s="270" t="s">
-        <v>1831</v>
+        <v>1827</v>
       </c>
       <c r="F44" s="270"/>
     </row>
@@ -17516,7 +16991,7 @@
         <v>1716</v>
       </c>
       <c r="E45" s="87" t="s">
-        <v>1834</v>
+        <v>1830</v>
       </c>
       <c r="F45" s="87"/>
     </row>
@@ -17550,7 +17025,7 @@
         <v>1717</v>
       </c>
       <c r="E47" s="87" t="s">
-        <v>1825</v>
+        <v>1821</v>
       </c>
       <c r="F47" s="87"/>
     </row>
@@ -17582,7 +17057,7 @@
         <v>1720</v>
       </c>
       <c r="E49" s="88" t="s">
-        <v>1835</v>
+        <v>1831</v>
       </c>
       <c r="F49" s="88"/>
     </row>
@@ -17594,11 +17069,11 @@
         <v>122</v>
       </c>
       <c r="C50" s="86" t="s">
-        <v>1815</v>
+        <v>1811</v>
       </c>
       <c r="D50" s="268"/>
       <c r="E50" s="268" t="s">
-        <v>1845</v>
+        <v>2154</v>
       </c>
       <c r="F50" s="268" t="s">
         <v>1702</v>
@@ -17612,14 +17087,14 @@
         <v>126</v>
       </c>
       <c r="C51" s="87" t="s">
-        <v>1736</v>
+        <v>1734</v>
       </c>
       <c r="D51" s="87"/>
       <c r="E51" s="87" t="s">
-        <v>1846</v>
+        <v>2153</v>
       </c>
       <c r="F51" s="87" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17630,14 +17105,14 @@
         <v>129</v>
       </c>
       <c r="C52" s="87" t="s">
-        <v>1739</v>
+        <v>1736</v>
       </c>
       <c r="D52" s="270"/>
       <c r="E52" s="270" t="s">
-        <v>1836</v>
+        <v>2155</v>
       </c>
       <c r="F52" s="270" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17648,10 +17123,12 @@
         <v>132</v>
       </c>
       <c r="C53" s="87" t="s">
-        <v>1737</v>
+        <v>2151</v>
       </c>
       <c r="D53" s="87"/>
-      <c r="E53" s="87"/>
+      <c r="E53" s="87" t="s">
+        <v>2148</v>
+      </c>
       <c r="F53" s="87"/>
     </row>
     <row r="54" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17662,10 +17139,12 @@
         <v>135</v>
       </c>
       <c r="C54" s="87" t="s">
-        <v>1741</v>
+        <v>1738</v>
       </c>
       <c r="D54" s="270"/>
-      <c r="E54" s="270"/>
+      <c r="E54" s="270" t="s">
+        <v>2147</v>
+      </c>
       <c r="F54" s="270"/>
     </row>
     <row r="55" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17676,11 +17155,9 @@
         <v>137</v>
       </c>
       <c r="C55" s="87" t="s">
-        <v>1733</v>
-      </c>
-      <c r="D55" s="87" t="s">
-        <v>1734</v>
-      </c>
+        <v>2152</v>
+      </c>
+      <c r="D55" s="87"/>
       <c r="E55" s="87"/>
       <c r="F55" s="87"/>
     </row>
@@ -17692,10 +17169,10 @@
         <v>140</v>
       </c>
       <c r="C56" s="87" t="s">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="D56" s="270" t="s">
-        <v>1735</v>
+        <v>1733</v>
       </c>
       <c r="E56" s="270"/>
       <c r="F56" s="270"/>
@@ -17708,10 +17185,10 @@
         <v>143</v>
       </c>
       <c r="C57" s="88" t="s">
-        <v>1752</v>
+        <v>1748</v>
       </c>
       <c r="D57" s="88" t="s">
-        <v>1738</v>
+        <v>1735</v>
       </c>
       <c r="E57" s="88"/>
       <c r="F57" s="88"/>
@@ -17724,11 +17201,11 @@
         <v>146</v>
       </c>
       <c r="C58" s="86" t="s">
-        <v>1744</v>
+        <v>1741</v>
       </c>
       <c r="D58" s="268"/>
       <c r="E58" s="268" t="s">
-        <v>1755</v>
+        <v>1751</v>
       </c>
       <c r="F58" s="268"/>
     </row>
@@ -17740,11 +17217,11 @@
         <v>149</v>
       </c>
       <c r="C59" s="87" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="D59" s="87"/>
       <c r="E59" s="87" t="s">
-        <v>1753</v>
+        <v>1749</v>
       </c>
       <c r="F59" s="87"/>
     </row>
@@ -17756,11 +17233,11 @@
         <v>151</v>
       </c>
       <c r="C60" s="87" t="s">
-        <v>1754</v>
+        <v>1750</v>
       </c>
       <c r="D60" s="270"/>
       <c r="E60" s="270" t="s">
-        <v>1833</v>
+        <v>1829</v>
       </c>
       <c r="F60" s="270"/>
     </row>
@@ -17772,10 +17249,10 @@
         <v>154</v>
       </c>
       <c r="C61" s="87" t="s">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="D61" s="87" t="s">
-        <v>1746</v>
+        <v>1743</v>
       </c>
       <c r="E61" s="87"/>
       <c r="F61" s="87"/>
@@ -17788,11 +17265,11 @@
         <v>156</v>
       </c>
       <c r="C62" s="87" t="s">
-        <v>1812</v>
+        <v>1808</v>
       </c>
       <c r="D62" s="270"/>
       <c r="E62" s="270" t="s">
-        <v>1813</v>
+        <v>1809</v>
       </c>
       <c r="F62" s="270"/>
     </row>
@@ -17804,12 +17281,14 @@
         <v>158</v>
       </c>
       <c r="C63" s="87" t="s">
-        <v>1747</v>
+        <v>1744</v>
       </c>
       <c r="D63" s="87" t="s">
-        <v>1748</v>
-      </c>
-      <c r="E63" s="87"/>
+        <v>2149</v>
+      </c>
+      <c r="E63" s="87" t="s">
+        <v>2150</v>
+      </c>
       <c r="F63" s="87"/>
     </row>
     <row r="64" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -17820,7 +17299,7 @@
         <v>160</v>
       </c>
       <c r="C64" s="87" t="s">
-        <v>1749</v>
+        <v>1745</v>
       </c>
       <c r="D64" s="270"/>
       <c r="E64" s="270"/>
@@ -17834,10 +17313,10 @@
         <v>163</v>
       </c>
       <c r="C65" s="88" t="s">
-        <v>1750</v>
+        <v>1746</v>
       </c>
       <c r="D65" s="88" t="s">
-        <v>1751</v>
+        <v>1747</v>
       </c>
       <c r="E65" s="88"/>
       <c r="F65" s="88"/>
@@ -17850,11 +17329,11 @@
         <v>165</v>
       </c>
       <c r="C66" s="86" t="s">
-        <v>1757</v>
+        <v>1753</v>
       </c>
       <c r="D66" s="268"/>
       <c r="E66" s="268" t="s">
-        <v>1832</v>
+        <v>1828</v>
       </c>
       <c r="F66" s="268"/>
     </row>
@@ -17866,11 +17345,11 @@
         <v>168</v>
       </c>
       <c r="C67" s="87" t="s">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="D67" s="87"/>
       <c r="E67" s="87" t="s">
-        <v>1816</v>
+        <v>1812</v>
       </c>
       <c r="F67" s="87"/>
     </row>
@@ -17882,16 +17361,16 @@
         <v>1273</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1759</v>
+        <v>1755</v>
       </c>
       <c r="D68" s="272" t="s">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="E68" s="272" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="F68" s="272" t="s">
-        <v>1840</v>
+        <v>1835</v>
       </c>
     </row>
   </sheetData>
@@ -18041,7 +17520,7 @@
     </row>
     <row r="6" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="167" t="s">
-        <v>1848</v>
+        <v>1841</v>
       </c>
       <c r="B6" s="169" t="s">
         <v>1506</v>
@@ -18064,7 +17543,7 @@
     </row>
     <row r="7" spans="1:8" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="167" t="s">
-        <v>1849</v>
+        <v>1842</v>
       </c>
       <c r="B7" s="169" t="s">
         <v>1532</v>
@@ -21212,7 +20691,7 @@
         <v>1104</v>
       </c>
       <c r="F24" s="99" t="s">
-        <v>1803</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="25" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -21652,7 +21131,7 @@
         <v>1191</v>
       </c>
       <c r="F46" s="99" t="s">
-        <v>1804</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="47" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -21692,7 +21171,7 @@
         <v>1198</v>
       </c>
       <c r="F48" s="99" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="49" spans="1:6" s="1" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -22046,7 +21525,7 @@
         <v>1267</v>
       </c>
       <c r="D66" s="86" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="E66" s="86" t="s">
         <v>1268</v>
@@ -22066,7 +21545,7 @@
         <v>1270</v>
       </c>
       <c r="D67" s="87" t="s">
-        <v>1809</v>
+        <v>1805</v>
       </c>
       <c r="E67" s="87" t="s">
         <v>1271</v>
@@ -22080,19 +21559,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="88" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="C68" s="88" t="s">
-        <v>1807</v>
+        <v>1803</v>
       </c>
       <c r="D68" s="88" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="E68" s="88" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="F68" s="101" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
     </row>
   </sheetData>
@@ -23106,16 +22585,16 @@
         <v>122</v>
       </c>
       <c r="C50" s="250" t="s">
-        <v>1762</v>
+        <v>1758</v>
       </c>
       <c r="D50" s="289" t="s">
-        <v>1763</v>
+        <v>1759</v>
       </c>
       <c r="E50" s="251" t="s">
-        <v>1764</v>
+        <v>1760</v>
       </c>
       <c r="F50" s="252" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
     </row>
     <row r="51" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -23126,16 +22605,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="253" t="s">
-        <v>1766</v>
+        <v>1762</v>
       </c>
       <c r="D51" s="254" t="s">
-        <v>1767</v>
+        <v>1763</v>
       </c>
       <c r="E51" s="140" t="s">
-        <v>1768</v>
+        <v>1764</v>
       </c>
       <c r="F51" s="249" t="s">
-        <v>1769</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -23146,16 +22625,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="253" t="s">
-        <v>1770</v>
+        <v>1766</v>
       </c>
       <c r="D52" s="254" t="s">
-        <v>1771</v>
+        <v>1767</v>
       </c>
       <c r="E52" s="140" t="s">
-        <v>1772</v>
+        <v>1768</v>
       </c>
       <c r="F52" s="249" t="s">
-        <v>1773</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -23386,16 +22865,16 @@
         <v>160</v>
       </c>
       <c r="C64" s="253" t="s">
-        <v>1774</v>
+        <v>1770</v>
       </c>
       <c r="D64" s="254" t="s">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="E64" s="140" t="s">
-        <v>1776</v>
+        <v>1772</v>
       </c>
       <c r="F64" s="249" t="s">
-        <v>1777</v>
+        <v>1773</v>
       </c>
     </row>
     <row r="65" spans="1:6" s="54" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -23426,16 +22905,16 @@
         <v>165</v>
       </c>
       <c r="C66" s="250" t="s">
-        <v>1778</v>
+        <v>1774</v>
       </c>
       <c r="D66" s="289" t="s">
-        <v>1779</v>
+        <v>1775</v>
       </c>
       <c r="E66" s="193" t="s">
         <v>761</v>
       </c>
       <c r="F66" s="252" t="s">
-        <v>1780</v>
+        <v>1776</v>
       </c>
     </row>
     <row r="67" spans="1:6" s="102" customFormat="1" ht="16.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -23446,10 +22925,10 @@
         <v>168</v>
       </c>
       <c r="C67" s="255" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="D67" s="256" t="s">
-        <v>1782</v>
+        <v>1778</v>
       </c>
       <c r="E67" s="199" t="s">
         <v>762</v>
@@ -23466,16 +22945,16 @@
         <v>1273</v>
       </c>
       <c r="C68" s="264" t="s">
-        <v>1783</v>
+        <v>1779</v>
       </c>
       <c r="D68" s="265" t="s">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="E68" s="266" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="F68" s="267" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
     </row>
   </sheetData>
@@ -24489,7 +23968,7 @@
         <v>122</v>
       </c>
       <c r="C50" s="224" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="D50" s="225" t="s">
         <v>956</v>
@@ -24509,16 +23988,16 @@
         <v>126</v>
       </c>
       <c r="C51" s="227" t="s">
-        <v>1788</v>
+        <v>1784</v>
       </c>
       <c r="D51" s="228" t="s">
-        <v>1789</v>
+        <v>1785</v>
       </c>
       <c r="E51" s="229" t="s">
-        <v>1790</v>
+        <v>1786</v>
       </c>
       <c r="F51" s="219" t="s">
-        <v>1791</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="52" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -24529,16 +24008,16 @@
         <v>129</v>
       </c>
       <c r="C52" s="227" t="s">
-        <v>1792</v>
+        <v>1788</v>
       </c>
       <c r="D52" s="228" t="s">
-        <v>1793</v>
+        <v>1789</v>
       </c>
       <c r="E52" s="229" t="s">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="F52" s="219" t="s">
-        <v>1795</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="53" spans="1:6" s="54" customFormat="1" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
@@ -24769,7 +24248,7 @@
         <v>160</v>
       </c>
       <c r="C64" s="227" t="s">
-        <v>1796</v>
+        <v>1792</v>
       </c>
       <c r="D64" s="228" t="s">
         <v>1003</v>
@@ -24809,7 +24288,7 @@
         <v>165</v>
       </c>
       <c r="C66" s="212" t="s">
-        <v>1797</v>
+        <v>1793</v>
       </c>
       <c r="D66" s="213" t="s">
         <v>1010</v>
@@ -24829,16 +24308,16 @@
         <v>168</v>
       </c>
       <c r="C67" s="216" t="s">
-        <v>1798</v>
+        <v>1794</v>
       </c>
       <c r="D67" s="217" t="s">
         <v>1013</v>
       </c>
       <c r="E67" s="299" t="s">
-        <v>1799</v>
+        <v>1795</v>
       </c>
       <c r="F67" s="296" t="s">
-        <v>1800</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="68" spans="1:6" ht="31.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -24846,19 +24325,19 @@
         <v>0</v>
       </c>
       <c r="B68" s="77" t="s">
-        <v>1801</v>
+        <v>1797</v>
       </c>
       <c r="C68" s="293" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="D68" s="294" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="E68" s="300" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
       <c r="F68" s="297" t="s">
-        <v>1802</v>
+        <v>1798</v>
       </c>
     </row>
   </sheetData>
